--- a/variable_selection/spearman_corr_median.xlsx
+++ b/variable_selection/spearman_corr_median.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ36"/>
+  <dimension ref="A1:AM39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,60 +546,75 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>TNMN</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>TNMM</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>STAGE</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>RAI</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>RAIDOSE</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>TSH PRE RAI</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>TG PRE RAI</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>ANTI TG PRE RAI (POSITIVE or NEGATIVE)</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">ANTI TG PRE RAI </t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>OUTCOMEFOLLOWUP_MONTHSPOSTSURGERY</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>TSH FOLLOW UP</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>TG FOLLOW UP</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>ANTI TG FOLLOW UP (POSITIVE or NEGATIVE)</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>ANTI TG FOLLOW UP</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>SUBTYPE_FOLLI_PAPIL</t>
         </is>
@@ -615,106 +630,115 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05840913162958681</v>
+        <v>0.01269073506129029</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04714330601398951</v>
+        <v>0.03687129697282684</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003665215821062397</v>
+        <v>0.01036870963692328</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1016654006757328</v>
+        <v>-0.1522337324098139</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02574630226727489</v>
+        <v>-0.01065204875704046</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01013092195425306</v>
+        <v>0.02051396006238272</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1489856641114466</v>
+        <v>0.1153968777790513</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.0627958055361949</v>
+        <v>-0.03738738940810835</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1683119115507617</v>
+        <v>-0.1646061582476439</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03275858355284983</v>
+        <v>0.01620244947506944</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.06255715580029865</v>
+        <v>-0.04606020581379727</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1539522245029346</v>
+        <v>-0.1435335702701097</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1514167333014552</v>
+        <v>-0.1184327178731212</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.005452022852055137</v>
+        <v>0.02781912045315838</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.06989524594587206</v>
+        <v>0.02283502544625617</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05265807539078503</v>
+        <v>0.09373332085645929</v>
       </c>
       <c r="S2" t="n">
-        <v>0.08917582125511839</v>
+        <v>0.1115595621038911</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05091042687031718</v>
+        <v>0.1088865201705398</v>
       </c>
       <c r="U2" t="n">
-        <v>0.18095694988456</v>
+        <v>0.1327240389581617</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1024243210168888</v>
+        <v>-0.1166667338227477</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02204201266678182</v>
+        <v>0.007133991226581892</v>
       </c>
       <c r="X2" t="n">
-        <v>0.04464680490417582</v>
+        <v>0.01159709222273092</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.09426868850895498</v>
+        <v>0.05547784873328553</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00802307081099014</v>
+        <v>-0.04198304653301659</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1127873299937686</v>
+        <v>0.04876424449888972</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.09815269968561122</v>
+        <v>0.08086035571558764</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.09924073886120452</v>
+        <v>-0.01963721415421305</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.09820424347704894</v>
+        <v>0.03413257328241422</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.05333849617270321</v>
+        <v>0.05010503584552657</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.02396956834931738</v>
+        <v>0.03905321747505927</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.1628376440033716</v>
+        <v>0.008465499285456039</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.1274414124715532</v>
+        <v>-0.02660642310995417</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.04927651108218349</v>
+        <v>0.02070778977938564</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.0378516752470492</v>
+        <v>0.06055183065567665</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-0.1199856792654779</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.04369434761947667</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-0.02356751784422266</v>
       </c>
     </row>
     <row r="3">
@@ -724,109 +748,118 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05840913162958681</v>
+        <v>0.01269073506129029</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04660573683078015</v>
+        <v>0.02578290024086439</v>
       </c>
       <c r="E3" t="n">
-        <v>0.103946041899407</v>
+        <v>0.07766483000761434</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1013010524471818</v>
+        <v>-0.09216899693437838</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04058985997493433</v>
+        <v>0.1094228685528726</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1603561052605443</v>
+        <v>-0.1437171873721365</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01443730561699839</v>
+        <v>0.01138921639626691</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1733897339763425</v>
+        <v>0.1900547927784644</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1196645657147427</v>
+        <v>-0.09065413764237114</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.02308323428795547</v>
+        <v>-0.02326956413808288</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.04667640752380986</v>
+        <v>-0.01835967955208173</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1519083646892877</v>
+        <v>-0.1316613877317259</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.001611812638787804</v>
+        <v>0.01352938446577086</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01647173080772497</v>
+        <v>0.002698547294766297</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2893062550025601</v>
+        <v>0.143028057646777</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.256243815979217</v>
+        <v>-0.142537494472403</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.317341753869948</v>
+        <v>-0.2007287471480622</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2966908451547349</v>
+        <v>-0.2053999318983533</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.03824453429304032</v>
+        <v>-0.07482035525590021</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.03809087403201362</v>
+        <v>-0.02168714376365774</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.09987029793234278</v>
+        <v>-0.1018875163575239</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.08111176013501493</v>
+        <v>-0.07258700476579903</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.07920133541101212</v>
+        <v>-0.1789914924324122</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.05505549379496147</v>
+        <v>0.0003435624366104266</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0148889500888936</v>
+        <v>0.2983461426226515</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.03022212873463089</v>
+        <v>0.04860203217566524</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.06634559493096817</v>
+        <v>-0.07612100916365676</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.07140966344039418</v>
+        <v>-0.1809373139895543</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.1247947155569244</v>
+        <v>-0.1453224209078465</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.04137888902262456</v>
+        <v>0.07794497293544218</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.04837323216622016</v>
+        <v>0.02281569781239416</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.05262196878056016</v>
+        <v>-0.07829998742629059</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.04640790316026284</v>
+        <v>0.02286278125906108</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1109755947232009</v>
+        <v>-0.04468516456514963</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.04331934169259238</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.02878162375726544</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.09285420806081821</v>
       </c>
     </row>
     <row r="4">
@@ -836,109 +869,118 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04714330601398951</v>
+        <v>0.03687129697282684</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04660573683078015</v>
+        <v>0.02578290024086439</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02702261376687274</v>
+        <v>0.03462538369366576</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.07719900261560034</v>
+        <v>-0.1554273563116664</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009684817758079741</v>
+        <v>-0.03905924321035227</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.07996401141339073</v>
+        <v>-0.09596103220008803</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03470199236178249</v>
+        <v>-0.0008797728635904786</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01540629572839074</v>
+        <v>0.01305887238962482</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1730986572829828</v>
+        <v>-0.1825901739185543</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001532307558284585</v>
+        <v>-0.01023648448285784</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.05590502523691093</v>
+        <v>-0.0705110790092968</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1096959754194636</v>
+        <v>-0.09839321867787555</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.02372886259075345</v>
+        <v>-0.02713256739816396</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06710865131166459</v>
+        <v>0.02352945977916111</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1220688091163222</v>
+        <v>0.1772591976667311</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.1106061587271768</v>
+        <v>0.00386801670923928</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1082774879038943</v>
+        <v>0.01537649932899007</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1044836177880937</v>
+        <v>0.01467616265921041</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08178134419514629</v>
+        <v>0.08818496857142781</v>
       </c>
       <c r="V4" t="n">
-        <v>0.006264882135330589</v>
+        <v>0.02386939372158895</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.08056315719215404</v>
+        <v>-0.07343917412845845</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.006693063143880768</v>
+        <v>-0.0317414117742708</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.1191207018988408</v>
+        <v>-0.02914510365667243</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.04892190223316589</v>
+        <v>-0.03212022651322469</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1025946107809987</v>
+        <v>0.01385546075246977</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1325750851981729</v>
+        <v>0.02833972317983941</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1358103372966104</v>
+        <v>-0.06766548818462662</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.1404601227226843</v>
+        <v>0.005455005854045259</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.1062061875588359</v>
+        <v>-0.01239950109491967</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.004608994858731909</v>
+        <v>0.0205109406573495</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.02135076009822365</v>
+        <v>0.02760907933986359</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.07259726776105671</v>
+        <v>0.07389975312941718</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.08256437881426303</v>
+        <v>0.08268452407301209</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.1249026030329004</v>
+        <v>0.04113830011822168</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.07258433773300187</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.01752410800053829</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-0.132974891054905</v>
       </c>
     </row>
     <row r="5">
@@ -948,109 +990,118 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003665215821062397</v>
+        <v>0.01036870963692328</v>
       </c>
       <c r="C5" t="n">
-        <v>0.103946041899407</v>
+        <v>0.07766483000761434</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02702261376687274</v>
+        <v>0.03462538369366576</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.02138497572077136</v>
+        <v>-0.109667169645882</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.004661345649587433</v>
+        <v>-0.005478593058844313</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.04476046525607032</v>
+        <v>-0.06675071872589464</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01771368727174595</v>
+        <v>0.0197209478272581</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01927680252069966</v>
+        <v>0.01828710258636054</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.05643725727082639</v>
+        <v>-0.08286459774615575</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.04172579547952508</v>
+        <v>-0.05040739675310264</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01706097157601919</v>
+        <v>0.01864985137676655</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0006598787264897917</v>
+        <v>0.006867152886379686</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1021496959703735</v>
+        <v>-0.09206742764169834</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.05889282401301207</v>
+        <v>-0.05210395222110989</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003723452517240107</v>
+        <v>0.05608662768726733</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.01814850313311274</v>
+        <v>0.0172031392190454</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0133047864786855</v>
+        <v>0.02818127808720527</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.01114925022027864</v>
+        <v>0.0214791314896809</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07702739029971768</v>
+        <v>0.05929950995374642</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03905222093378447</v>
+        <v>-0.0293521286412921</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.04984761307527224</v>
+        <v>-0.02348276053823919</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02503263442651215</v>
+        <v>0.02235593954320466</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.01080437692566738</v>
+        <v>-0.0190724348429142</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.05766114010520675</v>
+        <v>0.003213128002482984</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.005363961126576615</v>
+        <v>-0.0009886948036743936</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0871870098944468</v>
+        <v>0.08568014013553121</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.04198627881125391</v>
+        <v>-0.05754606730910285</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.04939373120337847</v>
+        <v>-0.02169219716636224</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.07112625346677384</v>
+        <v>0.031427238807974</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.03210013620248606</v>
+        <v>-0.01126592095209387</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.06213678475858197</v>
+        <v>0.01427456914278958</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.00999740530708918</v>
+        <v>-0.07257974945751368</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.04529015461253896</v>
+        <v>-0.0225806262958686</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.005450715131451302</v>
+        <v>-0.07076350084088558</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.03337615600880419</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.01252691811916841</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-0.0182348649208518</v>
       </c>
     </row>
     <row r="6">
@@ -1060,109 +1111,118 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1016654006757328</v>
+        <v>-0.1522337324098139</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1013010524471818</v>
+        <v>-0.09216899693437838</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.07719900261560034</v>
+        <v>-0.1554273563116664</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.02138497572077136</v>
+        <v>-0.109667169645882</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006265959626036138</v>
+        <v>0.01818774247676858</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2110974475727928</v>
+        <v>0.2828518103383994</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08602929592439822</v>
+        <v>-0.1043403094654996</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008680532463259913</v>
+        <v>-0.02706407238541058</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4742540973323067</v>
+        <v>0.633057645407523</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009134573705968931</v>
+        <v>0.04103048335024859</v>
       </c>
       <c r="M6" t="n">
-        <v>0.055966296533904</v>
+        <v>0.01434956078455301</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2226139756940234</v>
+        <v>0.2912123824277488</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1614379252312627</v>
+        <v>0.1977402119217909</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03036652716998972</v>
+        <v>0.09838922699319871</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1397398261157245</v>
+        <v>-0.3697675490419548</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1641734183930627</v>
+        <v>-0.1216414746635736</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1280608014735666</v>
+        <v>-0.1547206862155288</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1452362989480442</v>
+        <v>-0.1462649603350751</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.09893236402913978</v>
+        <v>-0.2683107582597542</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.05360528622132413</v>
+        <v>-0.01131855634550556</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2124423092661068</v>
+        <v>0.2141704782200169</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1579768443375814</v>
+        <v>0.1848759945627597</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2280899352214439</v>
+        <v>-0.1258623163043516</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1998614483568096</v>
+        <v>0.145392861228714</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.3012246406019373</v>
+        <v>0.01422760400390717</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.3080016657530053</v>
+        <v>-0.1809573883615606</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.2921616562879174</v>
+        <v>0.2112915488638085</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.3117693805920781</v>
+        <v>-0.1138065280523517</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.09621421053783238</v>
+        <v>0.04720402906016524</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1295450368579415</v>
+        <v>-0.04881607246094686</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.06673435246593405</v>
+        <v>-0.03069322229785222</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.244097621237361</v>
+        <v>-0.05032961222202263</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.3035047410747507</v>
+        <v>-0.1247737087617955</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.06152860522623345</v>
+        <v>0.01205958210200804</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.2827652169448908</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.02016682154898497</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.1583703193751885</v>
       </c>
     </row>
     <row r="7">
@@ -1172,109 +1232,118 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02574630226727489</v>
+        <v>-0.01065204875704046</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04058985997493433</v>
+        <v>0.1094228685528726</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009684817758079741</v>
+        <v>-0.03905924321035227</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.004661345649587433</v>
+        <v>-0.005478593058844313</v>
       </c>
       <c r="F7" t="n">
-        <v>0.006265959626036138</v>
+        <v>0.01818774247676858</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01791721983222819</v>
+        <v>0.02390314597833009</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0005760911740386923</v>
+        <v>0.02385514403226549</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.01779562876097019</v>
+        <v>-0.02851277720833561</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0275707676617475</v>
+        <v>0.01868546599770588</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.01420497258610046</v>
+        <v>-0.0414820432459385</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03775005905459129</v>
+        <v>-0.01744125107691647</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.05408345233879781</v>
+        <v>-0.05181687209293051</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02091801172331921</v>
+        <v>0.01892977263368882</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0137791438845513</v>
+        <v>0.03916078392112351</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.003162467821440319</v>
+        <v>-0.008086536865547741</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001329609234586964</v>
+        <v>-0.05582909029710705</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0002475929963154271</v>
+        <v>-0.05263035294845073</v>
       </c>
       <c r="T7" t="n">
-        <v>0.004623666652578752</v>
+        <v>-0.02213916173445776</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.03626387495364816</v>
+        <v>-0.0697871401667018</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.00980179292356834</v>
+        <v>0.02995739212893643</v>
       </c>
       <c r="W7" t="n">
-        <v>0.005503510528680406</v>
+        <v>0.01198449508643029</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01102368919273702</v>
+        <v>0.007137939687145619</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.05245622255556565</v>
+        <v>-0.05771359079438979</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.08001989145022192</v>
+        <v>-0.03045141488433014</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02638181263462756</v>
+        <v>-0.02460342921646849</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0281731848079774</v>
+        <v>-0.05518059524224142</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.01009623528252274</v>
+        <v>-0.08412534403458609</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.04103918569833374</v>
+        <v>-0.05447715116824579</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.04089224928265665</v>
+        <v>-0.03293430484177805</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.01033842863916536</v>
+        <v>-0.01957614020841991</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.05347330683955737</v>
+        <v>0.01507679414233331</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.03443271890961972</v>
+        <v>0.06031564003378743</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.008852760021730821</v>
+        <v>0.0223708674891002</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.07088504286698941</v>
+        <v>-0.06386657037580507</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.02619125271594785</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.02474080071933559</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.04206301245545643</v>
       </c>
     </row>
     <row r="8">
@@ -1284,109 +1353,118 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01013092195425306</v>
+        <v>0.02051396006238272</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1603561052605443</v>
+        <v>-0.1437171873721365</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07996401141339073</v>
+        <v>-0.09596103220008803</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.04476046525607032</v>
+        <v>-0.06675071872589464</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2110974475727928</v>
+        <v>0.2828518103383994</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01791721983222819</v>
+        <v>0.02390314597833009</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03462568005995852</v>
+        <v>0.07307438879841391</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.137999689957623</v>
+        <v>-0.1614482294268307</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4416222317540513</v>
+        <v>0.43609110674716</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1322276959742836</v>
+        <v>0.1450776926744153</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1050301884714981</v>
+        <v>-0.0884771231235036</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1053107076247745</v>
+        <v>0.07150913600771092</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.004889398728257361</v>
+        <v>0.01839907261593746</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.06524488961513486</v>
+        <v>0.01196369489792203</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.5742955638271783</v>
+        <v>-0.3085856379458771</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6663930274886102</v>
+        <v>0.29784416485028</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5789409126444214</v>
+        <v>0.2242098501533842</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5312157232134495</v>
+        <v>0.1911599013687688</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2404950476242242</v>
+        <v>0.2286117397162896</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2532158750310592</v>
+        <v>-0.07562405126357916</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1460197264826224</v>
+        <v>0.1179367828642263</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2129347183727352</v>
+        <v>0.2205190754324522</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2204203907609088</v>
+        <v>0.2211258560479276</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.3230304391649978</v>
+        <v>0.1383157890585368</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.1539482271993118</v>
+        <v>0.1306519756686255</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.1744426017526866</v>
+        <v>-0.2635633413353763</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.1698657420838913</v>
+        <v>0.3331668676946908</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.1635122628502674</v>
+        <v>0.009893619104127692</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.1352473964583196</v>
+        <v>0.09542397470336453</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.05938081122792462</v>
+        <v>-0.06746940011580897</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.006992519228565358</v>
+        <v>-0.1134656158083502</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.1779021351923735</v>
+        <v>-0.0920811748756737</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.171579240095186</v>
+        <v>-0.151371221076173</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.002670004425014695</v>
+        <v>0.04254251508171864</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.09687834182330435</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.006979120211387076</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.04159135941381416</v>
       </c>
     </row>
     <row r="9">
@@ -1396,109 +1474,118 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1489856641114466</v>
+        <v>0.1153968777790513</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01443730561699839</v>
+        <v>0.01138921639626691</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03470199236178249</v>
+        <v>-0.0008797728635904786</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01771368727174595</v>
+        <v>0.0197209478272581</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.08602929592439822</v>
+        <v>-0.1043403094654996</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0005760911740386923</v>
+        <v>0.02385514403226549</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03462568005995852</v>
+        <v>0.07307438879841391</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.054185059459655</v>
+        <v>-0.07124919980288573</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.04722603789502604</v>
+        <v>-0.01848601861956352</v>
       </c>
       <c r="L9" t="n">
-        <v>0.343252946127318</v>
+        <v>0.3340768875482937</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.06436015559882728</v>
+        <v>-0.07568404987026707</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1317351639128746</v>
+        <v>-0.1457651641647855</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1834606806257971</v>
+        <v>-0.1480544566903156</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.01626058401280375</v>
+        <v>0.03904611743900277</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.08202863552703836</v>
+        <v>-0.03937386683080294</v>
       </c>
       <c r="R9" t="n">
-        <v>0.06507355933553312</v>
+        <v>0.0829750981768265</v>
       </c>
       <c r="S9" t="n">
-        <v>0.09647559905871173</v>
+        <v>0.08981647732583906</v>
       </c>
       <c r="T9" t="n">
-        <v>0.05922513155391588</v>
+        <v>0.07461173815021643</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1365158152370549</v>
+        <v>0.1153019899707529</v>
       </c>
       <c r="V9" t="n">
-        <v>0.07943568132982903</v>
+        <v>-0.1732314704133533</v>
       </c>
       <c r="W9" t="n">
-        <v>0.05535095747637164</v>
+        <v>0.02956832568694377</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1518407096596547</v>
+        <v>0.1335841781562723</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.007873183498178789</v>
+        <v>0.1817821800479984</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03342010195364839</v>
+        <v>0.08652543757085339</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.140308445486605</v>
+        <v>0.1019059998238823</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.1796673884050835</v>
+        <v>-0.1314685515638324</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1558087644780302</v>
+        <v>0.02474026830718588</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.1724854762320824</v>
+        <v>0.02842145461144661</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.004000294543563248</v>
+        <v>0.1078235817655234</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.1028037782517043</v>
+        <v>-0.001791826021911512</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.1795841859081218</v>
+        <v>0.01337733425229855</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.08977557601038909</v>
+        <v>0.02168904689640586</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.06563507729642998</v>
+        <v>-0.01383114541241584</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.01677648841606776</v>
+        <v>0.05768907558258705</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.05982935279927063</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.03231620516151021</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.01175153130266056</v>
       </c>
     </row>
     <row r="10">
@@ -1508,109 +1595,118 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0627958055361949</v>
+        <v>-0.03738738940810835</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1733897339763425</v>
+        <v>0.1900547927784644</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01540629572839074</v>
+        <v>0.01305887238962482</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01927680252069966</v>
+        <v>0.01828710258636054</v>
       </c>
       <c r="F10" t="n">
-        <v>0.008680532463259913</v>
+        <v>-0.02706407238541058</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.01779562876097019</v>
+        <v>-0.02851277720833561</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.137999689957623</v>
+        <v>-0.1614482294268307</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.054185059459655</v>
+        <v>-0.07124919980288573</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.04654488620961112</v>
+        <v>0.02704243181800291</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1111966936254202</v>
+        <v>-0.1105551499112351</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1530533354587578</v>
+        <v>0.1335594495273136</v>
       </c>
       <c r="N10" t="n">
-        <v>0.06835259653677986</v>
+        <v>0.06427598582047506</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.03880854800810137</v>
+        <v>-0.02143083334347548</v>
       </c>
       <c r="P10" t="n">
-        <v>0.03851610886802213</v>
+        <v>0.05056684726522011</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1924743125341012</v>
+        <v>0.113781346640297</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.1871744368418164</v>
+        <v>-0.05729247253711287</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1841323433969151</v>
+        <v>-0.05650398729342467</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1829995284739863</v>
+        <v>-0.07364922870788</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1062326084275996</v>
+        <v>-0.07401030496073775</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1025129571592352</v>
+        <v>-0.03957853342849704</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.01279140096466309</v>
+        <v>-0.02124038645504387</v>
       </c>
       <c r="X10" t="n">
-        <v>0.197831019581835</v>
+        <v>0.1565593496771505</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.07010983811721636</v>
+        <v>-0.08435869091922807</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.02459220813023598</v>
+        <v>0.05462426531798821</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.004525054835909886</v>
+        <v>0.05151304677661937</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.04416570152876086</v>
+        <v>0.04130394740536714</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.03511271244712053</v>
+        <v>0.02431206048679479</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.04168177187228451</v>
+        <v>-0.02371728529060209</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.003812638107488955</v>
+        <v>0.003073174055598994</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.005364312022743699</v>
+        <v>-0.009067123639468795</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.04064909220842924</v>
+        <v>0.004888161671559483</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.05619502825477496</v>
+        <v>-0.01629973017812746</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.04279130314014581</v>
+        <v>0.03605121999259477</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.1321834544132011</v>
+        <v>0.03985109801639726</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.05601339761222462</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-0.01838990425296168</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.04344884681400774</v>
       </c>
     </row>
     <row r="11">
@@ -1620,109 +1716,118 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1683119115507617</v>
+        <v>-0.1646061582476439</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1196645657147427</v>
+        <v>-0.09065413764237114</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1730986572829828</v>
+        <v>-0.1825901739185543</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.05643725727082639</v>
+        <v>-0.08286459774615575</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4742540973323067</v>
+        <v>0.633057645407523</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0275707676617475</v>
+        <v>0.01868546599770588</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4416222317540513</v>
+        <v>0.43609110674716</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.04722603789502604</v>
+        <v>-0.01848601861956352</v>
       </c>
       <c r="J11" t="n">
-        <v>0.04654488620961112</v>
+        <v>0.02704243181800291</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1280350950089796</v>
+        <v>0.1576589984556851</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.09846172974074315</v>
+        <v>-0.04775394829154713</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3382473475127504</v>
+        <v>0.2896267267755826</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1395107431029424</v>
+        <v>0.1392703500850958</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.0806716325938153</v>
+        <v>-0.005207950996764357</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.3056491326400738</v>
+        <v>-0.4592727459815287</v>
       </c>
       <c r="R11" t="n">
-        <v>0.403715187453972</v>
+        <v>-0.0342657706664489</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3133426819343157</v>
+        <v>-0.08794470942920307</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3044434453191762</v>
+        <v>-0.08843311826960809</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1019464469075897</v>
+        <v>-0.1941317933539919</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.00234363369148144</v>
+        <v>-0.0392265915321642</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2471192591792255</v>
+        <v>0.2256410048462239</v>
       </c>
       <c r="X11" t="n">
-        <v>0.5122646886640241</v>
+        <v>0.5125796464254878</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3304961486789772</v>
+        <v>0.007980803355422528</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.3196073152279826</v>
+        <v>0.1338783962646908</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.4311544443863852</v>
+        <v>0.130241444553234</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.4381340405735343</v>
+        <v>-0.3625922373381958</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.4411349374572784</v>
+        <v>0.3398216854212531</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.4447852847400761</v>
+        <v>-0.1244799637763281</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.1803899171442074</v>
+        <v>0.05967235476613516</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0269521602989089</v>
+        <v>-0.06106495705265275</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.06762470139972009</v>
+        <v>-0.03449219263370141</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.3954698263446486</v>
+        <v>-0.1042297422424207</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.345451911822736</v>
+        <v>-0.1850102522346893</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.1475951006458546</v>
+        <v>0.006107822316626218</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.2903547206013168</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.006348383044623658</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.1719640818434555</v>
       </c>
     </row>
     <row r="12">
@@ -1732,109 +1837,118 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03275858355284983</v>
+        <v>0.01620244947506944</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.02308323428795547</v>
+        <v>-0.02326956413808288</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001532307558284585</v>
+        <v>-0.01023648448285784</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.04172579547952508</v>
+        <v>-0.05040739675310264</v>
       </c>
       <c r="F12" t="n">
-        <v>0.009134573705968931</v>
+        <v>0.04103048335024859</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01420497258610046</v>
+        <v>-0.0414820432459385</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1322276959742836</v>
+        <v>0.1450776926744153</v>
       </c>
       <c r="I12" t="n">
-        <v>0.343252946127318</v>
+        <v>0.3340768875482937</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1111966936254202</v>
+        <v>-0.1105551499112351</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1280350950089796</v>
+        <v>0.1576589984556851</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1275006793785095</v>
+        <v>-0.1086641718114566</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.07134220073555923</v>
+        <v>-0.09086355414068409</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2043016948162212</v>
+        <v>-0.2129911236675714</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1334607323934216</v>
+        <v>-0.1193935685433825</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.207397460606204</v>
+        <v>-0.1849651103532243</v>
       </c>
       <c r="R12" t="n">
-        <v>0.211493391615752</v>
+        <v>0.09757091954247528</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2172767023895293</v>
+        <v>0.100240797581537</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1893121623072199</v>
+        <v>0.07930358555136487</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1579364687318887</v>
+        <v>0.08882355842397915</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1249790243025361</v>
+        <v>-0.1465269211300922</v>
       </c>
       <c r="W12" t="n">
-        <v>0.04916160627235229</v>
+        <v>0.02409834409745392</v>
       </c>
       <c r="X12" t="n">
-        <v>0.197891040237252</v>
+        <v>0.2586789267292378</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.01844525039267545</v>
+        <v>0.1872976754025887</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.1159837535736635</v>
+        <v>0.1100039671067572</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.07187930977569956</v>
+        <v>0.09732227491769339</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.07395297859550827</v>
+        <v>-0.2545166963230679</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.07001124739547351</v>
+        <v>0.1263317895101808</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.07084507356888595</v>
+        <v>0.02811412236988389</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.06412218321007188</v>
+        <v>0.08106677851385956</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.05253739951344989</v>
+        <v>0.08190963173462597</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.05649622455862165</v>
+        <v>-0.00415276692903936</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.01159614345278304</v>
+        <v>-0.009259211382527015</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.002847657719432306</v>
+        <v>-0.1126512039312719</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.008718836121823583</v>
+        <v>0.06715208209719251</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.02010448954239287</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-0.02358558055727042</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.04422131885005764</v>
       </c>
     </row>
     <row r="13">
@@ -1844,109 +1958,118 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.06255715580029865</v>
+        <v>-0.04606020581379727</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.04667640752380986</v>
+        <v>-0.01835967955208173</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.05590502523691093</v>
+        <v>-0.0705110790092968</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01706097157601919</v>
+        <v>0.01864985137676655</v>
       </c>
       <c r="F13" t="n">
-        <v>0.055966296533904</v>
+        <v>0.01434956078455301</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.03775005905459129</v>
+        <v>-0.01744125107691647</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1050301884714981</v>
+        <v>-0.0884771231235036</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.06436015559882728</v>
+        <v>-0.07568404987026707</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1530533354587578</v>
+        <v>0.1335594495273136</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.09846172974074315</v>
+        <v>-0.04775394829154713</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1275006793785095</v>
+        <v>-0.1086641718114566</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4570998042437544</v>
+        <v>0.4156388191998225</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1217686937956478</v>
+        <v>0.1229403224515356</v>
       </c>
       <c r="P13" t="n">
-        <v>0.009959770695479712</v>
+        <v>0.04242800792153292</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1631868960944052</v>
+        <v>0.09167053116210271</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.1876149850543676</v>
+        <v>-0.1558552651534492</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1668887680631569</v>
+        <v>-0.1024413431323417</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1299020859833803</v>
+        <v>-0.06339282214547495</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1328868491851822</v>
+        <v>-0.1176529602519697</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1197055387623344</v>
+        <v>0.05427806986755476</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1005268172715409</v>
+        <v>0.1199230980476398</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.05819489636754475</v>
+        <v>-0.05431005658088087</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.04200872745327577</v>
+        <v>-0.09869731977897006</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.1313298221469905</v>
+        <v>0.004476247724968099</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.0533676567742</v>
+        <v>-0.04094374786868287</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.05252320352070759</v>
+        <v>0.1134852568977098</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.05518846714548916</v>
+        <v>-0.1273668191697876</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.06926612303768563</v>
+        <v>-0.001922529043938902</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.1076892569265196</v>
+        <v>0.01701822399793934</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.03760624173341789</v>
+        <v>-0.04693125196985402</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.01980488780437314</v>
+        <v>-0.02905902954884057</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.02757190463334472</v>
+        <v>0.0884110245886497</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.03026180988271241</v>
+        <v>0.07187267454303473</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.009394824856111277</v>
+        <v>0.04816148064538751</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0.1000141145102716</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.03938177142189196</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-0.004442661562165791</v>
       </c>
     </row>
     <row r="14">
@@ -1956,109 +2079,118 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.1539522245029346</v>
+        <v>-0.1435335702701097</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1519083646892877</v>
+        <v>-0.1316613877317259</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1096959754194636</v>
+        <v>-0.09839321867787555</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0006598787264897917</v>
+        <v>0.006867152886379686</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2226139756940234</v>
+        <v>0.2912123824277488</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.05408345233879781</v>
+        <v>-0.05181687209293051</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1053107076247745</v>
+        <v>0.07150913600771092</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1317351639128746</v>
+        <v>-0.1457651641647855</v>
       </c>
       <c r="J14" t="n">
-        <v>0.06835259653677986</v>
+        <v>0.06427598582047506</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3382473475127504</v>
+        <v>0.2896267267755826</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.07134220073555923</v>
+        <v>-0.09086355414068409</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4570998042437544</v>
+        <v>0.4156388191998225</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2314285107652671</v>
+        <v>0.177354939390939</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.03096582435432733</v>
+        <v>-0.05621013966283236</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.01016776784791228</v>
+        <v>-0.1228720013589826</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0532228879307122</v>
+        <v>-0.1134978182015774</v>
       </c>
       <c r="S14" t="n">
-        <v>0.006173247775418608</v>
+        <v>-0.129424393090303</v>
       </c>
       <c r="T14" t="n">
-        <v>0.02414214034241087</v>
+        <v>-0.09534171162795711</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2188186026337145</v>
+        <v>-0.1961509848795527</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1340791557362679</v>
+        <v>0.1053424912644674</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1837058693226754</v>
+        <v>0.1948520292257991</v>
       </c>
       <c r="X14" t="n">
-        <v>0.08540294268445346</v>
+        <v>0.06764489181216547</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0973615238078897</v>
+        <v>-0.1430907389358226</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.0001559469837671873</v>
+        <v>0.04889514688311423</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.3190751313085755</v>
+        <v>-0.002966127450942359</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.3126388605034885</v>
+        <v>0.06342396042209118</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.2984582122609136</v>
+        <v>-0.001787650657604119</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.3039465828354694</v>
+        <v>-0.084284410425547</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.0999379211666294</v>
+        <v>0.01656602158293573</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.02295599967588079</v>
+        <v>-0.1292330632252945</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.03760206189801404</v>
+        <v>-0.1413850866361684</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.1873775481953699</v>
+        <v>-0.1505605063409815</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.2373446800744995</v>
+        <v>-0.07676990751327779</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.08998811104534733</v>
+        <v>-0.00910270088149266</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.1687884836597827</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-0.000682756027358706</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.06043314061843652</v>
       </c>
     </row>
     <row r="15">
@@ -2068,109 +2200,118 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1514167333014552</v>
+        <v>-0.1184327178731212</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.001611812638787804</v>
+        <v>0.01352938446577086</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.02372886259075345</v>
+        <v>-0.02713256739816396</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1021496959703735</v>
+        <v>-0.09206742764169834</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1614379252312627</v>
+        <v>0.1977402119217909</v>
       </c>
       <c r="G15" t="n">
-        <v>0.02091801172331921</v>
+        <v>0.01892977263368882</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.004889398728257361</v>
+        <v>0.01839907261593746</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1834606806257971</v>
+        <v>-0.1480544566903156</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.03880854800810137</v>
+        <v>-0.02143083334347548</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1395107431029424</v>
+        <v>0.1392703500850958</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2043016948162212</v>
+        <v>-0.2129911236675714</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1217686937956478</v>
+        <v>0.1229403224515356</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2314285107652671</v>
+        <v>0.177354939390939</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3238843752395155</v>
+        <v>0.4367175439856157</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1400232313854412</v>
+        <v>0.03319611958242574</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.08882804337283712</v>
+        <v>-0.1766040614371755</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1526944220530529</v>
+        <v>-0.2214678411983576</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1326970052198685</v>
+        <v>-0.2181229464451943</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2416907080125407</v>
+        <v>-0.2627367986766575</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1567613452889612</v>
+        <v>0.2389615627654906</v>
       </c>
       <c r="W15" t="n">
-        <v>0.05067764954754139</v>
+        <v>0.05543274574799884</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.05801403642200456</v>
+        <v>-0.08226397361485951</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.004752974648442583</v>
+        <v>-0.1473555707181819</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.02899591842707675</v>
+        <v>-0.02914951831289996</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.2987308103222592</v>
+        <v>-0.08759634147277566</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.2920770943780602</v>
+        <v>0.1347339858367184</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.2639498813021089</v>
+        <v>-0.008003149378581148</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.259446576416083</v>
+        <v>-0.06962114321668407</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.100832166043131</v>
+        <v>-0.04512362270059302</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1171781380455823</v>
+        <v>-0.0929930944937133</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.04879460836840006</v>
+        <v>0.01302939189057944</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.09264219825939357</v>
+        <v>0.09117623973506245</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.1701070033332328</v>
+        <v>0.06735060286635219</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0.005566760996333206</v>
+        <v>-0.09082482076844595</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.03630756175922136</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.1328570560334042</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.0364422421236778</v>
       </c>
     </row>
     <row r="16">
@@ -2180,109 +2321,118 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.005452022852055137</v>
+        <v>0.02781912045315838</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01647173080772497</v>
+        <v>0.002698547294766297</v>
       </c>
       <c r="D16" t="n">
-        <v>0.06710865131166459</v>
+        <v>0.02352945977916111</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.05889282401301207</v>
+        <v>-0.05210395222110989</v>
       </c>
       <c r="F16" t="n">
-        <v>0.03036652716998972</v>
+        <v>0.09838922699319871</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0137791438845513</v>
+        <v>0.03916078392112351</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.06524488961513486</v>
+        <v>0.01196369489792203</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.01626058401280375</v>
+        <v>0.03904611743900277</v>
       </c>
       <c r="J16" t="n">
-        <v>0.03851610886802213</v>
+        <v>0.05056684726522011</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0806716325938153</v>
+        <v>-0.005207950996764357</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1334607323934216</v>
+        <v>-0.1193935685433825</v>
       </c>
       <c r="M16" t="n">
-        <v>0.009959770695479712</v>
+        <v>0.04242800792153292</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.03096582435432733</v>
+        <v>-0.05621013966283236</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3238843752395155</v>
+        <v>0.4367175439856157</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.07550956723227559</v>
+        <v>0.1031196932621134</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.07194870558440178</v>
+        <v>-0.0909430531783029</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.07407241357632445</v>
+        <v>-0.1080342902709622</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.07248209712577737</v>
+        <v>-0.08313639898439228</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.07511330458722576</v>
+        <v>-0.1402418085586185</v>
       </c>
       <c r="V16" t="n">
-        <v>0.00687642533234716</v>
+        <v>0.04921307264606269</v>
       </c>
       <c r="W16" t="n">
-        <v>0.04912145086136595</v>
+        <v>0.03829571541010627</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.001931425246920735</v>
+        <v>-0.04478243784183392</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.01718010725904659</v>
+        <v>-0.03035908832045084</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.1019054807138714</v>
+        <v>0.02247587791469958</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.004539827563902506</v>
+        <v>-0.02418898547761623</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0317429060302322</v>
+        <v>0.07681277742792297</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.04213965949196768</v>
+        <v>-0.06321465092938036</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.03807416099886983</v>
+        <v>0.02309346244203659</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.08569882407068527</v>
+        <v>0.02598746296277693</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.04773737766323616</v>
+        <v>-0.1117745860821232</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.01574532571655931</v>
+        <v>0.02057670768560088</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0.1279131873860186</v>
+        <v>0.1311760302983295</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0.03993275905876646</v>
+        <v>0.08954226173832408</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.004368914491667843</v>
+        <v>-0.01653791108975803</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-0.1729123751795936</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.08984920435561854</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.06560257166452294</v>
       </c>
     </row>
     <row r="17">
@@ -2292,109 +2442,118 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.06989524594587206</v>
+        <v>0.02283502544625617</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2893062550025601</v>
+        <v>0.143028057646777</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1220688091163222</v>
+        <v>0.1772591976667311</v>
       </c>
       <c r="E17" t="n">
-        <v>0.003723452517240107</v>
+        <v>0.05608662768726733</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1397398261157245</v>
+        <v>-0.3697675490419548</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.003162467821440319</v>
+        <v>-0.008086536865547741</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5742955638271783</v>
+        <v>-0.3085856379458771</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.08202863552703836</v>
+        <v>-0.03937386683080294</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1924743125341012</v>
+        <v>0.113781346640297</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3056491326400738</v>
+        <v>-0.4592727459815287</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.207397460606204</v>
+        <v>-0.1849651103532243</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1631868960944052</v>
+        <v>0.09167053116210271</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.01016776784791228</v>
+        <v>-0.1228720013589826</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1400232313854412</v>
+        <v>0.03319611958242574</v>
       </c>
       <c r="P17" t="n">
-        <v>0.07550956723227559</v>
+        <v>0.1031196932621134</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.8426369201865589</v>
+        <v>0.09724539673664948</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9566593119499615</v>
+        <v>0.003292363673661721</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9507737737292284</v>
+        <v>-0.04942778977759361</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4185514591175991</v>
+        <v>0.2704678156406798</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3749672056234148</v>
+        <v>0.1210352927727268</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.08107499998221722</v>
+        <v>-0.124071186217563</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.242713503420945</v>
+        <v>-0.1902589323580027</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.0756573657208989</v>
+        <v>-0.155352013949859</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.437170399923564</v>
+        <v>-0.04234622928629908</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.009387074393393133</v>
+        <v>-0.07814751335056276</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.02155019065377578</v>
+        <v>0.2657731674957998</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.00676561560830219</v>
+        <v>-0.287529181077385</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.02275367928315951</v>
+        <v>0.07271846158760008</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.1085979635647896</v>
+        <v>-0.1181139162182397</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.07509335384667835</v>
+        <v>0.01153021269081836</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.06152671370845591</v>
+        <v>0.08503031722204345</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.1399442703041758</v>
+        <v>0.0731007475613598</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0.06766339031483004</v>
+        <v>0.1723337734295052</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.04332393127940078</v>
+        <v>-0.07149311666886458</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-0.2737198565370546</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.04801467153188296</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-0.05921562488546625</v>
       </c>
     </row>
     <row r="18">
@@ -2404,109 +2563,118 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.05265807539078503</v>
+        <v>0.09373332085645929</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.256243815979217</v>
+        <v>-0.142537494472403</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1106061587271768</v>
+        <v>0.00386801670923928</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.01814850313311274</v>
+        <v>0.0172031392190454</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1641734183930627</v>
+        <v>-0.1216414746635736</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001329609234586964</v>
+        <v>-0.05582909029710705</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6663930274886102</v>
+        <v>0.29784416485028</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06507355933553312</v>
+        <v>0.0829750981768265</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1871744368418164</v>
+        <v>-0.05729247253711287</v>
       </c>
       <c r="K18" t="n">
-        <v>0.403715187453972</v>
+        <v>-0.0342657706664489</v>
       </c>
       <c r="L18" t="n">
-        <v>0.211493391615752</v>
+        <v>0.09757091954247528</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1876149850543676</v>
+        <v>-0.1558552651534492</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0532228879307122</v>
+        <v>-0.1134978182015774</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.08882804337283712</v>
+        <v>-0.1766040614371755</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.07194870558440178</v>
+        <v>-0.0909430531783029</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.8426369201865589</v>
+        <v>0.09724539673664948</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8800011559807913</v>
+        <v>0.8171310289579209</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7591915467652202</v>
+        <v>0.3981581527183871</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3815773758358645</v>
+        <v>0.6022936059421328</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3382099387377427</v>
+        <v>-0.137272525903153</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1194468678036805</v>
+        <v>-0.01357803827106311</v>
       </c>
       <c r="X18" t="n">
-        <v>0.242424864157835</v>
+        <v>0.2181352458137828</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1755085645692944</v>
+        <v>0.4560184558591066</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.4097766781606328</v>
+        <v>0.1808810703082079</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.07932871831423659</v>
+        <v>0.1576990375755911</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.08835197658830025</v>
+        <v>-0.0889701787765452</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.07064221585310096</v>
+        <v>0.2497508487635679</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.08335566223102338</v>
+        <v>0.08467550162215345</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.1536721186808014</v>
+        <v>0.1226495792497489</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.1135928652838122</v>
+        <v>0.08341003307023297</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.0728135596385853</v>
+        <v>0.01639237632889547</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.1394717857155122</v>
+        <v>0.001877224387934411</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.1217951212365447</v>
+        <v>-0.0937725174513806</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.01192714564423721</v>
+        <v>0.1560918975586815</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-0.07712409568247811</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-0.01482333250957654</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-0.09227270806344895</v>
       </c>
     </row>
     <row r="19">
@@ -2516,109 +2684,118 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08917582125511839</v>
+        <v>0.1115595621038911</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.317341753869948</v>
+        <v>-0.2007287471480622</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1082774879038943</v>
+        <v>0.01537649932899007</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0133047864786855</v>
+        <v>0.02818127808720527</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1280608014735666</v>
+        <v>-0.1547206862155288</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0002475929963154271</v>
+        <v>-0.05263035294845073</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5789409126444214</v>
+        <v>0.2242098501533842</v>
       </c>
       <c r="I19" t="n">
-        <v>0.09647559905871173</v>
+        <v>0.08981647732583906</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1841323433969151</v>
+        <v>-0.05650398729342467</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3133426819343157</v>
+        <v>-0.08794470942920307</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2172767023895293</v>
+        <v>0.100240797581537</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1668887680631569</v>
+        <v>-0.1024413431323417</v>
       </c>
       <c r="N19" t="n">
-        <v>0.006173247775418608</v>
+        <v>-0.129424393090303</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1526944220530529</v>
+        <v>-0.2214678411983576</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.07407241357632445</v>
+        <v>-0.1080342902709622</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9566593119499615</v>
+        <v>0.003292363673661721</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8800011559807913</v>
+        <v>0.8171310289579209</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9220224356756516</v>
+        <v>0.7018407952774988</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4063835861900543</v>
+        <v>0.5441526245972113</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3664394973587542</v>
+        <v>-0.1518666220782244</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1004196237936461</v>
+        <v>0.01242158903058095</v>
       </c>
       <c r="X19" t="n">
-        <v>0.2659784755157905</v>
+        <v>0.1836519705986888</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.08833615649112943</v>
+        <v>0.4992524952542949</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.4439094322931348</v>
+        <v>0.1621175235365684</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.001572357238546515</v>
+        <v>0.1228054286335495</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.005960318968613554</v>
+        <v>-0.1032140247012125</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.001012266449867295</v>
+        <v>0.2669872390626319</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.01386483719270653</v>
+        <v>0.1103506734093615</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.1030493208226727</v>
+        <v>0.2099900045568824</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.1078376646168328</v>
+        <v>0.06899658630311134</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.0926838014127799</v>
+        <v>-0.002067146615908513</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.1300936643176341</v>
+        <v>0.008925888860914893</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.07135242230361445</v>
+        <v>-0.0716573430255163</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0.04474307914758275</v>
+        <v>0.2079140640981204</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-0.07030634670141503</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-0.00430818422993476</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-0.1201712782548971</v>
       </c>
     </row>
     <row r="20">
@@ -2628,109 +2805,118 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.05091042687031718</v>
+        <v>0.1088865201705398</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.2966908451547349</v>
+        <v>-0.2053999318983533</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1044836177880937</v>
+        <v>0.01467616265921041</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.01114925022027864</v>
+        <v>0.0214791314896809</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1452362989480442</v>
+        <v>-0.1462649603350751</v>
       </c>
       <c r="G20" t="n">
-        <v>0.004623666652578752</v>
+        <v>-0.02213916173445776</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5312157232134495</v>
+        <v>0.1911599013687688</v>
       </c>
       <c r="I20" t="n">
-        <v>0.05922513155391588</v>
+        <v>0.07461173815021643</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1829995284739863</v>
+        <v>-0.07364922870788</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3044434453191762</v>
+        <v>-0.08843311826960809</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1893121623072199</v>
+        <v>0.07930358555136487</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1299020859833803</v>
+        <v>-0.06339282214547495</v>
       </c>
       <c r="N20" t="n">
-        <v>0.02414214034241087</v>
+        <v>-0.09534171162795711</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1326970052198685</v>
+        <v>-0.2181229464451943</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.07248209712577737</v>
+        <v>-0.08313639898439228</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9507737737292284</v>
+        <v>-0.04942778977759361</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7591915467652202</v>
+        <v>0.3981581527183871</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9220224356756516</v>
+        <v>0.7018407952774988</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3861824024048395</v>
+        <v>0.4681149572683444</v>
       </c>
       <c r="V20" t="n">
-        <v>0.36576727376662</v>
+        <v>-0.1027832153627894</v>
       </c>
       <c r="W20" t="n">
-        <v>0.09262555808784494</v>
+        <v>-0.03238547824092906</v>
       </c>
       <c r="X20" t="n">
-        <v>0.2184610364500127</v>
+        <v>0.1161125046832458</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.08214857215275789</v>
+        <v>0.4398256103095795</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.4245240921629139</v>
+        <v>0.1013364382837299</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.001348063959217262</v>
+        <v>0.08365000727700264</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.005953819157798404</v>
+        <v>-0.1194725852824816</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.0131030095141908</v>
+        <v>0.2360265774148869</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.0251352535911499</v>
+        <v>0.1130688738372151</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.09485462946659495</v>
+        <v>0.2052577627988174</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.05532171647768557</v>
+        <v>0.05955838532521428</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.06784733602725289</v>
+        <v>-0.009488071578062664</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.1501535549287084</v>
+        <v>-0.004643772790877314</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.05947993959518601</v>
+        <v>0.01546335272816284</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0.02910008661214432</v>
+        <v>0.1707350879842381</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>-0.05790497859738603</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>-0.0336176380878981</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>-0.0944442778409173</v>
       </c>
     </row>
     <row r="21">
@@ -2740,109 +2926,118 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.18095694988456</v>
+        <v>0.1327240389581617</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.03824453429304032</v>
+        <v>-0.07482035525590021</v>
       </c>
       <c r="D21" t="n">
-        <v>0.08178134419514629</v>
+        <v>0.08818496857142781</v>
       </c>
       <c r="E21" t="n">
-        <v>0.07702739029971768</v>
+        <v>0.05929950995374642</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.09893236402913978</v>
+        <v>-0.2683107582597542</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.03626387495364816</v>
+        <v>-0.0697871401667018</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2404950476242242</v>
+        <v>0.2286117397162896</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1365158152370549</v>
+        <v>0.1153019899707529</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1062326084275996</v>
+        <v>-0.07401030496073775</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1019464469075897</v>
+        <v>-0.1941317933539919</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1579364687318887</v>
+        <v>0.08882355842397915</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1328868491851822</v>
+        <v>-0.1176529602519697</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2188186026337145</v>
+        <v>-0.1961509848795527</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2416907080125407</v>
+        <v>-0.2627367986766575</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.07511330458722576</v>
+        <v>-0.1402418085586185</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.4185514591175991</v>
+        <v>0.2704678156406798</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3815773758358645</v>
+        <v>0.6022936059421328</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4063835861900543</v>
+        <v>0.5441526245972113</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3861824024048395</v>
+        <v>0.4681149572683444</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6951148971974302</v>
+        <v>-0.1550705431084468</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.05960079226693586</v>
+        <v>-0.1072016358477312</v>
       </c>
       <c r="X21" t="n">
-        <v>0.07391988071554255</v>
+        <v>0.08680603750002784</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.00139939888686017</v>
+        <v>0.3570625110593781</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.09454951419700701</v>
+        <v>0.02788149920988271</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.2470672634540378</v>
+        <v>0.09186406302566945</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.2399848757423723</v>
+        <v>-0.1032311028845723</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.2870911097511041</v>
+        <v>0.1565989485702848</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.2790836140038915</v>
+        <v>0.1478330263804629</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0.08185125147472462</v>
+        <v>0.07764300526176507</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.1447529631147572</v>
+        <v>0.1384638544652446</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.09933617528558722</v>
+        <v>0.006170876950018297</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.006235424833343505</v>
+        <v>-0.004782916242430454</v>
       </c>
       <c r="AI21" t="n">
-        <v>-0.1376032628045009</v>
+        <v>-0.03239079750678218</v>
       </c>
       <c r="AJ21" t="n">
-        <v>-0.09587009345138629</v>
+        <v>0.09338800585643421</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>-0.1117575912029964</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>-0.03688661356033774</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>-0.1207906220624961</v>
       </c>
     </row>
     <row r="22">
@@ -2852,109 +3047,118 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1024243210168888</v>
+        <v>-0.1166667338227477</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.03809087403201362</v>
+        <v>-0.02168714376365774</v>
       </c>
       <c r="D22" t="n">
-        <v>0.006264882135330589</v>
+        <v>0.02386939372158895</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03905222093378447</v>
+        <v>-0.0293521286412921</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.05360528622132413</v>
+        <v>-0.01131855634550556</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.00980179292356834</v>
+        <v>0.02995739212893643</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2532158750310592</v>
+        <v>-0.07562405126357916</v>
       </c>
       <c r="I22" t="n">
-        <v>0.07943568132982903</v>
+        <v>-0.1732314704133533</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1025129571592352</v>
+        <v>-0.03957853342849704</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.00234363369148144</v>
+        <v>-0.0392265915321642</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1249790243025361</v>
+        <v>-0.1465269211300922</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1197055387623344</v>
+        <v>0.05427806986755476</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1340791557362679</v>
+        <v>0.1053424912644674</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1567613452889612</v>
+        <v>0.2389615627654906</v>
       </c>
       <c r="P22" t="n">
-        <v>0.00687642533234716</v>
+        <v>0.04921307264606269</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.3749672056234148</v>
+        <v>0.1210352927727268</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3382099387377427</v>
+        <v>-0.137272525903153</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3664394973587542</v>
+        <v>-0.1518666220782244</v>
       </c>
       <c r="T22" t="n">
-        <v>0.36576727376662</v>
+        <v>-0.1027832153627894</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6951148971974302</v>
+        <v>-0.1550705431084468</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>0.008359868091825783</v>
+        <v>0.009331755783753979</v>
       </c>
       <c r="X22" t="n">
-        <v>0.08579347892602188</v>
+        <v>-0.1202135231138383</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.03988643692067073</v>
+        <v>-0.1016683851066388</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.09403078169205738</v>
+        <v>-0.112430145618894</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.1370395807868141</v>
+        <v>-0.1032404540521789</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.1535321190501708</v>
+        <v>0.06450288380053396</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.161377231527071</v>
+        <v>-0.1420913441373082</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.1674725408086119</v>
+        <v>0.01148419219441201</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.09437219101973364</v>
+        <v>-0.08856486263781818</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0.1132162568335883</v>
+        <v>0.03175361198294637</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.07949591590606644</v>
+        <v>0.01548383963097367</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.04153691902271812</v>
+        <v>0.06406564211229447</v>
       </c>
       <c r="AI22" t="n">
-        <v>-0.0571571850568778</v>
+        <v>0.0584740130158167</v>
       </c>
       <c r="AJ22" t="n">
-        <v>-0.04634614455280773</v>
+        <v>-0.1381227751095845</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>-0.03140179993924808</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0.008589749695373374</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>-0.03466037578468611</v>
       </c>
     </row>
     <row r="23">
@@ -2964,109 +3168,118 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.02204201266678182</v>
+        <v>0.007133991226581892</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.09987029793234278</v>
+        <v>-0.1018875163575239</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.08056315719215404</v>
+        <v>-0.07343917412845845</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.04984761307527224</v>
+        <v>-0.02348276053823919</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2124423092661068</v>
+        <v>0.2141704782200169</v>
       </c>
       <c r="G23" t="n">
-        <v>0.005503510528680406</v>
+        <v>0.01198449508643029</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1460197264826224</v>
+        <v>0.1179367828642263</v>
       </c>
       <c r="I23" t="n">
-        <v>0.05535095747637164</v>
+        <v>0.02956832568694377</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.01279140096466309</v>
+        <v>-0.02124038645504387</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2471192591792255</v>
+        <v>0.2256410048462239</v>
       </c>
       <c r="L23" t="n">
-        <v>0.04916160627235229</v>
+        <v>0.02409834409745392</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1005268172715409</v>
+        <v>0.1199230980476398</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1837058693226754</v>
+        <v>0.1948520292257991</v>
       </c>
       <c r="O23" t="n">
-        <v>0.05067764954754139</v>
+        <v>0.05543274574799884</v>
       </c>
       <c r="P23" t="n">
-        <v>0.04912145086136595</v>
+        <v>0.03829571541010627</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.08107499998221722</v>
+        <v>-0.124071186217563</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1194468678036805</v>
+        <v>-0.01357803827106311</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1004196237936461</v>
+        <v>0.01242158903058095</v>
       </c>
       <c r="T23" t="n">
-        <v>0.09262555808784494</v>
+        <v>-0.03238547824092906</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.05960079226693586</v>
+        <v>-0.1072016358477312</v>
       </c>
       <c r="V23" t="n">
-        <v>0.008359868091825783</v>
+        <v>0.009331755783753979</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>0.07045190331338337</v>
+        <v>0.04733102312672825</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.1278211830543892</v>
+        <v>-0.01570847387257455</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.08294656709663006</v>
+        <v>0.1017156805431056</v>
       </c>
       <c r="AA23" t="n">
-        <v>-0.1690331910194983</v>
+        <v>0.01091722212456692</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.0896998053830976</v>
+        <v>-0.01476055156627263</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.1729588821479186</v>
+        <v>0.08048739773288299</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.2067584718147851</v>
+        <v>-0.08128279859522436</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.06131315629540669</v>
+        <v>0.1326535509009975</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0.00474498157371526</v>
+        <v>-0.1505331416096787</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.08034345549229417</v>
+        <v>-0.1763849275930112</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.06514707646774137</v>
+        <v>-0.08799495546515586</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.07044208642859143</v>
+        <v>-0.05494634526497122</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.03306160750335749</v>
+        <v>0.09745564086479368</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0.05160164261045685</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>-0.03945118395865131</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.05743700788546895</v>
       </c>
     </row>
     <row r="24">
@@ -3076,1452 +3289,1932 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.04464680490417582</v>
+        <v>0.01159709222273092</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.08111176013501493</v>
+        <v>-0.07258700476579903</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.006693063143880768</v>
+        <v>-0.0317414117742708</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02503263442651215</v>
+        <v>0.02235593954320466</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1579768443375814</v>
+        <v>0.1848759945627597</v>
       </c>
       <c r="G24" t="n">
-        <v>0.01102368919273702</v>
+        <v>0.007137939687145619</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2129347183727352</v>
+        <v>0.2205190754324522</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1518407096596547</v>
+        <v>0.1335841781562723</v>
       </c>
       <c r="J24" t="n">
-        <v>0.197831019581835</v>
+        <v>0.1565593496771505</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5122646886640241</v>
+        <v>0.5125796464254878</v>
       </c>
       <c r="L24" t="n">
-        <v>0.197891040237252</v>
+        <v>0.2586789267292378</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.05819489636754475</v>
+        <v>-0.05431005658088087</v>
       </c>
       <c r="N24" t="n">
-        <v>0.08540294268445346</v>
+        <v>0.06764489181216547</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.05801403642200456</v>
+        <v>-0.08226397361485951</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.001931425246920735</v>
+        <v>-0.04478243784183392</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.242713503420945</v>
+        <v>-0.1902589323580027</v>
       </c>
       <c r="R24" t="n">
-        <v>0.242424864157835</v>
+        <v>0.2181352458137828</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2659784755157905</v>
+        <v>0.1836519705986888</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2184610364500127</v>
+        <v>0.1161125046832458</v>
       </c>
       <c r="U24" t="n">
-        <v>0.07391988071554255</v>
+        <v>0.08680603750002784</v>
       </c>
       <c r="V24" t="n">
-        <v>0.08579347892602188</v>
+        <v>-0.1202135231138383</v>
       </c>
       <c r="W24" t="n">
-        <v>0.07045190331338337</v>
+        <v>0.04733102312672825</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.08842008426665422</v>
+        <v>0.1776945823353726</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.241172919695705</v>
+        <v>0.1718904587610018</v>
       </c>
       <c r="AA24" t="n">
-        <v>-0.04755224972126298</v>
+        <v>0.2111409655558725</v>
       </c>
       <c r="AB24" t="n">
-        <v>-0.03043371366087548</v>
+        <v>-0.3065782778365298</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.05864863097755116</v>
+        <v>0.2586273185834694</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.06172838281011876</v>
+        <v>-0.009275368718551235</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.02116859472771644</v>
+        <v>0.1411850416595193</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0.009443956029929503</v>
+        <v>0.05082267014197236</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.02999956661144323</v>
+        <v>0.07193055171318515</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.08375799466189925</v>
+        <v>0.0202400452520998</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.06443610894974088</v>
+        <v>-0.1257158992499894</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.0727299339375302</v>
+        <v>0.1311917885649831</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0.06023483047205125</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>-0.0154444413432885</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0.04288568974563574</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>RAI</t>
+          <t>TNMN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.09426868850895498</v>
+        <v>0.05547784873328553</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.07920133541101212</v>
+        <v>-0.1789914924324122</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1191207018988408</v>
+        <v>-0.02914510365667243</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.01080437692566738</v>
+        <v>-0.0190724348429142</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2280899352214439</v>
+        <v>-0.1258623163043516</v>
       </c>
       <c r="G25" t="n">
-        <v>0.05245622255556565</v>
+        <v>-0.05771359079438979</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2204203907609088</v>
+        <v>0.2211258560479276</v>
       </c>
       <c r="I25" t="n">
-        <v>0.007873183498178789</v>
+        <v>0.1817821800479984</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.07010983811721636</v>
+        <v>-0.08435869091922807</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3304961486789772</v>
+        <v>0.007980803355422528</v>
       </c>
       <c r="L25" t="n">
-        <v>0.01844525039267545</v>
+        <v>0.1872976754025887</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.04200872745327577</v>
+        <v>-0.09869731977897006</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0973615238078897</v>
+        <v>-0.1430907389358226</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.004752974648442583</v>
+        <v>-0.1473555707181819</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.01718010725904659</v>
+        <v>-0.03035908832045084</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.0756573657208989</v>
+        <v>-0.155352013949859</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1755085645692944</v>
+        <v>0.4560184558591066</v>
       </c>
       <c r="S25" t="n">
-        <v>0.08833615649112943</v>
+        <v>0.4992524952542949</v>
       </c>
       <c r="T25" t="n">
-        <v>0.08214857215275789</v>
+        <v>0.4398256103095795</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.00139939888686017</v>
+        <v>0.3570625110593781</v>
       </c>
       <c r="V25" t="n">
-        <v>0.03988643692067073</v>
+        <v>-0.1016683851066388</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1278211830543892</v>
+        <v>-0.01570847387257455</v>
       </c>
       <c r="X25" t="n">
-        <v>0.08842008426665422</v>
+        <v>0.1776945823353726</v>
       </c>
       <c r="Y25" t="n">
         <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.04348797769404898</v>
+        <v>0.1232260080208425</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.06386683563758457</v>
+        <v>0.1718979810323338</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.05582394387532855</v>
+        <v>-0.2722855017777395</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.05142152221293294</v>
+        <v>0.2203383839600365</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.04673275812930502</v>
+        <v>0.06768603331783173</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.04301434682497986</v>
+        <v>0.1609059724238873</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.05731233613054878</v>
+        <v>0.08551985450341877</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.05090693309999909</v>
+        <v>0.01472743076138192</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.1898106507091225</v>
+        <v>0.1489531295353475</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.1845803460044396</v>
+        <v>-0.02559729979924891</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.1339619390590361</v>
+        <v>0.1077660316141049</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>-0.07050299248843558</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0.008367212640206316</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>-0.1110169822412851</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>RAIDOSE</t>
+          <t>TNMM</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.00802307081099014</v>
+        <v>-0.04198304653301659</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.05505549379496147</v>
+        <v>0.0003435624366104266</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.04892190223316589</v>
+        <v>-0.03212022651322469</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.05766114010520675</v>
+        <v>0.003213128002482984</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1998614483568096</v>
+        <v>0.145392861228714</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.08001989145022192</v>
+        <v>-0.03045141488433014</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3230304391649978</v>
+        <v>0.1383157890585368</v>
       </c>
       <c r="I26" t="n">
-        <v>0.03342010195364839</v>
+        <v>0.08652543757085339</v>
       </c>
       <c r="J26" t="n">
-        <v>0.02459220813023598</v>
+        <v>0.05462426531798821</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3196073152279826</v>
+        <v>0.1338783962646908</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1159837535736635</v>
+        <v>0.1100039671067572</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1313298221469905</v>
+        <v>0.004476247724968099</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.0001559469837671873</v>
+        <v>0.04889514688311423</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.02899591842707675</v>
+        <v>-0.02914951831289996</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.1019054807138714</v>
+        <v>0.02247587791469958</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.437170399923564</v>
+        <v>-0.04234622928629908</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4097766781606328</v>
+        <v>0.1808810703082079</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4439094322931348</v>
+        <v>0.1621175235365684</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4245240921629139</v>
+        <v>0.1013364382837299</v>
       </c>
       <c r="U26" t="n">
-        <v>0.09454951419700701</v>
+        <v>0.02788149920988271</v>
       </c>
       <c r="V26" t="n">
-        <v>0.09403078169205738</v>
+        <v>-0.112430145618894</v>
       </c>
       <c r="W26" t="n">
-        <v>0.08294656709663006</v>
+        <v>0.1017156805431056</v>
       </c>
       <c r="X26" t="n">
-        <v>0.241172919695705</v>
+        <v>0.1718904587610018</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.04348797769404898</v>
+        <v>0.1232260080208425</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>-0.1359794139252902</v>
+        <v>0.4232044727354066</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.1202107615767521</v>
+        <v>-0.1254034493607886</v>
       </c>
       <c r="AC26" t="n">
-        <v>-0.1536737477301625</v>
+        <v>0.2749925583666911</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.1818906566884235</v>
+        <v>0.0008441102064698741</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.1005955093335719</v>
+        <v>0.1822675323165109</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.08110712357273069</v>
+        <v>-0.011940414145192</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.1488722481402449</v>
+        <v>-0.02471492054491212</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.1670654890240136</v>
+        <v>0.02311093948188197</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.1357180814504419</v>
+        <v>-0.03385509408385932</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.06931490674948092</v>
+        <v>0.2984225767769396</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0.02680332647813333</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>-0.001318707098640264</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0.02298395062106526</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>TSH PRE RAI</t>
+          <t>STAGE</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1127873299937686</v>
+        <v>0.04876424449888972</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0148889500888936</v>
+        <v>0.2983461426226515</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1025946107809987</v>
+        <v>0.01385546075246977</v>
       </c>
       <c r="E27" t="n">
-        <v>0.005363961126576615</v>
+        <v>-0.0009886948036743936</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3012246406019373</v>
+        <v>0.01422760400390717</v>
       </c>
       <c r="G27" t="n">
-        <v>0.02638181263462756</v>
+        <v>-0.02460342921646849</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1539482271993118</v>
+        <v>0.1306519756686255</v>
       </c>
       <c r="I27" t="n">
-        <v>0.140308445486605</v>
+        <v>0.1019059998238823</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.004525054835909886</v>
+        <v>0.05151304677661937</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.4311544443863852</v>
+        <v>0.130241444553234</v>
       </c>
       <c r="L27" t="n">
-        <v>0.07187930977569956</v>
+        <v>0.09732227491769339</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0533676567742</v>
+        <v>-0.04094374786868287</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.3190751313085755</v>
+        <v>-0.002966127450942359</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.2987308103222592</v>
+        <v>-0.08759634147277566</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.004539827563902506</v>
+        <v>-0.02418898547761623</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.009387074393393133</v>
+        <v>-0.07814751335056276</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.07932871831423659</v>
+        <v>0.1576990375755911</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.001572357238546515</v>
+        <v>0.1228054286335495</v>
       </c>
       <c r="T27" t="n">
-        <v>0.001348063959217262</v>
+        <v>0.08365000727700264</v>
       </c>
       <c r="U27" t="n">
-        <v>0.2470672634540378</v>
+        <v>0.09186406302566945</v>
       </c>
       <c r="V27" t="n">
-        <v>0.1370395807868141</v>
+        <v>-0.1032404540521789</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.1690331910194983</v>
+        <v>0.01091722212456692</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.04755224972126298</v>
+        <v>0.2111409655558725</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.06386683563758457</v>
+        <v>0.1718979810323338</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.1359794139252902</v>
+        <v>0.4232044727354066</v>
       </c>
       <c r="AA27" t="n">
         <v>1</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.8144645183531841</v>
+        <v>-0.1692584381689046</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.8045859465220488</v>
+        <v>0.2722297570344954</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.7881721926658346</v>
+        <v>-0.1305317298126809</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.1431358212232606</v>
+        <v>0.1645873716700928</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.05086332713275012</v>
+        <v>0.000626270855736329</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.02130665437350098</v>
+        <v>-0.03726877476496396</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.252562260302303</v>
+        <v>-0.02917287716011005</v>
       </c>
       <c r="AI27" t="n">
-        <v>-0.2816104934927596</v>
+        <v>-0.05162334312940458</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-0.04336997767173514</v>
+        <v>0.150779985365596</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0.0466240469276788</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0.04196845334893702</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0.0411458088196802</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>TG PRE RAI</t>
+          <t>RAI</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.09815269968561122</v>
+        <v>0.08086035571558764</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03022212873463089</v>
+        <v>0.04860203217566524</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1325750851981729</v>
+        <v>0.02833972317983941</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0871870098944468</v>
+        <v>0.08568014013553121</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3080016657530053</v>
+        <v>-0.1809573883615606</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0281731848079774</v>
+        <v>-0.05518059524224142</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1744426017526866</v>
+        <v>-0.2635633413353763</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1796673884050835</v>
+        <v>-0.1314685515638324</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.04416570152876086</v>
+        <v>0.04130394740536714</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.4381340405735343</v>
+        <v>-0.3625922373381958</v>
       </c>
       <c r="L28" t="n">
-        <v>0.07395297859550827</v>
+        <v>-0.2545166963230679</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.05252320352070759</v>
+        <v>0.1134852568977098</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.3126388605034885</v>
+        <v>0.06342396042209118</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.2920770943780602</v>
+        <v>0.1347339858367184</v>
       </c>
       <c r="P28" t="n">
-        <v>0.0317429060302322</v>
+        <v>0.07681277742792297</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.02155019065377578</v>
+        <v>0.2657731674957998</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.08835197658830025</v>
+        <v>-0.0889701787765452</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.005960318968613554</v>
+        <v>-0.1032140247012125</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.005953819157798404</v>
+        <v>-0.1194725852824816</v>
       </c>
       <c r="U28" t="n">
-        <v>0.2399848757423723</v>
+        <v>-0.1032311028845723</v>
       </c>
       <c r="V28" t="n">
-        <v>0.1535321190501708</v>
+        <v>0.06450288380053396</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.0896998053830976</v>
+        <v>-0.01476055156627263</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.03043371366087548</v>
+        <v>-0.3065782778365298</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.05582394387532855</v>
+        <v>-0.2722855017777395</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.1202107615767521</v>
+        <v>-0.1254034493607886</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.8144645183531841</v>
+        <v>-0.1692584381689046</v>
       </c>
       <c r="AB28" t="n">
         <v>1</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.8106600740824814</v>
+        <v>-0.1698091469110241</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.7798404328267989</v>
+        <v>-0.01181078829441359</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.1430111294480242</v>
+        <v>-0.02019555291253303</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.1229841370604343</v>
+        <v>-0.09726711808217317</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.07407438735865136</v>
+        <v>-0.05205295558952357</v>
       </c>
       <c r="AH28" t="n">
-        <v>-0.2885646587056354</v>
+        <v>-0.228735512323846</v>
       </c>
       <c r="AI28" t="n">
-        <v>-0.3184287616794816</v>
+        <v>0.06438443538805516</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-0.05336585675972837</v>
+        <v>-0.01078374339868272</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>-0.03206847489636617</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>-0.07188612629757719</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>-0.04453039166457341</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>ANTI TG PRE RAI (POSITIVE or NEGATIVE)</t>
+          <t>RAIDOSE</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09924073886120452</v>
+        <v>-0.01963721415421305</v>
       </c>
       <c r="C29" t="n">
-        <v>0.06634559493096817</v>
+        <v>-0.07612100916365676</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1358103372966104</v>
+        <v>-0.06766548818462662</v>
       </c>
       <c r="E29" t="n">
-        <v>0.04198627881125391</v>
+        <v>-0.05754606730910285</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2921616562879174</v>
+        <v>0.2112915488638085</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01009623528252274</v>
+        <v>-0.08412534403458609</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1698657420838913</v>
+        <v>0.3331668676946908</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1558087644780302</v>
+        <v>0.02474026830718588</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.03511271244712053</v>
+        <v>0.02431206048679479</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.4411349374572784</v>
+        <v>0.3398216854212531</v>
       </c>
       <c r="L29" t="n">
-        <v>0.07001124739547351</v>
+        <v>0.1263317895101808</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.05518846714548916</v>
+        <v>-0.1273668191697876</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.2984582122609136</v>
+        <v>-0.001787650657604119</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.2639498813021089</v>
+        <v>-0.008003149378581148</v>
       </c>
       <c r="P29" t="n">
-        <v>0.04213965949196768</v>
+        <v>-0.06321465092938036</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.00676561560830219</v>
+        <v>-0.287529181077385</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.07064221585310096</v>
+        <v>0.2497508487635679</v>
       </c>
       <c r="S29" t="n">
-        <v>0.001012266449867295</v>
+        <v>0.2669872390626319</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.0131030095141908</v>
+        <v>0.2360265774148869</v>
       </c>
       <c r="U29" t="n">
-        <v>0.2870911097511041</v>
+        <v>0.1565989485702848</v>
       </c>
       <c r="V29" t="n">
-        <v>0.161377231527071</v>
+        <v>-0.1420913441373082</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.1729588821479186</v>
+        <v>0.08048739773288299</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.05864863097755116</v>
+        <v>0.2586273185834694</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.05142152221293294</v>
+        <v>0.2203383839600365</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.1536737477301625</v>
+        <v>0.2749925583666911</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.8045859465220488</v>
+        <v>0.2722297570344954</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.8106600740824814</v>
+        <v>-0.1698091469110241</v>
       </c>
       <c r="AC29" t="n">
         <v>1</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.9107029906690892</v>
+        <v>-0.009735258065301672</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.1320487365447541</v>
+        <v>0.2171687555490976</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.08717552952686271</v>
+        <v>-0.03846502869946892</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.007119010017816904</v>
+        <v>-0.100195159625834</v>
       </c>
       <c r="AH29" t="n">
-        <v>-0.293707243955094</v>
+        <v>-0.02743859429640343</v>
       </c>
       <c r="AI29" t="n">
-        <v>-0.2576428307579708</v>
+        <v>-0.1434685852042632</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-0.06717552510201222</v>
+        <v>0.1824562901897168</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.1461400800882485</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0.03826403504689955</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0.02715984333781421</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANTI TG PRE RAI </t>
+          <t>TSH PRE RAI</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.09820424347704894</v>
+        <v>0.03413257328241422</v>
       </c>
       <c r="C30" t="n">
-        <v>0.07140966344039418</v>
+        <v>-0.1809373139895543</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1404601227226843</v>
+        <v>0.005455005854045259</v>
       </c>
       <c r="E30" t="n">
-        <v>0.04939373120337847</v>
+        <v>-0.02169219716636224</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3117693805920781</v>
+        <v>-0.1138065280523517</v>
       </c>
       <c r="G30" t="n">
-        <v>0.04103918569833374</v>
+        <v>-0.05447715116824579</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1635122628502674</v>
+        <v>0.009893619104127692</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1724854762320824</v>
+        <v>0.02842145461144661</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.04168177187228451</v>
+        <v>-0.02371728529060209</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.4447852847400761</v>
+        <v>-0.1244799637763281</v>
       </c>
       <c r="L30" t="n">
-        <v>0.07084507356888595</v>
+        <v>0.02811412236988389</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.06926612303768563</v>
+        <v>-0.001922529043938902</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.3039465828354694</v>
+        <v>-0.084284410425547</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.259446576416083</v>
+        <v>-0.06962114321668407</v>
       </c>
       <c r="P30" t="n">
-        <v>0.03807416099886983</v>
+        <v>0.02309346244203659</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.02275367928315951</v>
+        <v>0.07271846158760008</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.08335566223102338</v>
+        <v>0.08467550162215345</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.01386483719270653</v>
+        <v>0.1103506734093615</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.0251352535911499</v>
+        <v>0.1130688738372151</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2790836140038915</v>
+        <v>0.1478330263804629</v>
       </c>
       <c r="V30" t="n">
-        <v>0.1674725408086119</v>
+        <v>0.01148419219441201</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.2067584718147851</v>
+        <v>-0.08128279859522436</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.06172838281011876</v>
+        <v>-0.009275368718551235</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.04673275812930502</v>
+        <v>0.06768603331783173</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.1818906566884235</v>
+        <v>0.0008441102064698741</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.7881721926658346</v>
+        <v>-0.1305317298126809</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.7798404328267989</v>
+        <v>-0.01181078829441359</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.9107029906690892</v>
+        <v>-0.009735258065301672</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.1209185190700906</v>
+        <v>0.09064763087658405</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.09252082490362389</v>
+        <v>-0.05734530250083441</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.02858941891950162</v>
+        <v>0.02653594977184845</v>
       </c>
       <c r="AH30" t="n">
-        <v>-0.2811110741469246</v>
+        <v>0.04931321406824798</v>
       </c>
       <c r="AI30" t="n">
-        <v>-0.2633882094396819</v>
+        <v>0.08300093579337978</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-0.04710524643896782</v>
+        <v>0.006761051019426505</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>-0.08320731686207405</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>-0.04184125845058375</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>-0.06147210330866285</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>OUTCOMEFOLLOWUP_MONTHSPOSTSURGERY</t>
+          <t>TG PRE RAI</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.05333849617270321</v>
+        <v>0.05010503584552657</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1247947155569244</v>
+        <v>-0.1453224209078465</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1062061875588359</v>
+        <v>-0.01239950109491967</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.07112625346677384</v>
+        <v>0.031427238807974</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.09621421053783238</v>
+        <v>0.04720402906016524</v>
       </c>
       <c r="G31" t="n">
-        <v>0.04089224928265665</v>
+        <v>-0.03293430484177805</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1352473964583196</v>
+        <v>0.09542397470336453</v>
       </c>
       <c r="I31" t="n">
-        <v>0.004000294543563248</v>
+        <v>0.1078235817655234</v>
       </c>
       <c r="J31" t="n">
-        <v>0.003812638107488955</v>
+        <v>0.003073174055598994</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.1803899171442074</v>
+        <v>0.05967235476613516</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.06412218321007188</v>
+        <v>0.08106677851385956</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1076892569265196</v>
+        <v>0.01701822399793934</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.0999379211666294</v>
+        <v>0.01656602158293573</v>
       </c>
       <c r="O31" t="n">
-        <v>0.100832166043131</v>
+        <v>-0.04512362270059302</v>
       </c>
       <c r="P31" t="n">
-        <v>0.08569882407068527</v>
+        <v>0.02598746296277693</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1085979635647896</v>
+        <v>-0.1181139162182397</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.1536721186808014</v>
+        <v>0.1226495792497489</v>
       </c>
       <c r="S31" t="n">
-        <v>-0.1030493208226727</v>
+        <v>0.2099900045568824</v>
       </c>
       <c r="T31" t="n">
-        <v>-0.09485462946659495</v>
+        <v>0.2052577627988174</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.08185125147472462</v>
+        <v>0.07764300526176507</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.09437219101973364</v>
+        <v>-0.08856486263781818</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.06131315629540669</v>
+        <v>0.1326535509009975</v>
       </c>
       <c r="X31" t="n">
-        <v>-0.02116859472771644</v>
+        <v>0.1411850416595193</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.04301434682497986</v>
+        <v>0.1609059724238873</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.1005955093335719</v>
+        <v>0.1822675323165109</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.1431358212232606</v>
+        <v>0.1645873716700928</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.1430111294480242</v>
+        <v>-0.02019555291253303</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.1320487365447541</v>
+        <v>0.2171687555490976</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.1209185190700906</v>
+        <v>0.09064763087658405</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.1476495262648052</v>
+        <v>-0.07521139663542452</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.002862847320034285</v>
+        <v>-0.1362682595670872</v>
       </c>
       <c r="AH31" t="n">
-        <v>-0.1239000266443861</v>
+        <v>0.004281074827935901</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.1508142204682478</v>
+        <v>-0.1227387958225873</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-0.1281521707305529</v>
+        <v>0.3308638520901785</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0.05313019012491828</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>-0.02131551747179619</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>-0.01609719787912343</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>TSH FOLLOW UP</t>
+          <t>ANTI TG PRE RAI (POSITIVE or NEGATIVE)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.02396956834931738</v>
+        <v>0.03905321747505927</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.04137888902262456</v>
+        <v>0.07794497293544218</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.004608994858731909</v>
+        <v>0.0205109406573495</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.03210013620248606</v>
+        <v>-0.01126592095209387</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1295450368579415</v>
+        <v>-0.04881607246094686</v>
       </c>
       <c r="G32" t="n">
-        <v>0.01033842863916536</v>
+        <v>-0.01957614020841991</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.05938081122792462</v>
+        <v>-0.06746940011580897</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1028037782517043</v>
+        <v>-0.001791826021911512</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.005364312022743699</v>
+        <v>-0.009067123639468795</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0269521602989089</v>
+        <v>-0.06106495705265275</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.05253739951344989</v>
+        <v>0.08190963173462597</v>
       </c>
       <c r="M32" t="n">
-        <v>0.03760624173341789</v>
+        <v>-0.04693125196985402</v>
       </c>
       <c r="N32" t="n">
-        <v>0.02295599967588079</v>
+        <v>-0.1292330632252945</v>
       </c>
       <c r="O32" t="n">
-        <v>0.1171781380455823</v>
+        <v>-0.0929930944937133</v>
       </c>
       <c r="P32" t="n">
-        <v>0.04773737766323616</v>
+        <v>-0.1117745860821232</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.07509335384667835</v>
+        <v>0.01153021269081836</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.1135928652838122</v>
+        <v>0.08341003307023297</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.1078376646168328</v>
+        <v>0.06899658630311134</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.05532171647768557</v>
+        <v>0.05955838532521428</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.1447529631147572</v>
+        <v>0.1384638544652446</v>
       </c>
       <c r="V32" t="n">
-        <v>-0.1132162568335883</v>
+        <v>0.03175361198294637</v>
       </c>
       <c r="W32" t="n">
-        <v>-0.00474498157371526</v>
+        <v>-0.1505331416096787</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.009443956029929503</v>
+        <v>0.05082267014197236</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.05731233613054878</v>
+        <v>0.08551985450341877</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.08110712357273069</v>
+        <v>-0.011940414145192</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.05086332713275012</v>
+        <v>0.000626270855736329</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.1229841370604343</v>
+        <v>-0.09726711808217317</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.08717552952686271</v>
+        <v>-0.03846502869946892</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.09252082490362389</v>
+        <v>-0.05734530250083441</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.1476495262648052</v>
+        <v>-0.07521139663542452</v>
       </c>
       <c r="AF32" t="n">
         <v>1</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.1152724690395168</v>
+        <v>0.5656066019972623</v>
       </c>
       <c r="AH32" t="n">
-        <v>-0.03622831611834096</v>
+        <v>-0.002125639303751816</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.06766930992280408</v>
+        <v>-0.02731187437055567</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.01237976022205755</v>
+        <v>0.00527661640501789</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.08386679951724943</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0.07737308647122249</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>-0.03893810004768056</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>TG FOLLOW UP</t>
+          <t xml:space="preserve">ANTI TG PRE RAI </t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1628376440033716</v>
+        <v>0.008465499285456039</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.04837323216622016</v>
+        <v>0.02281569781239416</v>
       </c>
       <c r="D33" t="n">
-        <v>0.02135076009822365</v>
+        <v>0.02760907933986359</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.06213678475858197</v>
+        <v>0.01427456914278958</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.06673435246593405</v>
+        <v>-0.03069322229785222</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.05347330683955737</v>
+        <v>0.01507679414233331</v>
       </c>
       <c r="H33" t="n">
-        <v>0.006992519228565358</v>
+        <v>-0.1134656158083502</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1795841859081218</v>
+        <v>0.01337733425229855</v>
       </c>
       <c r="J33" t="n">
-        <v>0.04064909220842924</v>
+        <v>0.004888161671559483</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.06762470139972009</v>
+        <v>-0.03449219263370141</v>
       </c>
       <c r="L33" t="n">
-        <v>0.05649622455862165</v>
+        <v>-0.00415276692903936</v>
       </c>
       <c r="M33" t="n">
-        <v>0.01980488780437314</v>
+        <v>-0.02905902954884057</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.03760206189801404</v>
+        <v>-0.1413850866361684</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.04879460836840006</v>
+        <v>0.01302939189057944</v>
       </c>
       <c r="P33" t="n">
-        <v>0.01574532571655931</v>
+        <v>0.02057670768560088</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.06152671370845591</v>
+        <v>0.08503031722204345</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0728135596385853</v>
+        <v>0.01639237632889547</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0926838014127799</v>
+        <v>-0.002067146615908513</v>
       </c>
       <c r="T33" t="n">
-        <v>0.06784733602725289</v>
+        <v>-0.009488071578062664</v>
       </c>
       <c r="U33" t="n">
-        <v>0.09933617528558722</v>
+        <v>0.006170876950018297</v>
       </c>
       <c r="V33" t="n">
-        <v>0.07949591590606644</v>
+        <v>0.01548383963097367</v>
       </c>
       <c r="W33" t="n">
-        <v>0.08034345549229417</v>
+        <v>-0.1763849275930112</v>
       </c>
       <c r="X33" t="n">
-        <v>0.02999956661144323</v>
+        <v>0.07193055171318515</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.05090693309999909</v>
+        <v>0.01472743076138192</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.1488722481402449</v>
+        <v>-0.02471492054491212</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.02130665437350098</v>
+        <v>-0.03726877476496396</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.07407438735865136</v>
+        <v>-0.05205295558952357</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.007119010017816904</v>
+        <v>-0.100195159625834</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.02858941891950162</v>
+        <v>0.02653594977184845</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.002862847320034285</v>
+        <v>-0.1362682595670872</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.1152724690395168</v>
+        <v>0.5656066019972623</v>
       </c>
       <c r="AG33" t="n">
         <v>1</v>
       </c>
       <c r="AH33" t="n">
-        <v>-0.08916520475571797</v>
+        <v>0.1213020515726692</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.01440012692666132</v>
+        <v>0.07879144243330909</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.0137715870343292</v>
+        <v>-0.09314230155300302</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0.06209626182645942</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0.2299191137310003</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>-0.01148040364927585</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>ANTI TG FOLLOW UP (POSITIVE or NEGATIVE)</t>
+          <t>OUTCOMEFOLLOWUP_MONTHSPOSTSURGERY</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.1274414124715532</v>
+        <v>-0.02660642310995417</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.05262196878056016</v>
+        <v>-0.07829998742629059</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.07259726776105671</v>
+        <v>0.07389975312941718</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.00999740530708918</v>
+        <v>-0.07257974945751368</v>
       </c>
       <c r="F34" t="n">
-        <v>0.244097621237361</v>
+        <v>-0.05032961222202263</v>
       </c>
       <c r="G34" t="n">
-        <v>0.03443271890961972</v>
+        <v>0.06031564003378743</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1779021351923735</v>
+        <v>-0.0920811748756737</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.08977557601038909</v>
+        <v>0.02168904689640586</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.05619502825477496</v>
+        <v>-0.01629973017812746</v>
       </c>
       <c r="K34" t="n">
-        <v>0.3954698263446486</v>
+        <v>-0.1042297422424207</v>
       </c>
       <c r="L34" t="n">
-        <v>0.01159614345278304</v>
+        <v>-0.009259211382527015</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.02757190463334472</v>
+        <v>0.0884110245886497</v>
       </c>
       <c r="N34" t="n">
-        <v>0.1873775481953699</v>
+        <v>-0.1505605063409815</v>
       </c>
       <c r="O34" t="n">
-        <v>0.09264219825939357</v>
+        <v>0.09117623973506245</v>
       </c>
       <c r="P34" t="n">
-        <v>-0.1279131873860186</v>
+        <v>0.1311760302983295</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.1399442703041758</v>
+        <v>0.0731007475613598</v>
       </c>
       <c r="R34" t="n">
-        <v>0.1394717857155122</v>
+        <v>0.001877224387934411</v>
       </c>
       <c r="S34" t="n">
-        <v>0.1300936643176341</v>
+        <v>0.008925888860914893</v>
       </c>
       <c r="T34" t="n">
-        <v>0.1501535549287084</v>
+        <v>-0.004643772790877314</v>
       </c>
       <c r="U34" t="n">
-        <v>-0.006235424833343505</v>
+        <v>-0.004782916242430454</v>
       </c>
       <c r="V34" t="n">
-        <v>0.04153691902271812</v>
+        <v>0.06406564211229447</v>
       </c>
       <c r="W34" t="n">
-        <v>0.06514707646774137</v>
+        <v>-0.08799495546515586</v>
       </c>
       <c r="X34" t="n">
-        <v>0.08375799466189925</v>
+        <v>0.0202400452520998</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.1898106507091225</v>
+        <v>0.1489531295353475</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.1670654890240136</v>
+        <v>0.02311093948188197</v>
       </c>
       <c r="AA34" t="n">
-        <v>-0.252562260302303</v>
+        <v>-0.02917287716011005</v>
       </c>
       <c r="AB34" t="n">
-        <v>-0.2885646587056354</v>
+        <v>-0.228735512323846</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.293707243955094</v>
+        <v>-0.02743859429640343</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.2811110741469246</v>
+        <v>0.04931321406824798</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.1239000266443861</v>
+        <v>0.004281074827935901</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.03622831611834096</v>
+        <v>-0.002125639303751816</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.08916520475571797</v>
+        <v>0.1213020515726692</v>
       </c>
       <c r="AH34" t="n">
         <v>1</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.3189095238332704</v>
+        <v>0.1284506996040896</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.1033190292967405</v>
+        <v>0.01903425100941919</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>-0.1548592696232827</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0.05440568318083076</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>-0.07857443134371904</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>ANTI TG FOLLOW UP</t>
+          <t>TSH FOLLOW UP</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.04927651108218349</v>
+        <v>0.02070778977938564</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.04640790316026284</v>
+        <v>0.02286278125906108</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.08256437881426303</v>
+        <v>0.08268452407301209</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.04529015461253896</v>
+        <v>-0.0225806262958686</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3035047410747507</v>
+        <v>-0.1247737087617955</v>
       </c>
       <c r="G35" t="n">
-        <v>0.008852760021730821</v>
+        <v>0.0223708674891002</v>
       </c>
       <c r="H35" t="n">
-        <v>0.171579240095186</v>
+        <v>-0.151371221076173</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.06563507729642998</v>
+        <v>-0.01383114541241584</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.04279130314014581</v>
+        <v>0.03605121999259477</v>
       </c>
       <c r="K35" t="n">
-        <v>0.345451911822736</v>
+        <v>-0.1850102522346893</v>
       </c>
       <c r="L35" t="n">
-        <v>0.002847657719432306</v>
+        <v>-0.1126512039312719</v>
       </c>
       <c r="M35" t="n">
-        <v>0.03026180988271241</v>
+        <v>0.07187267454303473</v>
       </c>
       <c r="N35" t="n">
-        <v>0.2373446800744995</v>
+        <v>-0.07676990751327779</v>
       </c>
       <c r="O35" t="n">
-        <v>0.1701070033332328</v>
+        <v>0.06735060286635219</v>
       </c>
       <c r="P35" t="n">
-        <v>-0.03993275905876646</v>
+        <v>0.08954226173832408</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.06766339031483004</v>
+        <v>0.1723337734295052</v>
       </c>
       <c r="R35" t="n">
-        <v>0.1217951212365447</v>
+        <v>-0.0937725174513806</v>
       </c>
       <c r="S35" t="n">
-        <v>0.07135242230361445</v>
+        <v>-0.0716573430255163</v>
       </c>
       <c r="T35" t="n">
-        <v>0.05947993959518601</v>
+        <v>0.01546335272816284</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.1376032628045009</v>
+        <v>-0.03239079750678218</v>
       </c>
       <c r="V35" t="n">
-        <v>-0.0571571850568778</v>
+        <v>0.0584740130158167</v>
       </c>
       <c r="W35" t="n">
-        <v>0.07044208642859143</v>
+        <v>-0.05494634526497122</v>
       </c>
       <c r="X35" t="n">
-        <v>0.06443610894974088</v>
+        <v>-0.1257158992499894</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.1845803460044396</v>
+        <v>-0.02559729979924891</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.1357180814504419</v>
+        <v>-0.03385509408385932</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.2816104934927596</v>
+        <v>-0.05162334312940458</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.3184287616794816</v>
+        <v>0.06438443538805516</v>
       </c>
       <c r="AC35" t="n">
-        <v>-0.2576428307579708</v>
+        <v>-0.1434685852042632</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.2633882094396819</v>
+        <v>0.08300093579337978</v>
       </c>
       <c r="AE35" t="n">
-        <v>-0.1508142204682478</v>
+        <v>-0.1227387958225873</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.06766930992280408</v>
+        <v>-0.02731187437055567</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.01440012692666132</v>
+        <v>0.07879144243330909</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.3189095238332704</v>
+        <v>0.1284506996040896</v>
       </c>
       <c r="AI35" t="n">
         <v>1</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.07451804090237538</v>
+        <v>-0.08626527531995123</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>-0.1124133509236517</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0.04050372650058295</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>-0.02733344394835103</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
+          <t>TG FOLLOW UP</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.06055183065567665</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.04468516456514963</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.04113830011822168</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.07076350084088558</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.01205958210200804</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-0.06386657037580507</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.04254251508171864</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.05768907558258705</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.03985109801639726</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.006107822316626218</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.06715208209719251</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.04816148064538751</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-0.00910270088149266</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-0.09082482076844595</v>
+      </c>
+      <c r="P36" t="n">
+        <v>-0.01653791108975803</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>-0.07149311666886458</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.1560918975586815</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.2079140640981204</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.1707350879842381</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.09338800585643421</v>
+      </c>
+      <c r="V36" t="n">
+        <v>-0.1381227751095845</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.09745564086479368</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.1311917885649831</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.1077660316141049</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.2984225767769396</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.150779985365596</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>-0.01078374339868272</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.1824562901897168</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.006761051019426505</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.3308638520901785</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.00527661640501789</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>-0.09314230155300302</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0.01903425100941919</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>-0.08626527531995123</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>-0.02645108826982346</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0.02757115949809522</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>-0.009684040952457802</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>ANTI TG FOLLOW UP (POSITIVE or NEGATIVE)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.1199856792654779</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.04331934169259238</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.07258433773300187</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.03337615600880419</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.2827652169448908</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.02619125271594785</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.09687834182330435</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-0.05982935279927063</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-0.05601339761222462</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.2903547206013168</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.02010448954239287</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-0.1000141145102716</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.1687884836597827</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.03630756175922136</v>
+      </c>
+      <c r="P37" t="n">
+        <v>-0.1729123751795936</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>-0.2737198565370546</v>
+      </c>
+      <c r="R37" t="n">
+        <v>-0.07712409568247811</v>
+      </c>
+      <c r="S37" t="n">
+        <v>-0.07030634670141503</v>
+      </c>
+      <c r="T37" t="n">
+        <v>-0.05790497859738603</v>
+      </c>
+      <c r="U37" t="n">
+        <v>-0.1117575912029964</v>
+      </c>
+      <c r="V37" t="n">
+        <v>-0.03140179993924808</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.05160164261045685</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.06023483047205125</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>-0.07050299248843558</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.02680332647813333</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.0466240469276788</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>-0.03206847489636617</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.1461400800882485</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>-0.08320731686207405</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.05313019012491828</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.08386679951724943</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.06209626182645942</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>-0.1548592696232827</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>-0.1124133509236517</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>-0.02645108826982346</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>-0.009724934215663361</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0.08598707547789738</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>ANTI TG FOLLOW UP</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.04369434761947667</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.02878162375726544</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.01752410800053829</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.01252691811916841</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-0.02016682154898497</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.02474080071933559</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.006979120211387076</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.03231620516151021</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-0.01838990425296168</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-0.006348383044623658</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-0.02358558055727042</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.03938177142189196</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-0.000682756027358706</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.1328570560334042</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.08984920435561854</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.04801467153188296</v>
+      </c>
+      <c r="R38" t="n">
+        <v>-0.01482333250957654</v>
+      </c>
+      <c r="S38" t="n">
+        <v>-0.00430818422993476</v>
+      </c>
+      <c r="T38" t="n">
+        <v>-0.0336176380878981</v>
+      </c>
+      <c r="U38" t="n">
+        <v>-0.03688661356033774</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.008589749695373374</v>
+      </c>
+      <c r="W38" t="n">
+        <v>-0.03945118395865131</v>
+      </c>
+      <c r="X38" t="n">
+        <v>-0.0154444413432885</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.008367212640206316</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-0.001318707098640264</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.04196845334893702</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>-0.07188612629757719</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.03826403504689955</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>-0.04184125845058375</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>-0.02131551747179619</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.07737308647122249</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.2299191137310003</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.05440568318083076</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.04050372650058295</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.02757115949809522</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>-0.009724934215663361</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0.009158040022286392</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
           <t>SUBTYPE_FOLLI_PAPIL</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>-0.0378516752470492</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0.1109755947232009</v>
-      </c>
-      <c r="D36" t="n">
-        <v>-0.1249026030329004</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.005450715131451302</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.06152860522623345</v>
-      </c>
-      <c r="G36" t="n">
-        <v>-0.07088504286698941</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.002670004425014695</v>
-      </c>
-      <c r="I36" t="n">
-        <v>-0.01677648841606776</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.1321834544132011</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.1475951006458546</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.008718836121823583</v>
-      </c>
-      <c r="M36" t="n">
-        <v>-0.009394824856111277</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0.08998811104534733</v>
-      </c>
-      <c r="O36" t="n">
-        <v>-0.005566760996333206</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0.004368914491667843</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0.04332393127940078</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0.01192714564423721</v>
-      </c>
-      <c r="S36" t="n">
-        <v>-0.04474307914758275</v>
-      </c>
-      <c r="T36" t="n">
-        <v>-0.02910008661214432</v>
-      </c>
-      <c r="U36" t="n">
-        <v>-0.09587009345138629</v>
-      </c>
-      <c r="V36" t="n">
-        <v>-0.04634614455280773</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0.03306160750335749</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0.0727299339375302</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0.1339619390590361</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0.06931490674948092</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>-0.04336997767173514</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>-0.05336585675972837</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>-0.06717552510201222</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>-0.04710524643896782</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>-0.1281521707305529</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0.01237976022205755</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0.0137715870343292</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0.1033190292967405</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0.07451804090237538</v>
-      </c>
-      <c r="AJ36" t="n">
+      <c r="B39" t="n">
+        <v>-0.02356751784422266</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.09285420806081821</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-0.132974891054905</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.0182348649208518</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.1583703193751885</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.04206301245545643</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.04159135941381416</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.01175153130266056</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.04344884681400774</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.1719640818434555</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.04422131885005764</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-0.004442661562165791</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.06043314061843652</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.0364422421236778</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.06560257166452294</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>-0.05921562488546625</v>
+      </c>
+      <c r="R39" t="n">
+        <v>-0.09227270806344895</v>
+      </c>
+      <c r="S39" t="n">
+        <v>-0.1201712782548971</v>
+      </c>
+      <c r="T39" t="n">
+        <v>-0.0944442778409173</v>
+      </c>
+      <c r="U39" t="n">
+        <v>-0.1207906220624961</v>
+      </c>
+      <c r="V39" t="n">
+        <v>-0.03466037578468611</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.05743700788546895</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.04288568974563574</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>-0.1110169822412851</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.02298395062106526</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.0411458088196802</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>-0.04453039166457341</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.02715984333781421</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>-0.06147210330866285</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>-0.01609719787912343</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>-0.03893810004768056</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>-0.01148040364927585</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>-0.07857443134371904</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>-0.02733344394835103</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>-0.009684040952457802</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0.08598707547789738</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0.009158040022286392</v>
+      </c>
+      <c r="AM39" t="n">
         <v>1</v>
       </c>
     </row>

--- a/variable_selection/spearman_corr_median.xlsx
+++ b/variable_selection/spearman_corr_median.xlsx
@@ -630,115 +630,115 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01269073506129029</v>
+        <v>0.03966417736053531</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03687129697282684</v>
+        <v>0.0305495587521682</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01036870963692328</v>
+        <v>-0.01835332458867056</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1522337324098139</v>
+        <v>-0.115637046863328</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.01065204875704046</v>
+        <v>-0.007655165232165101</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02051396006238272</v>
+        <v>0.04940594315424665</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1153968777790513</v>
+        <v>0.08344343987995004</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.03738738940810835</v>
+        <v>-0.04126738113247247</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1646061582476439</v>
+        <v>-0.1094824673616731</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01620244947506944</v>
+        <v>0.02305554586458248</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.04606020581379727</v>
+        <v>-0.02515538807269458</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1435335702701097</v>
+        <v>-0.07384235493348991</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1184327178731212</v>
+        <v>-0.1224300174203899</v>
       </c>
       <c r="P2" t="n">
-        <v>0.02781912045315838</v>
+        <v>0.006611582905645562</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02283502544625617</v>
+        <v>-0.0726758681161495</v>
       </c>
       <c r="R2" t="n">
-        <v>0.09373332085645929</v>
+        <v>0.09613146515819812</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1115595621038911</v>
+        <v>0.1085354535738797</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1088865201705398</v>
+        <v>0.08335664681153869</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1327240389581617</v>
+        <v>0.06403214902062797</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1166667338227477</v>
+        <v>-0.1161754311025996</v>
       </c>
       <c r="W2" t="n">
-        <v>0.007133991226581892</v>
+        <v>0.04335795594139932</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01159709222273092</v>
+        <v>0.02743076083534806</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05547784873328553</v>
+        <v>0.07691086095090374</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.04198304653301659</v>
+        <v>-0.00516984602510667</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.04876424449888972</v>
+        <v>0.06591941177995644</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.08086035571558764</v>
+        <v>0.06395916593038545</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.01963721415421305</v>
+        <v>0.04343607775541357</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.03413257328241422</v>
+        <v>0.04351174223573295</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.05010503584552657</v>
+        <v>0.08727834421609863</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.03905321747505927</v>
+        <v>-0.02031255225135883</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.008465499285456039</v>
+        <v>0.009936171530269891</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.02660642310995417</v>
+        <v>-0.01557973530699345</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.02070778977938564</v>
+        <v>0.02248376290198343</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.06055183065567665</v>
+        <v>0.09313853133981533</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.1199856792654779</v>
+        <v>-0.1932832690412749</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.04369434761947667</v>
+        <v>0.04991420707723565</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.02356751784422266</v>
+        <v>-0.01153433783728882</v>
       </c>
     </row>
     <row r="3">
@@ -748,118 +748,118 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01269073506129029</v>
+        <v>0.03966417736053531</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02578290024086439</v>
+        <v>0.04590683239666549</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07766483000761434</v>
+        <v>0.08771623816592503</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.09216899693437838</v>
+        <v>-0.117729095808594</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1094228685528726</v>
+        <v>0.1194623143686935</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1437171873721365</v>
+        <v>-0.1808371248003078</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01138921639626691</v>
+        <v>0.06091415363539143</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1900547927784644</v>
+        <v>0.138707859125643</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.09065413764237114</v>
+        <v>-0.1321395674697735</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.02326956413808288</v>
+        <v>0.009979938780738886</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.01835967955208173</v>
+        <v>-0.009882259919587435</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1316613877317259</v>
+        <v>-0.1165163794290833</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01352938446577086</v>
+        <v>0.04922418435569348</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002698547294766297</v>
+        <v>0.004060620121186458</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.143028057646777</v>
+        <v>0.2580079271563647</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.142537494472403</v>
+        <v>-0.1272598125253477</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2007287471480622</v>
+        <v>-0.1782534741493452</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2053999318983533</v>
+        <v>-0.1452275104984067</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.07482035525590021</v>
+        <v>0.01584632963403111</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.02168714376365774</v>
+        <v>-0.02545727048511588</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1018875163575239</v>
+        <v>-0.06846933207227221</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.07258700476579903</v>
+        <v>-0.05637427865429282</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.1789914924324122</v>
+        <v>-0.2218908228203615</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0003435624366104266</v>
+        <v>0.009193074103452315</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.2983461426226515</v>
+        <v>0.336796275022256</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.04860203217566524</v>
+        <v>0.07764393714667839</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.07612100916365676</v>
+        <v>-0.0958136554101664</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.1809373139895543</v>
+        <v>-0.1531559221723365</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.1453224209078465</v>
+        <v>-0.121910172489243</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.07794497293544218</v>
+        <v>0.1564016723751438</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.02281569781239416</v>
+        <v>0.03019536798675048</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.07829998742629059</v>
+        <v>-0.05069201368705699</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.02286278125906108</v>
+        <v>0.02531542127428177</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.04468516456514963</v>
+        <v>-0.04702960274841114</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.04331934169259238</v>
+        <v>-0.03455516344636985</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.02878162375726544</v>
+        <v>0.03582453827256738</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.09285420806081821</v>
+        <v>0.09337859248232171</v>
       </c>
     </row>
     <row r="4">
@@ -869,118 +869,118 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03687129697282684</v>
+        <v>0.0305495587521682</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02578290024086439</v>
+        <v>0.04590683239666549</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03462538369366576</v>
+        <v>0.05194261261899185</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1554273563116664</v>
+        <v>-0.1727793656264587</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.03905924321035227</v>
+        <v>-0.02918476583823183</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.09596103220008803</v>
+        <v>-0.1035037179964977</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0008797728635904786</v>
+        <v>0.02052746897122345</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01305887238962482</v>
+        <v>0.007914568465467946</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1825901739185543</v>
+        <v>-0.1989554596997055</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.01023648448285784</v>
+        <v>0.007514682249310486</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0705110790092968</v>
+        <v>-0.0504827970705829</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.09839321867787555</v>
+        <v>-0.09448611476592358</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.02713256739816396</v>
+        <v>-0.01003066735788836</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02352945977916111</v>
+        <v>0.001623884599273957</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1772591976667311</v>
+        <v>0.1144643612995026</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00386801670923928</v>
+        <v>0.01912772961658323</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01537649932899007</v>
+        <v>0.02809405190301223</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01467616265921041</v>
+        <v>0.001525233990799146</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08818496857142781</v>
+        <v>0.01177281589768749</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02386939372158895</v>
+        <v>0.02549045261313348</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.07343917412845845</v>
+        <v>-0.07576171853287501</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.0317414117742708</v>
+        <v>-0.0207061618020149</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.02914510365667243</v>
+        <v>-0.04296555172101447</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.03212022651322469</v>
+        <v>-0.03997009012762456</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01385546075246977</v>
+        <v>0.02547584781604136</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02833972317983941</v>
+        <v>0.02365505702770799</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.06766548818462662</v>
+        <v>-0.09591108231253311</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.005455005854045259</v>
+        <v>-0.00275150612978952</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.01239950109491967</v>
+        <v>-0.01455195335256021</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0205109406573495</v>
+        <v>0.1015838141185567</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.02760907933986359</v>
+        <v>0.03142754912093982</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.07389975312941718</v>
+        <v>0.109442256778459</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.08268452407301209</v>
+        <v>0.07091216352600369</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.04113830011822168</v>
+        <v>0.04145736893493546</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.07258433773300187</v>
+        <v>-0.1201469003951805</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.01752410800053829</v>
+        <v>0.01739507195281018</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.132974891054905</v>
+        <v>-0.1202532894096583</v>
       </c>
     </row>
     <row r="5">
@@ -990,118 +990,118 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01036870963692328</v>
+        <v>-0.01835332458867056</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07766483000761434</v>
+        <v>0.08771623816592503</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03462538369366576</v>
+        <v>0.05194261261899185</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.109667169645882</v>
+        <v>-0.1167020355762861</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.005478593058844313</v>
+        <v>0.001104600929204267</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.06675071872589464</v>
+        <v>-0.07443360449257923</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0197209478272581</v>
+        <v>0.03306526802210073</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01828710258636054</v>
+        <v>0.03278441843798845</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.08286459774615575</v>
+        <v>-0.1096731780102079</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.05040739675310264</v>
+        <v>-0.02228490706952123</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01864985137676655</v>
+        <v>0.03367092744948193</v>
       </c>
       <c r="N5" t="n">
-        <v>0.006867152886379686</v>
+        <v>0.0006450745851180126</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.09206742764169834</v>
+        <v>-0.04833641824115277</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.05210395222110989</v>
+        <v>-0.06286653421445899</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.05608662768726733</v>
+        <v>0.03821350844527899</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0172031392190454</v>
+        <v>0.01758980418763172</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02818127808720527</v>
+        <v>0.02160563950877607</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0214791314896809</v>
+        <v>-0.007839355576798752</v>
       </c>
       <c r="U5" t="n">
-        <v>0.05929950995374642</v>
+        <v>-0.02430360961017555</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0293521286412921</v>
+        <v>-0.02446309284812376</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.02348276053823919</v>
+        <v>-0.03053474560726398</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02235593954320466</v>
+        <v>0.01423361992531246</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.0190724348429142</v>
+        <v>-0.04463831446220175</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.003213128002482984</v>
+        <v>-0.02492956399870845</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.0009886948036743936</v>
+        <v>-0.003906027338621654</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.08568014013553121</v>
+        <v>0.07887884871248191</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.05754606730910285</v>
+        <v>-0.09315770082509091</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.02169219716636224</v>
+        <v>-0.01084428440937876</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.031427238807974</v>
+        <v>0.03588596017311229</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.01126592095209387</v>
+        <v>0.09424224330222147</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.01427456914278958</v>
+        <v>0.02108010328987807</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.07257974945751368</v>
+        <v>-0.04876196204867768</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.0225806262958686</v>
+        <v>-0.02421338136450438</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.07076350084088558</v>
+        <v>-0.05659886028063899</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.03337615600880419</v>
+        <v>-0.004750214430648298</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.01252691811916841</v>
+        <v>-0.0130962319225582</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.0182348649208518</v>
+        <v>0.008066099441391051</v>
       </c>
     </row>
     <row r="6">
@@ -1111,118 +1111,118 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1522337324098139</v>
+        <v>-0.115637046863328</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.09216899693437838</v>
+        <v>-0.117729095808594</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1554273563116664</v>
+        <v>-0.1727793656264587</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.109667169645882</v>
+        <v>-0.1167020355762861</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01818774247676858</v>
+        <v>0.01972095887573155</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2828518103383994</v>
+        <v>0.2866917523174407</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1043403094654996</v>
+        <v>-0.1545111319955361</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.02706407238541058</v>
+        <v>-0.01825906105364129</v>
       </c>
       <c r="K6" t="n">
-        <v>0.633057645407523</v>
+        <v>0.6024754209102676</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04103048335024859</v>
+        <v>-0.01656063573425788</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01434956078455301</v>
+        <v>-0.0215712608018891</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2912123824277488</v>
+        <v>0.260269710321736</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1977402119217909</v>
+        <v>0.1254016565685502</v>
       </c>
       <c r="P6" t="n">
-        <v>0.09838922699319871</v>
+        <v>0.1106698430544161</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.3697675490419548</v>
+        <v>-0.1561088192130219</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1216414746635736</v>
+        <v>-0.1036057698539964</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1547206862155288</v>
+        <v>-0.134800668233367</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1462649603350751</v>
+        <v>-0.02946003691012613</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2683107582597542</v>
+        <v>0.05734165369372754</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.01131855634550556</v>
+        <v>-0.0296046945812596</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2141704782200169</v>
+        <v>0.1922829914499318</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1848759945627597</v>
+        <v>0.1481174892059698</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.1258623163043516</v>
+        <v>-0.04762607025480222</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.145392861228714</v>
+        <v>0.123219146318828</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01422760400390717</v>
+        <v>-0.0283806042852627</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.1809573883615606</v>
+        <v>-0.1258261360314079</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2112915488638085</v>
+        <v>0.2852031045707436</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.1138065280523517</v>
+        <v>-0.08711457705674198</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.04720402906016524</v>
+        <v>0.06460503404016603</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.04881607246094686</v>
+        <v>-0.2809877914210465</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.03069322229785222</v>
+        <v>-0.02043260750154726</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.05032961222202263</v>
+        <v>-0.1241712451200391</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.1247737087617955</v>
+        <v>-0.09466646578017396</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01205958210200804</v>
+        <v>0.001088144885599773</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.2827652169448908</v>
+        <v>0.357193694517332</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.02016682154898497</v>
+        <v>-0.02850053632515961</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.1583703193751885</v>
+        <v>0.1233841420151827</v>
       </c>
     </row>
     <row r="7">
@@ -1232,118 +1232,118 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.01065204875704046</v>
+        <v>-0.007655165232165101</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1094228685528726</v>
+        <v>0.1194623143686935</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.03905924321035227</v>
+        <v>-0.02918476583823183</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.005478593058844313</v>
+        <v>0.001104600929204267</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01818774247676858</v>
+        <v>0.01972095887573155</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02390314597833009</v>
+        <v>0.0001372224422580808</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02385514403226549</v>
+        <v>0.01418601727489574</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.02851277720833561</v>
+        <v>-0.02600436298325554</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01868546599770588</v>
+        <v>0.01689739278064869</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0414820432459385</v>
+        <v>-0.03546212850110445</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.01744125107691647</v>
+        <v>-0.02790718933526038</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.05181687209293051</v>
+        <v>-0.05622300513782007</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01892977263368882</v>
+        <v>0.05175052691015226</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03916078392112351</v>
+        <v>0.05057637294087458</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.008086536865547741</v>
+        <v>0.04036719094913472</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.05582909029710705</v>
+        <v>-0.07108895076072222</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.05263035294845073</v>
+        <v>-0.0716163267228199</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.02213916173445776</v>
+        <v>-0.01148823867608542</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0697871401667018</v>
+        <v>-0.006611724227291254</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02995739212893643</v>
+        <v>0.03383924880863003</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01198449508643029</v>
+        <v>0.0115914103572963</v>
       </c>
       <c r="X7" t="n">
-        <v>0.007137939687145619</v>
+        <v>0.0002682532067612749</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.05771359079438979</v>
+        <v>-0.07139800548439802</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.03045141488433014</v>
+        <v>-0.04259179597633447</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.02460342921646849</v>
+        <v>0.004459347085231402</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.05518059524224142</v>
+        <v>-0.0266252727592989</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.08412534403458609</v>
+        <v>-0.06752619875881324</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.05447715116824579</v>
+        <v>-0.03156906911896547</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.03293430484177805</v>
+        <v>-0.01527513187579614</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.01957614020841991</v>
+        <v>0.002516327957631364</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.01507679414233331</v>
+        <v>0.01525651252800324</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.06031564003378743</v>
+        <v>0.06420969514996855</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0223708674891002</v>
+        <v>0.007722041152113097</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.06386657037580507</v>
+        <v>-0.04285193184980705</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.02619125271594785</v>
+        <v>0.0228640905639778</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.02474080071933559</v>
+        <v>0.03318385792398505</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.04206301245545643</v>
+        <v>0.05375488601022387</v>
       </c>
     </row>
     <row r="8">
@@ -1353,118 +1353,118 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02051396006238272</v>
+        <v>0.04940594315424665</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1437171873721365</v>
+        <v>-0.1808371248003078</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.09596103220008803</v>
+        <v>-0.1035037179964977</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.06675071872589464</v>
+        <v>-0.07443360449257923</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2828518103383994</v>
+        <v>0.2866917523174407</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02390314597833009</v>
+        <v>0.0001372224422580808</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07307438879841391</v>
+        <v>0.02408133319861092</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1614482294268307</v>
+        <v>-0.1479769348076943</v>
       </c>
       <c r="K8" t="n">
-        <v>0.43609110674716</v>
+        <v>0.4310369000634316</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1450776926744153</v>
+        <v>0.1436302191815103</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0884771231235036</v>
+        <v>-0.09942388190262322</v>
       </c>
       <c r="N8" t="n">
-        <v>0.07150913600771092</v>
+        <v>0.06787830475643222</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01839907261593746</v>
+        <v>0.002533409763365991</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01196369489792203</v>
+        <v>-0.0120949723752487</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.3085856379458771</v>
+        <v>-0.5747760637043353</v>
       </c>
       <c r="R8" t="n">
-        <v>0.29784416485028</v>
+        <v>0.299799493158914</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2242098501533842</v>
+        <v>0.2073694991195718</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1911599013687688</v>
+        <v>-0.01238302761558865</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2286117397162896</v>
+        <v>0.0987721715159882</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.07562405126357916</v>
+        <v>-0.08488752040746821</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1179367828642263</v>
+        <v>0.09194464832272316</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2205190754324522</v>
+        <v>0.2044465444928462</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2211258560479276</v>
+        <v>0.3278842704773186</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1383157890585368</v>
+        <v>0.1128007836533903</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.1306519756686255</v>
+        <v>0.09190717078294861</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.2635633413353763</v>
+        <v>-0.2634306698931043</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.3331668676946908</v>
+        <v>0.3280659043212374</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.009893619104127692</v>
+        <v>0.006536185694891158</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.09542397470336453</v>
+        <v>0.1124655427513775</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.06746940011580897</v>
+        <v>-0.190165662433137</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.1134656158083502</v>
+        <v>-0.05442581933528388</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.0920811748756737</v>
+        <v>-0.1203378324896288</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.151371221076173</v>
+        <v>-0.1392493058251338</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.04254251508171864</v>
+        <v>0.03912097008960316</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.09687834182330435</v>
+        <v>0.1376772925775237</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.006979120211387076</v>
+        <v>0.02567084236753841</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.04159135941381416</v>
+        <v>0.02349933314193967</v>
       </c>
     </row>
     <row r="9">
@@ -1474,118 +1474,118 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1153968777790513</v>
+        <v>0.08344343987995004</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01138921639626691</v>
+        <v>0.06091415363539143</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0008797728635904786</v>
+        <v>0.02052746897122345</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0197209478272581</v>
+        <v>0.03306526802210073</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1043403094654996</v>
+        <v>-0.1545111319955361</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02385514403226549</v>
+        <v>0.01418601727489574</v>
       </c>
       <c r="H9" t="n">
-        <v>0.07307438879841391</v>
+        <v>0.02408133319861092</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.07124919980288573</v>
+        <v>-0.04857231853572606</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.01848601861956352</v>
+        <v>-0.01168688329931937</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3340768875482937</v>
+        <v>0.3963325384802109</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.07568404987026707</v>
+        <v>-0.04103134340466048</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1457651641647855</v>
+        <v>-0.1484053561941188</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1480544566903156</v>
+        <v>-0.09739489314312397</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03904611743900277</v>
+        <v>-0.1345589332218204</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.03937386683080294</v>
+        <v>-0.05229438754479994</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0829750981768265</v>
+        <v>0.07623389954291393</v>
       </c>
       <c r="S9" t="n">
-        <v>0.08981647732583906</v>
+        <v>0.09872356641761418</v>
       </c>
       <c r="T9" t="n">
-        <v>0.07461173815021643</v>
+        <v>0.007307391974001648</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1153019899707529</v>
+        <v>0.02444231200951125</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1732314704133533</v>
+        <v>-0.1084970877830468</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02956832568694377</v>
+        <v>0.02033228354191519</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1335841781562723</v>
+        <v>0.2317095409306767</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1817821800479984</v>
+        <v>0.09552973575374833</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.08652543757085339</v>
+        <v>0.07357497000723452</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.1019059998238823</v>
+        <v>0.199680494810203</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.1314685515638324</v>
+        <v>-0.1425186363913494</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.02474026830718588</v>
+        <v>-0.008839303300320001</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.02842145461144661</v>
+        <v>0.02804296377479942</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.1078235817655234</v>
+        <v>0.1305976127520379</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.001791826021911512</v>
+        <v>0.1374728952416535</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.01337733425229855</v>
+        <v>0.05276045372031026</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.02168904689640586</v>
+        <v>0.0703119413668022</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.01383114541241584</v>
+        <v>-0.04604690155678313</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.05768907558258705</v>
+        <v>0.1128352462530348</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.05982935279927063</v>
+        <v>-0.1087142311184365</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.03231620516151021</v>
+        <v>0.06475014708383739</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.01175153130266056</v>
+        <v>0.007960125724786068</v>
       </c>
     </row>
     <row r="10">
@@ -1595,118 +1595,118 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.03738738940810835</v>
+        <v>-0.04126738113247247</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1900547927784644</v>
+        <v>0.138707859125643</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01305887238962482</v>
+        <v>0.007914568465467946</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01828710258636054</v>
+        <v>0.03278441843798845</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.02706407238541058</v>
+        <v>-0.01825906105364129</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.02851277720833561</v>
+        <v>-0.02600436298325554</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1614482294268307</v>
+        <v>-0.1479769348076943</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.07124919980288573</v>
+        <v>-0.04857231853572606</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02704243181800291</v>
+        <v>0.06577816128877451</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1105551499112351</v>
+        <v>-0.09860865727569394</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1335594495273136</v>
+        <v>0.1311174475080887</v>
       </c>
       <c r="N10" t="n">
-        <v>0.06427598582047506</v>
+        <v>0.07317627173730071</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.02143083334347548</v>
+        <v>-0.05863304685539938</v>
       </c>
       <c r="P10" t="n">
-        <v>0.05056684726522011</v>
+        <v>0.05863671137011208</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.113781346640297</v>
+        <v>0.1400378816602204</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.05729247253711287</v>
+        <v>-0.03861396167681506</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.05650398729342467</v>
+        <v>-0.03240110425051796</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.07364922870788</v>
+        <v>-0.01322008910615778</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.07401030496073775</v>
+        <v>0.01631091114606687</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.03957853342849704</v>
+        <v>-0.0307279899755764</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.02124038645504387</v>
+        <v>-0.00135052281934775</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1565593496771505</v>
+        <v>0.1753551009756561</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.08435869091922807</v>
+        <v>-0.04979208040739266</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.05462426531798821</v>
+        <v>0.1219948080944262</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.05151304677661937</v>
+        <v>0.09273087914046169</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.04130394740536714</v>
+        <v>0.03037675143640918</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.02431206048679479</v>
+        <v>0.04540133042782918</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.02371728529060209</v>
+        <v>-0.02335722849295793</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.003073174055598994</v>
+        <v>0.01209374571465077</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.009067123639468795</v>
+        <v>-0.01114251725317284</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.004888161671559483</v>
+        <v>-0.02961178482574818</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.01629973017812746</v>
+        <v>-0.02504217273383481</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.03605121999259477</v>
+        <v>-0.003320340679930911</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.03985109801639726</v>
+        <v>0.04380857502794992</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.05601339761222462</v>
+        <v>-0.0422713537798215</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.01838990425296168</v>
+        <v>-0.04571942718531442</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.04344884681400774</v>
+        <v>0.1005430860688317</v>
       </c>
     </row>
     <row r="11">
@@ -1716,118 +1716,118 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1646061582476439</v>
+        <v>-0.1094824673616731</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.09065413764237114</v>
+        <v>-0.1321395674697735</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1825901739185543</v>
+        <v>-0.1989554596997055</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.08286459774615575</v>
+        <v>-0.1096731780102079</v>
       </c>
       <c r="F11" t="n">
-        <v>0.633057645407523</v>
+        <v>0.6024754209102676</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01868546599770588</v>
+        <v>0.01689739278064869</v>
       </c>
       <c r="H11" t="n">
-        <v>0.43609110674716</v>
+        <v>0.4310369000634316</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01848601861956352</v>
+        <v>-0.01168688329931937</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02704243181800291</v>
+        <v>0.06577816128877451</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1576589984556851</v>
+        <v>0.1390911347946316</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.04775394829154713</v>
+        <v>-0.0666977944883158</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2896267267755826</v>
+        <v>0.2333268040226478</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1392703500850958</v>
+        <v>0.0483855304905853</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.005207950996764357</v>
+        <v>0.004446979543487518</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.4592727459815287</v>
+        <v>-0.2991325931333052</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.0342657706664489</v>
+        <v>-0.02006257852707587</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.08794470942920307</v>
+        <v>-0.06992213764196778</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.08843311826960809</v>
+        <v>-0.03237988433494737</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1941317933539919</v>
+        <v>0.07045211108745553</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0392265915321642</v>
+        <v>-0.06398921929979283</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2256410048462239</v>
+        <v>0.2190077770598675</v>
       </c>
       <c r="X11" t="n">
-        <v>0.5125796464254878</v>
+        <v>0.5121174659761561</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.007980803355422528</v>
+        <v>0.1093155754376719</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.1338783962646908</v>
+        <v>0.1436397159386585</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.130241444553234</v>
+        <v>0.1054889312571502</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.3625922373381958</v>
+        <v>-0.3455220371632705</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.3398216854212531</v>
+        <v>0.4005548041603108</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.1244799637763281</v>
+        <v>-0.09911824647973455</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.05967235476613516</v>
+        <v>0.1005443519951172</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.06106495705265275</v>
+        <v>-0.2886086323851482</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.03449219263370141</v>
+        <v>-0.01902684162819378</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.1042297422424207</v>
+        <v>-0.1558810589898874</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.1850102522346893</v>
+        <v>-0.1966532787729737</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.006107822316626218</v>
+        <v>0.03061249721217357</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.2903547206013168</v>
+        <v>0.3557231048932721</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.006348383044623658</v>
+        <v>-0.002650952581590977</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.1719640818434555</v>
+        <v>0.1391279009679643</v>
       </c>
     </row>
     <row r="12">
@@ -1837,118 +1837,118 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01620244947506944</v>
+        <v>0.02305554586458248</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.02326956413808288</v>
+        <v>0.009979938780738886</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.01023648448285784</v>
+        <v>0.007514682249310486</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.05040739675310264</v>
+        <v>-0.02228490706952123</v>
       </c>
       <c r="F12" t="n">
-        <v>0.04103048335024859</v>
+        <v>-0.01656063573425788</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0414820432459385</v>
+        <v>-0.03546212850110445</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1450776926744153</v>
+        <v>0.1436302191815103</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3340768875482937</v>
+        <v>0.3963325384802109</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1105551499112351</v>
+        <v>-0.09860865727569394</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1576589984556851</v>
+        <v>0.1390911347946316</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1086641718114566</v>
+        <v>-0.09545538355072358</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.09086355414068409</v>
+        <v>-0.1416629496049961</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2129911236675714</v>
+        <v>-0.1704830371823579</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1193935685433825</v>
+        <v>-0.2220675150573169</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1849651103532243</v>
+        <v>-0.2037544230648809</v>
       </c>
       <c r="R12" t="n">
-        <v>0.09757091954247528</v>
+        <v>0.1332712177928847</v>
       </c>
       <c r="S12" t="n">
-        <v>0.100240797581537</v>
+        <v>0.137715457145394</v>
       </c>
       <c r="T12" t="n">
-        <v>0.07930358555136487</v>
+        <v>0.02844001274661359</v>
       </c>
       <c r="U12" t="n">
-        <v>0.08882355842397915</v>
+        <v>0.05421645881420206</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1465269211300922</v>
+        <v>-0.153309241860334</v>
       </c>
       <c r="W12" t="n">
-        <v>0.02409834409745392</v>
+        <v>0.05376102431534226</v>
       </c>
       <c r="X12" t="n">
-        <v>0.2586789267292378</v>
+        <v>0.3345847341323175</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1872976754025887</v>
+        <v>0.167767556531489</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.1100039671067572</v>
+        <v>0.09443220054879853</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.09732227491769339</v>
+        <v>0.198632534250445</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.2545166963230679</v>
+        <v>-0.262430125896178</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1263317895101808</v>
+        <v>0.07021344641507432</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.02811412236988389</v>
+        <v>0.02805925396012487</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.08106677851385956</v>
+        <v>0.1328396032260491</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.08190963173462597</v>
+        <v>0.1749377444589405</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.00415276692903936</v>
+        <v>0.02127116322811755</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.009259211382527015</v>
+        <v>0.03712125199121296</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.1126512039312719</v>
+        <v>-0.1350750381760649</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.06715208209719251</v>
+        <v>0.1285150003132419</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.02010448954239287</v>
+        <v>-0.0003810795160044098</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.02358558055727042</v>
+        <v>0.01145480576553741</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.04422131885005764</v>
+        <v>0.04490067847168426</v>
       </c>
     </row>
     <row r="13">
@@ -1958,118 +1958,118 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.04606020581379727</v>
+        <v>-0.02515538807269458</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.01835967955208173</v>
+        <v>-0.009882259919587435</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0705110790092968</v>
+        <v>-0.0504827970705829</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01864985137676655</v>
+        <v>0.03367092744948193</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01434956078455301</v>
+        <v>-0.0215712608018891</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.01744125107691647</v>
+        <v>-0.02790718933526038</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0884771231235036</v>
+        <v>-0.09942388190262322</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.07568404987026707</v>
+        <v>-0.04103134340466048</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1335594495273136</v>
+        <v>0.1311174475080887</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.04775394829154713</v>
+        <v>-0.0666977944883158</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1086641718114566</v>
+        <v>-0.09545538355072358</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4156388191998225</v>
+        <v>0.4716224685575643</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1229403224515356</v>
+        <v>0.1161520286421683</v>
       </c>
       <c r="P13" t="n">
-        <v>0.04242800792153292</v>
+        <v>0.03756643658106745</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.09167053116210271</v>
+        <v>0.1278399363458385</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.1558552651534492</v>
+        <v>-0.1258283963184078</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1024413431323417</v>
+        <v>-0.0765840584732477</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.06339282214547495</v>
+        <v>-0.00419968170459278</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1176529602519697</v>
+        <v>-0.04109016329439494</v>
       </c>
       <c r="V13" t="n">
-        <v>0.05427806986755476</v>
+        <v>0.04825586386953187</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1199230980476398</v>
+        <v>0.08274820643481702</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.05431005658088087</v>
+        <v>-0.05323445447963348</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.09869731977897006</v>
+        <v>-0.08048445955910374</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.004476247724968099</v>
+        <v>-0.002104070175083831</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.04094374786868287</v>
+        <v>-0.03452366883273245</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.1134852568977098</v>
+        <v>0.09198366519674726</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.1273668191697876</v>
+        <v>-0.1164069740545392</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.001922529043938902</v>
+        <v>-0.00307709536432054</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.01701822399793934</v>
+        <v>0.03265692537516056</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.04693125196985402</v>
+        <v>0.03606522044946776</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.02905902954884057</v>
+        <v>-0.02549776577030493</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.0884110245886497</v>
+        <v>0.102427372763429</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.07187267454303473</v>
+        <v>0.07740411964590795</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.04816148064538751</v>
+        <v>0.03921950257913655</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.1000141145102716</v>
+        <v>-0.03614325861285465</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.03938177142189196</v>
+        <v>0.03850841213680282</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0.004442661562165791</v>
+        <v>-0.03248599822604527</v>
       </c>
     </row>
     <row r="14">
@@ -2079,118 +2079,118 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.1435335702701097</v>
+        <v>-0.07384235493348991</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1316613877317259</v>
+        <v>-0.1165163794290833</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09839321867787555</v>
+        <v>-0.09448611476592358</v>
       </c>
       <c r="E14" t="n">
-        <v>0.006867152886379686</v>
+        <v>0.0006450745851180126</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2912123824277488</v>
+        <v>0.260269710321736</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.05181687209293051</v>
+        <v>-0.05622300513782007</v>
       </c>
       <c r="H14" t="n">
-        <v>0.07150913600771092</v>
+        <v>0.06787830475643222</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1457651641647855</v>
+        <v>-0.1484053561941188</v>
       </c>
       <c r="J14" t="n">
-        <v>0.06427598582047506</v>
+        <v>0.07317627173730071</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2896267267755826</v>
+        <v>0.2333268040226478</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.09086355414068409</v>
+        <v>-0.1416629496049961</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4156388191998225</v>
+        <v>0.4716224685575643</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.177354939390939</v>
+        <v>0.1254331686871325</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.05621013966283236</v>
+        <v>0.02823435888770986</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1228720013589826</v>
+        <v>-0.02521614682322305</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.1134978182015774</v>
+        <v>-0.08395728887688214</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.129424393090303</v>
+        <v>-0.1154348266372058</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.09534171162795711</v>
+        <v>-0.04914692243181745</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1961509848795527</v>
+        <v>-0.04657503310025886</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1053424912644674</v>
+        <v>0.06724854529454637</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1948520292257991</v>
+        <v>0.1423643749912813</v>
       </c>
       <c r="X14" t="n">
-        <v>0.06764489181216547</v>
+        <v>0.01250604383410962</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.1430907389358226</v>
+        <v>-0.06154598321558994</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.04889514688311423</v>
+        <v>0.05707298851726765</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.002966127450942359</v>
+        <v>-0.03783673237164049</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.06342396042209118</v>
+        <v>0.04026969725567445</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.001787650657604119</v>
+        <v>0.06413559029739187</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.084284410425547</v>
+        <v>-0.0785113947352353</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.01656602158293573</v>
+        <v>0.03213977805668538</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.1292330632252945</v>
+        <v>-0.1711676953858127</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.1413850866361684</v>
+        <v>-0.1242057202197978</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.1505605063409815</v>
+        <v>-0.154403617876576</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.07676990751327779</v>
+        <v>-0.06028738530628312</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.00910270088149266</v>
+        <v>0.01131373754909017</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.1687884836597827</v>
+        <v>0.2260185669317089</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.000682756027358706</v>
+        <v>-0.0279661825906723</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.06043314061843652</v>
+        <v>0.01866377910837834</v>
       </c>
     </row>
     <row r="15">
@@ -2200,118 +2200,118 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1184327178731212</v>
+        <v>-0.1224300174203899</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01352938446577086</v>
+        <v>0.04922418435569348</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.02713256739816396</v>
+        <v>-0.01003066735788836</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.09206742764169834</v>
+        <v>-0.04833641824115277</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1977402119217909</v>
+        <v>0.1254016565685502</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01892977263368882</v>
+        <v>0.05175052691015226</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01839907261593746</v>
+        <v>0.002533409763365991</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1480544566903156</v>
+        <v>-0.09739489314312397</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.02143083334347548</v>
+        <v>-0.05863304685539938</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1392703500850958</v>
+        <v>0.0483855304905853</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2129911236675714</v>
+        <v>-0.1704830371823579</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1229403224515356</v>
+        <v>0.1161520286421683</v>
       </c>
       <c r="N15" t="n">
-        <v>0.177354939390939</v>
+        <v>0.1254331686871325</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4367175439856157</v>
+        <v>0.3054315381328672</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.03319611958242574</v>
+        <v>0.1614136135186657</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.1766040614371755</v>
+        <v>-0.163425882888857</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2214678411983576</v>
+        <v>-0.2059853270402139</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2181229464451943</v>
+        <v>-0.08664263684430294</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2627367986766575</v>
+        <v>0.03359840536658078</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2389615627654906</v>
+        <v>0.2073913853768473</v>
       </c>
       <c r="W15" t="n">
-        <v>0.05543274574799884</v>
+        <v>0.0007256260691689213</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.08226397361485951</v>
+        <v>-0.0985113970796701</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.1473555707181819</v>
+        <v>-0.1509933825754785</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.02914951831289996</v>
+        <v>-0.07459653367222162</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.08759634147277566</v>
+        <v>-0.06951713561401776</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.1347339858367184</v>
+        <v>0.1353875603390245</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.008003149378581148</v>
+        <v>-0.06211550874624753</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.06962114321668407</v>
+        <v>-0.05361160385572424</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.04512362270059302</v>
+        <v>-0.03670614796071862</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.0929930944937133</v>
+        <v>0.0800453664614155</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.01302939189057944</v>
+        <v>-0.03074254762907916</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.09117623973506245</v>
+        <v>0.1105888121836512</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.06735060286635219</v>
+        <v>0.06765800229097831</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0.09082482076844595</v>
+        <v>-0.08838657961624677</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.03630756175922136</v>
+        <v>0.1614136135186657</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.1328570560334042</v>
+        <v>0.1177279562826777</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.0364422421236778</v>
+        <v>0.03987860464449715</v>
       </c>
     </row>
     <row r="16">
@@ -2321,118 +2321,118 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02781912045315838</v>
+        <v>0.006611582905645562</v>
       </c>
       <c r="C16" t="n">
-        <v>0.002698547294766297</v>
+        <v>0.004060620121186458</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02352945977916111</v>
+        <v>0.001623884599273957</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.05210395222110989</v>
+        <v>-0.06286653421445899</v>
       </c>
       <c r="F16" t="n">
-        <v>0.09838922699319871</v>
+        <v>0.1106698430544161</v>
       </c>
       <c r="G16" t="n">
-        <v>0.03916078392112351</v>
+        <v>0.05057637294087458</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01196369489792203</v>
+        <v>-0.0120949723752487</v>
       </c>
       <c r="I16" t="n">
-        <v>0.03904611743900277</v>
+        <v>-0.1345589332218204</v>
       </c>
       <c r="J16" t="n">
-        <v>0.05056684726522011</v>
+        <v>0.05863671137011208</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.005207950996764357</v>
+        <v>0.004446979543487518</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1193935685433825</v>
+        <v>-0.2220675150573169</v>
       </c>
       <c r="M16" t="n">
-        <v>0.04242800792153292</v>
+        <v>0.03756643658106745</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.05621013966283236</v>
+        <v>0.02823435888770986</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4367175439856157</v>
+        <v>0.3054315381328672</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1031196932621134</v>
+        <v>0.1262961197874888</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.0909430531783029</v>
+        <v>-0.1284943000909214</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1080342902709622</v>
+        <v>-0.1330096056883042</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.08313639898439228</v>
+        <v>-0.03220867515488822</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1402418085586185</v>
+        <v>0.03839066049388265</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04921307264606269</v>
+        <v>0.04998654145890091</v>
       </c>
       <c r="W16" t="n">
-        <v>0.03829571541010627</v>
+        <v>0.01989993315831153</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.04478243784183392</v>
+        <v>-0.1204580244850225</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.03035908832045084</v>
+        <v>-0.04282794630938499</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.02247587791469958</v>
+        <v>0.01375282839248555</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.02418898547761623</v>
+        <v>-0.0728262318041554</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.07681277742792297</v>
+        <v>0.1089686720507212</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.06321465092938036</v>
+        <v>-0.01563214231879743</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.02309346244203659</v>
+        <v>0.02234421664760864</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.02598746296277693</v>
+        <v>0.0227034588132153</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.1117745860821232</v>
+        <v>-0.1909359381735785</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.02057670768560088</v>
+        <v>-0.05604134921498066</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.1311760302983295</v>
+        <v>0.06253686917187083</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.08954226173832408</v>
+        <v>0.09963274822586074</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.01653791108975803</v>
+        <v>0.005352215309613654</v>
       </c>
       <c r="AK16" t="n">
-        <v>-0.1729123751795936</v>
+        <v>-0.1156245413286303</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.08984920435561854</v>
+        <v>0.07423800517902247</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.06560257166452294</v>
+        <v>0.04572139647582533</v>
       </c>
     </row>
     <row r="17">
@@ -2442,118 +2442,118 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.02283502544625617</v>
+        <v>-0.0726758681161495</v>
       </c>
       <c r="C17" t="n">
-        <v>0.143028057646777</v>
+        <v>0.2580079271563647</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1772591976667311</v>
+        <v>0.1144643612995026</v>
       </c>
       <c r="E17" t="n">
-        <v>0.05608662768726733</v>
+        <v>0.03821350844527899</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3697675490419548</v>
+        <v>-0.1561088192130219</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.008086536865547741</v>
+        <v>0.04036719094913472</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3085856379458771</v>
+        <v>-0.5747760637043353</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.03937386683080294</v>
+        <v>-0.05229438754479994</v>
       </c>
       <c r="J17" t="n">
-        <v>0.113781346640297</v>
+        <v>0.1400378816602204</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4592727459815287</v>
+        <v>-0.2991325931333052</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1849651103532243</v>
+        <v>-0.2037544230648809</v>
       </c>
       <c r="M17" t="n">
-        <v>0.09167053116210271</v>
+        <v>0.1278399363458385</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1228720013589826</v>
+        <v>-0.02521614682322305</v>
       </c>
       <c r="O17" t="n">
-        <v>0.03319611958242574</v>
+        <v>0.1614136135186657</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1031196932621134</v>
+        <v>0.1262961197874888</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.09724539673664948</v>
+        <v>-0.4810609173487458</v>
       </c>
       <c r="S17" t="n">
-        <v>0.003292363673661721</v>
+        <v>-0.5145371272547211</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.04942778977759361</v>
+        <v>-0.2954803325121165</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2704678156406798</v>
+        <v>0.03187615956331746</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1210352927727268</v>
+        <v>0.1675943591681757</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.124071186217563</v>
+        <v>-0.04669877587856207</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1902589323580027</v>
+        <v>-0.2357219470128521</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.155352013949859</v>
+        <v>-0.6197758530605817</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.04234622928629908</v>
+        <v>-0.11887710948871</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.07814751335056276</v>
+        <v>-0.1258712163419846</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.2657731674957998</v>
+        <v>0.2914051727233095</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.287529181077385</v>
+        <v>-0.3595036118574367</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.07271846158760008</v>
+        <v>-0.02663824391335205</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.1181139162182397</v>
+        <v>-0.1725519960082395</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.01153021269081836</v>
+        <v>0.06704855380713223</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.08503031722204345</v>
+        <v>0.006808186336081163</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.0731007475613598</v>
+        <v>0.08139255210818223</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.1723337734295052</v>
+        <v>0.1257749295421985</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0.07149311666886458</v>
+        <v>-0.1418405636559324</v>
       </c>
       <c r="AK17" t="n">
-        <v>-0.2737198565370546</v>
+        <v>-0.06053690718227459</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.04801467153188296</v>
+        <v>0.02975066125774279</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0.05921562488546625</v>
+        <v>0.01139611505143039</v>
       </c>
     </row>
     <row r="18">
@@ -2563,118 +2563,118 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.09373332085645929</v>
+        <v>0.09613146515819812</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.142537494472403</v>
+        <v>-0.1272598125253477</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00386801670923928</v>
+        <v>0.01912772961658323</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0172031392190454</v>
+        <v>0.01758980418763172</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1216414746635736</v>
+        <v>-0.1036057698539964</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.05582909029710705</v>
+        <v>-0.07108895076072222</v>
       </c>
       <c r="H18" t="n">
-        <v>0.29784416485028</v>
+        <v>0.299799493158914</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0829750981768265</v>
+        <v>0.07623389954291393</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.05729247253711287</v>
+        <v>-0.03861396167681506</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0342657706664489</v>
+        <v>-0.02006257852707587</v>
       </c>
       <c r="L18" t="n">
-        <v>0.09757091954247528</v>
+        <v>0.1332712177928847</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1558552651534492</v>
+        <v>-0.1258283963184078</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1134978182015774</v>
+        <v>-0.08395728887688214</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1766040614371755</v>
+        <v>-0.163425882888857</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.0909430531783029</v>
+        <v>-0.1284943000909214</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.09724539673664948</v>
+        <v>-0.4810609173487458</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8171310289579209</v>
+        <v>0.7932986099995417</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3981581527183871</v>
+        <v>-0.08024219574239706</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6022936059421328</v>
+        <v>0.165259272219616</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.137272525903153</v>
+        <v>-0.1433657941194089</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.01357803827106311</v>
+        <v>-0.01017142740429909</v>
       </c>
       <c r="X18" t="n">
-        <v>0.2181352458137828</v>
+        <v>0.2255887910132671</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.4560184558591066</v>
+        <v>0.4403196902462133</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.1808810703082079</v>
+        <v>0.1668272407359127</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.1576990375755911</v>
+        <v>0.1594393748425492</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.0889701787765452</v>
+        <v>-0.1059925914390361</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.2497508487635679</v>
+        <v>0.1865496056558602</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.08467550162215345</v>
+        <v>0.06208763907039853</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.1226495792497489</v>
+        <v>0.1105718891229198</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.08341003307023297</v>
+        <v>0.07037637072552237</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.01639237632889547</v>
+        <v>0.05557218930384546</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.001877224387934411</v>
+        <v>0.01346432751608314</v>
       </c>
       <c r="AI18" t="n">
-        <v>-0.0937725174513806</v>
+        <v>-0.1165513071808118</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.1560918975586815</v>
+        <v>0.1409744544663763</v>
       </c>
       <c r="AK18" t="n">
-        <v>-0.07712409568247811</v>
+        <v>-0.09752352145671984</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.01482333250957654</v>
+        <v>-0.003775362655905516</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0.09227270806344895</v>
+        <v>-0.07935022954746014</v>
       </c>
     </row>
     <row r="19">
@@ -2684,118 +2684,118 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1115595621038911</v>
+        <v>0.1085354535738797</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.2007287471480622</v>
+        <v>-0.1782534741493452</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01537649932899007</v>
+        <v>0.02809405190301223</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02818127808720527</v>
+        <v>0.02160563950877607</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1547206862155288</v>
+        <v>-0.134800668233367</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.05263035294845073</v>
+        <v>-0.0716163267228199</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2242098501533842</v>
+        <v>0.2073694991195718</v>
       </c>
       <c r="I19" t="n">
-        <v>0.08981647732583906</v>
+        <v>0.09872356641761418</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.05650398729342467</v>
+        <v>-0.03240110425051796</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.08794470942920307</v>
+        <v>-0.06992213764196778</v>
       </c>
       <c r="L19" t="n">
-        <v>0.100240797581537</v>
+        <v>0.137715457145394</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1024413431323417</v>
+        <v>-0.0765840584732477</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.129424393090303</v>
+        <v>-0.1154348266372058</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2214678411983576</v>
+        <v>-0.2059853270402139</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1080342902709622</v>
+        <v>-0.1330096056883042</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.003292363673661721</v>
+        <v>-0.5145371272547211</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8171310289579209</v>
+        <v>0.7932986099995417</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7018407952774988</v>
+        <v>0.3507371540829122</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5441526245972113</v>
+        <v>0.1585713256320133</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1518666220782244</v>
+        <v>-0.1482637399987542</v>
       </c>
       <c r="W19" t="n">
-        <v>0.01242158903058095</v>
+        <v>0.01963324854780769</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1836519705986888</v>
+        <v>0.2029139461754157</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.4992524952542949</v>
+        <v>0.4660890900920631</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.1621175235365684</v>
+        <v>0.1421572305021455</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.1228054286335495</v>
+        <v>0.1202452539934454</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.1032140247012125</v>
+        <v>-0.1195180406656834</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.2669872390626319</v>
+        <v>0.2004367853862505</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.1103506734093615</v>
+        <v>0.09422584266241835</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.2099900045568824</v>
+        <v>0.197344290522715</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.06899658630311134</v>
+        <v>0.07986614034680996</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.002067146615908513</v>
+        <v>0.03750523279533142</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.008925888860914893</v>
+        <v>0.03174918457203308</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.0716573430255163</v>
+        <v>-0.08242151664333695</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.2079140640981204</v>
+        <v>0.18890226327545</v>
       </c>
       <c r="AK19" t="n">
-        <v>-0.07030634670141503</v>
+        <v>-0.1196862608667493</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0.00430818422993476</v>
+        <v>0.01915075203868699</v>
       </c>
       <c r="AM19" t="n">
-        <v>-0.1201712782548971</v>
+        <v>-0.08910589315564565</v>
       </c>
     </row>
     <row r="20">
@@ -2805,118 +2805,118 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1088865201705398</v>
+        <v>0.08335664681153869</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.2053999318983533</v>
+        <v>-0.1452275104984067</v>
       </c>
       <c r="D20" t="n">
-        <v>0.01467616265921041</v>
+        <v>0.001525233990799146</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0214791314896809</v>
+        <v>-0.007839355576798752</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1462649603350751</v>
+        <v>-0.02946003691012613</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.02213916173445776</v>
+        <v>-0.01148823867608542</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1911599013687688</v>
+        <v>-0.01238302761558865</v>
       </c>
       <c r="I20" t="n">
-        <v>0.07461173815021643</v>
+        <v>0.007307391974001648</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.07364922870788</v>
+        <v>-0.01322008910615778</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.08843311826960809</v>
+        <v>-0.03237988433494737</v>
       </c>
       <c r="L20" t="n">
-        <v>0.07930358555136487</v>
+        <v>0.02844001274661359</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.06339282214547495</v>
+        <v>-0.00419968170459278</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.09534171162795711</v>
+        <v>-0.04914692243181745</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2181229464451943</v>
+        <v>-0.08664263684430294</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.08313639898439228</v>
+        <v>-0.03220867515488822</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.04942778977759361</v>
+        <v>-0.2954803325121165</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3981581527183871</v>
+        <v>-0.08024219574239706</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7018407952774988</v>
+        <v>0.3507371540829122</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4681149572683444</v>
+        <v>-0.06540218017805718</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1027832153627894</v>
+        <v>-0.05989383860215906</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.03238547824092906</v>
+        <v>0.0441852034882087</v>
       </c>
       <c r="X20" t="n">
-        <v>0.1161125046832458</v>
+        <v>0.04375774413813528</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.4398256103095795</v>
+        <v>0.1869031057381521</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.1013364382837299</v>
+        <v>0.05278745284719726</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.08365000727700264</v>
+        <v>0.005174222632728991</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.1194725852824816</v>
+        <v>-0.08098946226074288</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.2360265774148869</v>
+        <v>0.0973556735940438</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.1130688738372151</v>
+        <v>0.04868289417135598</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.2052577627988174</v>
+        <v>0.1704715329359974</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.05955838532521428</v>
+        <v>0.005320763281059321</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.009488071578062664</v>
+        <v>0.008901177195220522</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.004643772790877314</v>
+        <v>0.004539072906233244</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.01546335272816284</v>
+        <v>0.04802358655719308</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.1707350879842381</v>
+        <v>0.1538922148310312</v>
       </c>
       <c r="AK20" t="n">
-        <v>-0.05790497859738603</v>
+        <v>-0.02266485559482928</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.0336176380878981</v>
+        <v>0.01131706273348498</v>
       </c>
       <c r="AM20" t="n">
-        <v>-0.0944442778409173</v>
+        <v>-0.01419843883629691</v>
       </c>
     </row>
     <row r="21">
@@ -2926,118 +2926,118 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1327240389581617</v>
+        <v>0.06403214902062797</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.07482035525590021</v>
+        <v>0.01584632963403111</v>
       </c>
       <c r="D21" t="n">
-        <v>0.08818496857142781</v>
+        <v>0.01177281589768749</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05929950995374642</v>
+        <v>-0.02430360961017555</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2683107582597542</v>
+        <v>0.05734165369372754</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0697871401667018</v>
+        <v>-0.006611724227291254</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2286117397162896</v>
+        <v>0.0987721715159882</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1153019899707529</v>
+        <v>0.02444231200951125</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.07401030496073775</v>
+        <v>0.01631091114606687</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1941317933539919</v>
+        <v>0.07045211108745553</v>
       </c>
       <c r="L21" t="n">
-        <v>0.08882355842397915</v>
+        <v>0.05421645881420206</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1176529602519697</v>
+        <v>-0.04109016329439494</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1961509848795527</v>
+        <v>-0.04657503310025886</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2627367986766575</v>
+        <v>0.03359840536658078</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1402418085586185</v>
+        <v>0.03839066049388265</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.2704678156406798</v>
+        <v>0.03187615956331746</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6022936059421328</v>
+        <v>0.165259272219616</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5441526245972113</v>
+        <v>0.1585713256320133</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4681149572683444</v>
+        <v>-0.06540218017805718</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1550705431084468</v>
+        <v>-0.1045153167353654</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.1072016358477312</v>
+        <v>0.02313342899407405</v>
       </c>
       <c r="X21" t="n">
-        <v>0.08680603750002784</v>
+        <v>0.04974087321169957</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.3570625110593781</v>
+        <v>0.03962819407428563</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.02788149920988271</v>
+        <v>0.06215113969231604</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.09186406302566945</v>
+        <v>0.05431245534464492</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.1032311028845723</v>
+        <v>-0.05515842740483892</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.1565989485702848</v>
+        <v>0.1328011777631433</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.1478330263804629</v>
+        <v>0.07636591520341662</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.07764300526176507</v>
+        <v>0.08283063184601662</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.1384638544652446</v>
+        <v>0.009906420708498568</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.006170876950018297</v>
+        <v>0.0435819018409121</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.004782916242430454</v>
+        <v>0.04409029926723178</v>
       </c>
       <c r="AI21" t="n">
-        <v>-0.03239079750678218</v>
+        <v>-0.06134381435307598</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.09338800585643421</v>
+        <v>0.02335872046994559</v>
       </c>
       <c r="AK21" t="n">
-        <v>-0.1117575912029964</v>
+        <v>0.02499257582493832</v>
       </c>
       <c r="AL21" t="n">
-        <v>-0.03688661356033774</v>
+        <v>0.04794838272220092</v>
       </c>
       <c r="AM21" t="n">
-        <v>-0.1207906220624961</v>
+        <v>-0.01254719346114898</v>
       </c>
     </row>
     <row r="22">
@@ -3047,118 +3047,118 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1166667338227477</v>
+        <v>-0.1161754311025996</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.02168714376365774</v>
+        <v>-0.02545727048511588</v>
       </c>
       <c r="D22" t="n">
-        <v>0.02386939372158895</v>
+        <v>0.02549045261313348</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0293521286412921</v>
+        <v>-0.02446309284812376</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.01131855634550556</v>
+        <v>-0.0296046945812596</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02995739212893643</v>
+        <v>0.03383924880863003</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.07562405126357916</v>
+        <v>-0.08488752040746821</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1732314704133533</v>
+        <v>-0.1084970877830468</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.03957853342849704</v>
+        <v>-0.0307279899755764</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0392265915321642</v>
+        <v>-0.06398921929979283</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1465269211300922</v>
+        <v>-0.153309241860334</v>
       </c>
       <c r="M22" t="n">
-        <v>0.05427806986755476</v>
+        <v>0.04825586386953187</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1053424912644674</v>
+        <v>0.06724854529454637</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2389615627654906</v>
+        <v>0.2073913853768473</v>
       </c>
       <c r="P22" t="n">
-        <v>0.04921307264606269</v>
+        <v>0.04998654145890091</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1210352927727268</v>
+        <v>0.1675943591681757</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.137272525903153</v>
+        <v>-0.1433657941194089</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1518666220782244</v>
+        <v>-0.1482637399987542</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1027832153627894</v>
+        <v>-0.05989383860215906</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1550705431084468</v>
+        <v>-0.1045153167353654</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>0.009331755783753979</v>
+        <v>-0.01263056498890736</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1202135231138383</v>
+        <v>-0.1396298577042195</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.1016683851066388</v>
+        <v>-0.1278618265713624</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.112430145618894</v>
+        <v>-0.09966302165058569</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.1032404540521789</v>
+        <v>-0.1123395752921952</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.06450288380053396</v>
+        <v>0.06579781736839468</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.1420913441373082</v>
+        <v>-0.1562526303629606</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.01148419219441201</v>
+        <v>0.01477496358080518</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.08856486263781818</v>
+        <v>-0.08694930207535373</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.03175361198294637</v>
+        <v>0.0582927678769526</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.01548383963097367</v>
+        <v>-0.04760456661089639</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.06406564211229447</v>
+        <v>0.06687520528944713</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.0584740130158167</v>
+        <v>0.06069985519034429</v>
       </c>
       <c r="AJ22" t="n">
-        <v>-0.1381227751095845</v>
+        <v>-0.1133370470009298</v>
       </c>
       <c r="AK22" t="n">
-        <v>-0.03140179993924808</v>
+        <v>0.01408931292942522</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.008589749695373374</v>
+        <v>-0.03833885429104597</v>
       </c>
       <c r="AM22" t="n">
-        <v>-0.03466037578468611</v>
+        <v>-0.02420958839001201</v>
       </c>
     </row>
     <row r="23">
@@ -3168,118 +3168,118 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.007133991226581892</v>
+        <v>0.04335795594139932</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.1018875163575239</v>
+        <v>-0.06846933207227221</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.07343917412845845</v>
+        <v>-0.07576171853287501</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.02348276053823919</v>
+        <v>-0.03053474560726398</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2141704782200169</v>
+        <v>0.1922829914499318</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01198449508643029</v>
+        <v>0.0115914103572963</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1179367828642263</v>
+        <v>0.09194464832272316</v>
       </c>
       <c r="I23" t="n">
-        <v>0.02956832568694377</v>
+        <v>0.02033228354191519</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.02124038645504387</v>
+        <v>-0.00135052281934775</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2256410048462239</v>
+        <v>0.2190077770598675</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02409834409745392</v>
+        <v>0.05376102431534226</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1199230980476398</v>
+        <v>0.08274820643481702</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1948520292257991</v>
+        <v>0.1423643749912813</v>
       </c>
       <c r="O23" t="n">
-        <v>0.05543274574799884</v>
+        <v>0.0007256260691689213</v>
       </c>
       <c r="P23" t="n">
-        <v>0.03829571541010627</v>
+        <v>0.01989993315831153</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.124071186217563</v>
+        <v>-0.04669877587856207</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.01357803827106311</v>
+        <v>-0.01017142740429909</v>
       </c>
       <c r="S23" t="n">
-        <v>0.01242158903058095</v>
+        <v>0.01963324854780769</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.03238547824092906</v>
+        <v>0.0441852034882087</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1072016358477312</v>
+        <v>0.02313342899407405</v>
       </c>
       <c r="V23" t="n">
-        <v>0.009331755783753979</v>
+        <v>-0.01263056498890736</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>0.04733102312672825</v>
+        <v>0.08464719765421742</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.01570847387257455</v>
+        <v>0.02532182392046311</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.1017156805431056</v>
+        <v>0.1186807899620888</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.01091722212456692</v>
+        <v>0.05254946740481271</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.01476055156627263</v>
+        <v>-0.03348149947799706</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.08048739773288299</v>
+        <v>0.1401646278539037</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.08128279859522436</v>
+        <v>-0.05772110038996672</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.1326535509009975</v>
+        <v>0.1717556784375831</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0.1505331416096787</v>
+        <v>-0.106823273063822</v>
       </c>
       <c r="AG23" t="n">
-        <v>-0.1763849275930112</v>
+        <v>-0.182694486661743</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.08799495546515586</v>
+        <v>-0.1050692597441514</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.05494634526497122</v>
+        <v>-0.04936596969589684</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.09745564086479368</v>
+        <v>0.1161203218772501</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.05160164261045685</v>
+        <v>0.1552675035556252</v>
       </c>
       <c r="AL23" t="n">
-        <v>-0.03945118395865131</v>
+        <v>-0.06671001858465236</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.05743700788546895</v>
+        <v>0.05631938963740523</v>
       </c>
     </row>
     <row r="24">
@@ -3289,118 +3289,118 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.01159709222273092</v>
+        <v>0.02743076083534806</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.07258700476579903</v>
+        <v>-0.05637427865429282</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0317414117742708</v>
+        <v>-0.0207061618020149</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02235593954320466</v>
+        <v>0.01423361992531246</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1848759945627597</v>
+        <v>0.1481174892059698</v>
       </c>
       <c r="G24" t="n">
-        <v>0.007137939687145619</v>
+        <v>0.0002682532067612749</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2205190754324522</v>
+        <v>0.2044465444928462</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1335841781562723</v>
+        <v>0.2317095409306767</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1565593496771505</v>
+        <v>0.1753551009756561</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5125796464254878</v>
+        <v>0.5121174659761561</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2586789267292378</v>
+        <v>0.3345847341323175</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.05431005658088087</v>
+        <v>-0.05323445447963348</v>
       </c>
       <c r="N24" t="n">
-        <v>0.06764489181216547</v>
+        <v>0.01250604383410962</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.08226397361485951</v>
+        <v>-0.0985113970796701</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.04478243784183392</v>
+        <v>-0.1204580244850225</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.1902589323580027</v>
+        <v>-0.2357219470128521</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2181352458137828</v>
+        <v>0.2255887910132671</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1836519705986888</v>
+        <v>0.2029139461754157</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1161125046832458</v>
+        <v>0.04375774413813528</v>
       </c>
       <c r="U24" t="n">
-        <v>0.08680603750002784</v>
+        <v>0.04974087321169957</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1202135231138383</v>
+        <v>-0.1396298577042195</v>
       </c>
       <c r="W24" t="n">
-        <v>0.04733102312672825</v>
+        <v>0.08464719765421742</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.1776945823353726</v>
+        <v>0.1888189196853977</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.1718904587610018</v>
+        <v>0.1614392045820586</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.2111409655558725</v>
+        <v>0.2821889701245853</v>
       </c>
       <c r="AB24" t="n">
-        <v>-0.3065782778365298</v>
+        <v>-0.2894239393268243</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.2586273185834694</v>
+        <v>0.2428228661957113</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.009275368718551235</v>
+        <v>0.00468980594221941</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.1411850416595193</v>
+        <v>0.1705740288905822</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.05082267014197236</v>
+        <v>0.01247559343044024</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.07193055171318515</v>
+        <v>0.07207627291394522</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.0202400452520998</v>
+        <v>0.02483183404841733</v>
       </c>
       <c r="AI24" t="n">
-        <v>-0.1257158992499894</v>
+        <v>-0.1692454369401523</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.1311917885649831</v>
+        <v>0.1393683530151411</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.06023483047205125</v>
+        <v>0.08401198414727033</v>
       </c>
       <c r="AL24" t="n">
-        <v>-0.0154444413432885</v>
+        <v>0.002245807558204633</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.04288568974563574</v>
+        <v>0.03408872175788728</v>
       </c>
     </row>
     <row r="25">
@@ -3410,118 +3410,118 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.05547784873328553</v>
+        <v>0.07691086095090374</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1789914924324122</v>
+        <v>-0.2218908228203615</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.02914510365667243</v>
+        <v>-0.04296555172101447</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0190724348429142</v>
+        <v>-0.04463831446220175</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1258623163043516</v>
+        <v>-0.04762607025480222</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.05771359079438979</v>
+        <v>-0.07139800548439802</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2211258560479276</v>
+        <v>0.3278842704773186</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1817821800479984</v>
+        <v>0.09552973575374833</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.08435869091922807</v>
+        <v>-0.04979208040739266</v>
       </c>
       <c r="K25" t="n">
-        <v>0.007980803355422528</v>
+        <v>0.1093155754376719</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1872976754025887</v>
+        <v>0.167767556531489</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.09869731977897006</v>
+        <v>-0.08048445955910374</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1430907389358226</v>
+        <v>-0.06154598321558994</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.1473555707181819</v>
+        <v>-0.1509933825754785</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.03035908832045084</v>
+        <v>-0.04282794630938499</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.155352013949859</v>
+        <v>-0.6197758530605817</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4560184558591066</v>
+        <v>0.4403196902462133</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4992524952542949</v>
+        <v>0.4660890900920631</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4398256103095795</v>
+        <v>0.1869031057381521</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3570625110593781</v>
+        <v>0.03962819407428563</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1016683851066388</v>
+        <v>-0.1278618265713624</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.01570847387257455</v>
+        <v>0.02532182392046311</v>
       </c>
       <c r="X25" t="n">
-        <v>0.1776945823353726</v>
+        <v>0.1888189196853977</v>
       </c>
       <c r="Y25" t="n">
         <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.1232260080208425</v>
+        <v>0.1382949766384594</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.1718979810323338</v>
+        <v>0.1337101859644265</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0.2722855017777395</v>
+        <v>-0.2756461674541762</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.2203383839600365</v>
+        <v>0.2381386820194237</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.06768603331783173</v>
+        <v>0.04862617100258575</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.1609059724238873</v>
+        <v>0.1675284183579059</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.08551985450341877</v>
+        <v>-0.1265148475418092</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.01472743076138192</v>
+        <v>0.01387784130945478</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.1489531295353475</v>
+        <v>0.09904479195052246</v>
       </c>
       <c r="AI25" t="n">
-        <v>-0.02559729979924891</v>
+        <v>-0.06287078499266356</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.1077660316141049</v>
+        <v>0.1292543701763148</v>
       </c>
       <c r="AK25" t="n">
-        <v>-0.07050299248843558</v>
+        <v>-0.2052387484364861</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.008367212640206316</v>
+        <v>0.01481275793674942</v>
       </c>
       <c r="AM25" t="n">
-        <v>-0.1110169822412851</v>
+        <v>-0.08814755491224889</v>
       </c>
     </row>
     <row r="26">
@@ -3531,118 +3531,118 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.04198304653301659</v>
+        <v>-0.00516984602510667</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0003435624366104266</v>
+        <v>0.009193074103452315</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03212022651322469</v>
+        <v>-0.03997009012762456</v>
       </c>
       <c r="E26" t="n">
-        <v>0.003213128002482984</v>
+        <v>-0.02492956399870845</v>
       </c>
       <c r="F26" t="n">
-        <v>0.145392861228714</v>
+        <v>0.123219146318828</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.03045141488433014</v>
+        <v>-0.04259179597633447</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1383157890585368</v>
+        <v>0.1128007836533903</v>
       </c>
       <c r="I26" t="n">
-        <v>0.08652543757085339</v>
+        <v>0.07357497000723452</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05462426531798821</v>
+        <v>0.1219948080944262</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1338783962646908</v>
+        <v>0.1436397159386585</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1100039671067572</v>
+        <v>0.09443220054879853</v>
       </c>
       <c r="M26" t="n">
-        <v>0.004476247724968099</v>
+        <v>-0.002104070175083831</v>
       </c>
       <c r="N26" t="n">
-        <v>0.04889514688311423</v>
+        <v>0.05707298851726765</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.02914951831289996</v>
+        <v>-0.07459653367222162</v>
       </c>
       <c r="P26" t="n">
-        <v>0.02247587791469958</v>
+        <v>0.01375282839248555</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.04234622928629908</v>
+        <v>-0.11887710948871</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1808810703082079</v>
+        <v>0.1668272407359127</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1621175235365684</v>
+        <v>0.1421572305021455</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1013364382837299</v>
+        <v>0.05278745284719726</v>
       </c>
       <c r="U26" t="n">
-        <v>0.02788149920988271</v>
+        <v>0.06215113969231604</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.112430145618894</v>
+        <v>-0.09966302165058569</v>
       </c>
       <c r="W26" t="n">
-        <v>0.1017156805431056</v>
+        <v>0.1186807899620888</v>
       </c>
       <c r="X26" t="n">
-        <v>0.1718904587610018</v>
+        <v>0.1614392045820586</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.1232260080208425</v>
+        <v>0.1382949766384594</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.4232044727354066</v>
+        <v>0.4210146222685162</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.1254034493607886</v>
+        <v>-0.1174359645399637</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.2749925583666911</v>
+        <v>0.2795045218602972</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.0008441102064698741</v>
+        <v>-0.007266827425638252</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.1822675323165109</v>
+        <v>0.1761226966959629</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.011940414145192</v>
+        <v>-0.0522921367605467</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.02471492054491212</v>
+        <v>-0.02961704060989143</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.02311093948188197</v>
+        <v>-0.00838805465583046</v>
       </c>
       <c r="AI26" t="n">
-        <v>-0.03385509408385932</v>
+        <v>-0.0410190506543692</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.2984225767769396</v>
+        <v>0.2783037713890198</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.02680332647813333</v>
+        <v>0.004831115042512533</v>
       </c>
       <c r="AL26" t="n">
-        <v>-0.001318707098640264</v>
+        <v>-0.01986809171855179</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.02298395062106526</v>
+        <v>0.05457044928817863</v>
       </c>
     </row>
     <row r="27">
@@ -3652,118 +3652,118 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.04876424449888972</v>
+        <v>0.06591941177995644</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2983461426226515</v>
+        <v>0.336796275022256</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01385546075246977</v>
+        <v>0.02547584781604136</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0009886948036743936</v>
+        <v>-0.003906027338621654</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01422760400390717</v>
+        <v>-0.0283806042852627</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02460342921646849</v>
+        <v>0.004459347085231402</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1306519756686255</v>
+        <v>0.09190717078294861</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1019059998238823</v>
+        <v>0.199680494810203</v>
       </c>
       <c r="J27" t="n">
-        <v>0.05151304677661937</v>
+        <v>0.09273087914046169</v>
       </c>
       <c r="K27" t="n">
-        <v>0.130241444553234</v>
+        <v>0.1054889312571502</v>
       </c>
       <c r="L27" t="n">
-        <v>0.09732227491769339</v>
+        <v>0.198632534250445</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.04094374786868287</v>
+        <v>-0.03452366883273245</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.002966127450942359</v>
+        <v>-0.03783673237164049</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.08759634147277566</v>
+        <v>-0.06951713561401776</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.02418898547761623</v>
+        <v>-0.0728262318041554</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.07814751335056276</v>
+        <v>-0.1258712163419846</v>
       </c>
       <c r="R27" t="n">
-        <v>0.1576990375755911</v>
+        <v>0.1594393748425492</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1228054286335495</v>
+        <v>0.1202452539934454</v>
       </c>
       <c r="T27" t="n">
-        <v>0.08365000727700264</v>
+        <v>0.005174222632728991</v>
       </c>
       <c r="U27" t="n">
-        <v>0.09186406302566945</v>
+        <v>0.05431245534464492</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.1032404540521789</v>
+        <v>-0.1123395752921952</v>
       </c>
       <c r="W27" t="n">
-        <v>0.01091722212456692</v>
+        <v>0.05254946740481271</v>
       </c>
       <c r="X27" t="n">
-        <v>0.2111409655558725</v>
+        <v>0.2821889701245853</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.1718979810323338</v>
+        <v>0.1337101859644265</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.4232044727354066</v>
+        <v>0.4210146222685162</v>
       </c>
       <c r="AA27" t="n">
         <v>1</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.1692584381689046</v>
+        <v>-0.1627517824534519</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.2722297570344954</v>
+        <v>0.1807880034214155</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.1305317298126809</v>
+        <v>-0.09774888494456214</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.1645873716700928</v>
+        <v>0.1697302626698553</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.000626270855736329</v>
+        <v>0.09630486571032507</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.03726877476496396</v>
+        <v>0.02608933660120252</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.02917287716011005</v>
+        <v>0.003348463737515781</v>
       </c>
       <c r="AI27" t="n">
-        <v>-0.05162334312940458</v>
+        <v>-0.07882612437787029</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.150779985365596</v>
+        <v>0.1669357044389539</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.0466240469276788</v>
+        <v>0.01177142535445024</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.04196845334893702</v>
+        <v>0.04594528496591099</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.0411458088196802</v>
+        <v>0.05395999196570581</v>
       </c>
     </row>
     <row r="28">
@@ -3773,118 +3773,118 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.08086035571558764</v>
+        <v>0.06395916593038545</v>
       </c>
       <c r="C28" t="n">
-        <v>0.04860203217566524</v>
+        <v>0.07764393714667839</v>
       </c>
       <c r="D28" t="n">
-        <v>0.02833972317983941</v>
+        <v>0.02365505702770799</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08568014013553121</v>
+        <v>0.07887884871248191</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1809573883615606</v>
+        <v>-0.1258261360314079</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.05518059524224142</v>
+        <v>-0.0266252727592989</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2635633413353763</v>
+        <v>-0.2634306698931043</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1314685515638324</v>
+        <v>-0.1425186363913494</v>
       </c>
       <c r="J28" t="n">
-        <v>0.04130394740536714</v>
+        <v>0.03037675143640918</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.3625922373381958</v>
+        <v>-0.3455220371632705</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.2545166963230679</v>
+        <v>-0.262430125896178</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1134852568977098</v>
+        <v>0.09198366519674726</v>
       </c>
       <c r="N28" t="n">
-        <v>0.06342396042209118</v>
+        <v>0.04026969725567445</v>
       </c>
       <c r="O28" t="n">
-        <v>0.1347339858367184</v>
+        <v>0.1353875603390245</v>
       </c>
       <c r="P28" t="n">
-        <v>0.07681277742792297</v>
+        <v>0.1089686720507212</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.2657731674957998</v>
+        <v>0.2914051727233095</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.0889701787765452</v>
+        <v>-0.1059925914390361</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.1032140247012125</v>
+        <v>-0.1195180406656834</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.1194725852824816</v>
+        <v>-0.08098946226074288</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.1032311028845723</v>
+        <v>-0.05515842740483892</v>
       </c>
       <c r="V28" t="n">
-        <v>0.06450288380053396</v>
+        <v>0.06579781736839468</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.01476055156627263</v>
+        <v>-0.03348149947799706</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.3065782778365298</v>
+        <v>-0.2894239393268243</v>
       </c>
       <c r="Y28" t="n">
-        <v>-0.2722855017777395</v>
+        <v>-0.2756461674541762</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.1254034493607886</v>
+        <v>-0.1174359645399637</v>
       </c>
       <c r="AA28" t="n">
-        <v>-0.1692584381689046</v>
+        <v>-0.1627517824534519</v>
       </c>
       <c r="AB28" t="n">
         <v>1</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.1698091469110241</v>
+        <v>-0.0371511002258265</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.01181078829441359</v>
+        <v>-0.000603389821210706</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.02019555291253303</v>
+        <v>-0.01332326923409272</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.09726711808217317</v>
+        <v>-0.007317886759605085</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.05205295558952357</v>
+        <v>-0.06707775338052191</v>
       </c>
       <c r="AH28" t="n">
-        <v>-0.228735512323846</v>
+        <v>-0.1975312920349051</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.06438443538805516</v>
+        <v>0.07401979687732615</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-0.01078374339868272</v>
+        <v>-0.005355677601492692</v>
       </c>
       <c r="AK28" t="n">
-        <v>-0.03206847489636617</v>
+        <v>0.01649119132158247</v>
       </c>
       <c r="AL28" t="n">
-        <v>-0.07188612629757719</v>
+        <v>-0.08411941622961244</v>
       </c>
       <c r="AM28" t="n">
-        <v>-0.04453039166457341</v>
+        <v>-0.04513258315519091</v>
       </c>
     </row>
     <row r="29">
@@ -3894,118 +3894,118 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.01963721415421305</v>
+        <v>0.04343607775541357</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.07612100916365676</v>
+        <v>-0.0958136554101664</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.06766548818462662</v>
+        <v>-0.09591108231253311</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.05754606730910285</v>
+        <v>-0.09315770082509091</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2112915488638085</v>
+        <v>0.2852031045707436</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.08412534403458609</v>
+        <v>-0.06752619875881324</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3331668676946908</v>
+        <v>0.3280659043212374</v>
       </c>
       <c r="I29" t="n">
-        <v>0.02474026830718588</v>
+        <v>-0.008839303300320001</v>
       </c>
       <c r="J29" t="n">
-        <v>0.02431206048679479</v>
+        <v>0.04540133042782918</v>
       </c>
       <c r="K29" t="n">
-        <v>0.3398216854212531</v>
+        <v>0.4005548041603108</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1263317895101808</v>
+        <v>0.07021344641507432</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1273668191697876</v>
+        <v>-0.1164069740545392</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.001787650657604119</v>
+        <v>0.06413559029739187</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.008003149378581148</v>
+        <v>-0.06211550874624753</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.06321465092938036</v>
+        <v>-0.01563214231879743</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.287529181077385</v>
+        <v>-0.3595036118574367</v>
       </c>
       <c r="R29" t="n">
-        <v>0.2497508487635679</v>
+        <v>0.1865496056558602</v>
       </c>
       <c r="S29" t="n">
-        <v>0.2669872390626319</v>
+        <v>0.2004367853862505</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2360265774148869</v>
+        <v>0.0973556735940438</v>
       </c>
       <c r="U29" t="n">
-        <v>0.1565989485702848</v>
+        <v>0.1328011777631433</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.1420913441373082</v>
+        <v>-0.1562526303629606</v>
       </c>
       <c r="W29" t="n">
-        <v>0.08048739773288299</v>
+        <v>0.1401646278539037</v>
       </c>
       <c r="X29" t="n">
-        <v>0.2586273185834694</v>
+        <v>0.2428228661957113</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.2203383839600365</v>
+        <v>0.2381386820194237</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.2749925583666911</v>
+        <v>0.2795045218602972</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.2722297570344954</v>
+        <v>0.1807880034214155</v>
       </c>
       <c r="AB29" t="n">
-        <v>-0.1698091469110241</v>
+        <v>-0.0371511002258265</v>
       </c>
       <c r="AC29" t="n">
         <v>1</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.009735258065301672</v>
+        <v>-0.01383351685020588</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.2171687555490976</v>
+        <v>0.247945816737227</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.03846502869946892</v>
+        <v>-0.3224362900511968</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.100195159625834</v>
+        <v>-0.106731904717529</v>
       </c>
       <c r="AH29" t="n">
-        <v>-0.02743859429640343</v>
+        <v>-0.1187960071844147</v>
       </c>
       <c r="AI29" t="n">
-        <v>-0.1434685852042632</v>
+        <v>-0.1437277089040234</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.1824562901897168</v>
+        <v>0.21982443557404</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.1461400800882485</v>
+        <v>0.1034451967092695</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.03826403504689955</v>
+        <v>0.01856310268264218</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.02715984333781421</v>
+        <v>0.03948681695964336</v>
       </c>
     </row>
     <row r="30">
@@ -4015,118 +4015,118 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.03413257328241422</v>
+        <v>0.04351174223573295</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1809373139895543</v>
+        <v>-0.1531559221723365</v>
       </c>
       <c r="D30" t="n">
-        <v>0.005455005854045259</v>
+        <v>-0.00275150612978952</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.02169219716636224</v>
+        <v>-0.01084428440937876</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1138065280523517</v>
+        <v>-0.08711457705674198</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.05447715116824579</v>
+        <v>-0.03156906911896547</v>
       </c>
       <c r="H30" t="n">
-        <v>0.009893619104127692</v>
+        <v>0.006536185694891158</v>
       </c>
       <c r="I30" t="n">
-        <v>0.02842145461144661</v>
+        <v>0.02804296377479942</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.02371728529060209</v>
+        <v>-0.02335722849295793</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.1244799637763281</v>
+        <v>-0.09911824647973455</v>
       </c>
       <c r="L30" t="n">
-        <v>0.02811412236988389</v>
+        <v>0.02805925396012487</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.001922529043938902</v>
+        <v>-0.00307709536432054</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.084284410425547</v>
+        <v>-0.0785113947352353</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.06962114321668407</v>
+        <v>-0.05361160385572424</v>
       </c>
       <c r="P30" t="n">
-        <v>0.02309346244203659</v>
+        <v>0.02234421664760864</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.07271846158760008</v>
+        <v>-0.02663824391335205</v>
       </c>
       <c r="R30" t="n">
-        <v>0.08467550162215345</v>
+        <v>0.06208763907039853</v>
       </c>
       <c r="S30" t="n">
-        <v>0.1103506734093615</v>
+        <v>0.09422584266241835</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1130688738372151</v>
+        <v>0.04868289417135598</v>
       </c>
       <c r="U30" t="n">
-        <v>0.1478330263804629</v>
+        <v>0.07636591520341662</v>
       </c>
       <c r="V30" t="n">
-        <v>0.01148419219441201</v>
+        <v>0.01477496358080518</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.08128279859522436</v>
+        <v>-0.05772110038996672</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.009275368718551235</v>
+        <v>0.00468980594221941</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.06768603331783173</v>
+        <v>0.04862617100258575</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.0008441102064698741</v>
+        <v>-0.007266827425638252</v>
       </c>
       <c r="AA30" t="n">
-        <v>-0.1305317298126809</v>
+        <v>-0.09774888494456214</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.01181078829441359</v>
+        <v>-0.000603389821210706</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.009735258065301672</v>
+        <v>-0.01383351685020588</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.09064763087658405</v>
+        <v>0.08405076516250425</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.05734530250083441</v>
+        <v>-0.02299309530165522</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.02653594977184845</v>
+        <v>0.02854270336115018</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.04931321406824798</v>
+        <v>0.07058405982208475</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.08300093579337978</v>
+        <v>0.08212097102055843</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.006761051019426505</v>
+        <v>0.01759440767427094</v>
       </c>
       <c r="AK30" t="n">
-        <v>-0.08320731686207405</v>
+        <v>-0.122954021193424</v>
       </c>
       <c r="AL30" t="n">
-        <v>-0.04184125845058375</v>
+        <v>-0.01927207793431578</v>
       </c>
       <c r="AM30" t="n">
-        <v>-0.06147210330866285</v>
+        <v>-0.06142063364338014</v>
       </c>
     </row>
     <row r="31">
@@ -4136,118 +4136,118 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.05010503584552657</v>
+        <v>0.08727834421609863</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1453224209078465</v>
+        <v>-0.121910172489243</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.01239950109491967</v>
+        <v>-0.01455195335256021</v>
       </c>
       <c r="E31" t="n">
-        <v>0.031427238807974</v>
+        <v>0.03588596017311229</v>
       </c>
       <c r="F31" t="n">
-        <v>0.04720402906016524</v>
+        <v>0.06460503404016603</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.03293430484177805</v>
+        <v>-0.01527513187579614</v>
       </c>
       <c r="H31" t="n">
-        <v>0.09542397470336453</v>
+        <v>0.1124655427513775</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1078235817655234</v>
+        <v>0.1305976127520379</v>
       </c>
       <c r="J31" t="n">
-        <v>0.003073174055598994</v>
+        <v>0.01209374571465077</v>
       </c>
       <c r="K31" t="n">
-        <v>0.05967235476613516</v>
+        <v>0.1005443519951172</v>
       </c>
       <c r="L31" t="n">
-        <v>0.08106677851385956</v>
+        <v>0.1328396032260491</v>
       </c>
       <c r="M31" t="n">
-        <v>0.01701822399793934</v>
+        <v>0.03265692537516056</v>
       </c>
       <c r="N31" t="n">
-        <v>0.01656602158293573</v>
+        <v>0.03213977805668538</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.04512362270059302</v>
+        <v>-0.03670614796071862</v>
       </c>
       <c r="P31" t="n">
-        <v>0.02598746296277693</v>
+        <v>0.0227034588132153</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.1181139162182397</v>
+        <v>-0.1725519960082395</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1226495792497489</v>
+        <v>0.1105718891229198</v>
       </c>
       <c r="S31" t="n">
-        <v>0.2099900045568824</v>
+        <v>0.197344290522715</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2052577627988174</v>
+        <v>0.1704715329359974</v>
       </c>
       <c r="U31" t="n">
-        <v>0.07764300526176507</v>
+        <v>0.08283063184601662</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.08856486263781818</v>
+        <v>-0.08694930207535373</v>
       </c>
       <c r="W31" t="n">
-        <v>0.1326535509009975</v>
+        <v>0.1717556784375831</v>
       </c>
       <c r="X31" t="n">
-        <v>0.1411850416595193</v>
+        <v>0.1705740288905822</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.1609059724238873</v>
+        <v>0.1675284183579059</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.1822675323165109</v>
+        <v>0.1761226966959629</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.1645873716700928</v>
+        <v>0.1697302626698553</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.02019555291253303</v>
+        <v>-0.01332326923409272</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.2171687555490976</v>
+        <v>0.247945816737227</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.09064763087658405</v>
+        <v>0.08405076516250425</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.07521139663542452</v>
+        <v>-0.04937140741558395</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.1362682595670872</v>
+        <v>-0.09952228143997793</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.004281074827935901</v>
+        <v>0.0005717655094982244</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.1227387958225873</v>
+        <v>-0.105840627836392</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.3308638520901785</v>
+        <v>0.3561606166402851</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.05313019012491828</v>
+        <v>-0.001225121283936577</v>
       </c>
       <c r="AL31" t="n">
-        <v>-0.02131551747179619</v>
+        <v>-0.02524996387762798</v>
       </c>
       <c r="AM31" t="n">
-        <v>-0.01609719787912343</v>
+        <v>-0.004231438816541684</v>
       </c>
     </row>
     <row r="32">
@@ -4257,118 +4257,118 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.03905321747505927</v>
+        <v>-0.02031255225135883</v>
       </c>
       <c r="C32" t="n">
-        <v>0.07794497293544218</v>
+        <v>0.1564016723751438</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0205109406573495</v>
+        <v>0.1015838141185567</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.01126592095209387</v>
+        <v>0.09424224330222147</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.04881607246094686</v>
+        <v>-0.2809877914210465</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.01957614020841991</v>
+        <v>0.002516327957631364</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.06746940011580897</v>
+        <v>-0.190165662433137</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.001791826021911512</v>
+        <v>0.1374728952416535</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.009067123639468795</v>
+        <v>-0.01114251725317284</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.06106495705265275</v>
+        <v>-0.2886086323851482</v>
       </c>
       <c r="L32" t="n">
-        <v>0.08190963173462597</v>
+        <v>0.1749377444589405</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.04693125196985402</v>
+        <v>0.03606522044946776</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.1292330632252945</v>
+        <v>-0.1711676953858127</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.0929930944937133</v>
+        <v>0.0800453664614155</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.1117745860821232</v>
+        <v>-0.1909359381735785</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.01153021269081836</v>
+        <v>0.06704855380713223</v>
       </c>
       <c r="R32" t="n">
-        <v>0.08341003307023297</v>
+        <v>0.07037637072552237</v>
       </c>
       <c r="S32" t="n">
-        <v>0.06899658630311134</v>
+        <v>0.07986614034680996</v>
       </c>
       <c r="T32" t="n">
-        <v>0.05955838532521428</v>
+        <v>0.005320763281059321</v>
       </c>
       <c r="U32" t="n">
-        <v>0.1384638544652446</v>
+        <v>0.009906420708498568</v>
       </c>
       <c r="V32" t="n">
-        <v>0.03175361198294637</v>
+        <v>0.0582927678769526</v>
       </c>
       <c r="W32" t="n">
-        <v>-0.1505331416096787</v>
+        <v>-0.106823273063822</v>
       </c>
       <c r="X32" t="n">
-        <v>0.05082267014197236</v>
+        <v>0.01247559343044024</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.08551985450341877</v>
+        <v>-0.1265148475418092</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.011940414145192</v>
+        <v>-0.0522921367605467</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.000626270855736329</v>
+        <v>0.09630486571032507</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.09726711808217317</v>
+        <v>-0.007317886759605085</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.03846502869946892</v>
+        <v>-0.3224362900511968</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.05734530250083441</v>
+        <v>-0.02299309530165522</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.07521139663542452</v>
+        <v>-0.04937140741558395</v>
       </c>
       <c r="AF32" t="n">
         <v>1</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.5656066019972623</v>
+        <v>0.1737080669799149</v>
       </c>
       <c r="AH32" t="n">
-        <v>-0.002125639303751816</v>
+        <v>0.1403315801944311</v>
       </c>
       <c r="AI32" t="n">
-        <v>-0.02731187437055567</v>
+        <v>0.01117491479480457</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.00527661640501789</v>
+        <v>-0.0259925460690936</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.08386679951724943</v>
+        <v>0.2428768817859106</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.07737308647122249</v>
+        <v>0.02932280958967689</v>
       </c>
       <c r="AM32" t="n">
-        <v>-0.03893810004768056</v>
+        <v>0.05226552907284862</v>
       </c>
     </row>
     <row r="33">
@@ -4378,118 +4378,118 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.008465499285456039</v>
+        <v>0.009936171530269891</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02281569781239416</v>
+        <v>0.03019536798675048</v>
       </c>
       <c r="D33" t="n">
-        <v>0.02760907933986359</v>
+        <v>0.03142754912093982</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01427456914278958</v>
+        <v>0.02108010328987807</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.03069322229785222</v>
+        <v>-0.02043260750154726</v>
       </c>
       <c r="G33" t="n">
-        <v>0.01507679414233331</v>
+        <v>0.01525651252800324</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1134656158083502</v>
+        <v>-0.05442581933528388</v>
       </c>
       <c r="I33" t="n">
-        <v>0.01337733425229855</v>
+        <v>0.05276045372031026</v>
       </c>
       <c r="J33" t="n">
-        <v>0.004888161671559483</v>
+        <v>-0.02961178482574818</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.03449219263370141</v>
+        <v>-0.01902684162819378</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.00415276692903936</v>
+        <v>0.02127116322811755</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.02905902954884057</v>
+        <v>-0.02549776577030493</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.1413850866361684</v>
+        <v>-0.1242057202197978</v>
       </c>
       <c r="O33" t="n">
-        <v>0.01302939189057944</v>
+        <v>-0.03074254762907916</v>
       </c>
       <c r="P33" t="n">
-        <v>0.02057670768560088</v>
+        <v>-0.05604134921498066</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.08503031722204345</v>
+        <v>0.006808186336081163</v>
       </c>
       <c r="R33" t="n">
-        <v>0.01639237632889547</v>
+        <v>0.05557218930384546</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.002067146615908513</v>
+        <v>0.03750523279533142</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.009488071578062664</v>
+        <v>0.008901177195220522</v>
       </c>
       <c r="U33" t="n">
-        <v>0.006170876950018297</v>
+        <v>0.0435819018409121</v>
       </c>
       <c r="V33" t="n">
-        <v>0.01548383963097367</v>
+        <v>-0.04760456661089639</v>
       </c>
       <c r="W33" t="n">
-        <v>-0.1763849275930112</v>
+        <v>-0.182694486661743</v>
       </c>
       <c r="X33" t="n">
-        <v>0.07193055171318515</v>
+        <v>0.07207627291394522</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.01472743076138192</v>
+        <v>0.01387784130945478</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.02471492054491212</v>
+        <v>-0.02961704060989143</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.03726877476496396</v>
+        <v>0.02608933660120252</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.05205295558952357</v>
+        <v>-0.06707775338052191</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.100195159625834</v>
+        <v>-0.106731904717529</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.02653594977184845</v>
+        <v>0.02854270336115018</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.1362682595670872</v>
+        <v>-0.09952228143997793</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.5656066019972623</v>
+        <v>0.1737080669799149</v>
       </c>
       <c r="AG33" t="n">
         <v>1</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.1213020515726692</v>
+        <v>0.06892703351430983</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.07879144243330909</v>
+        <v>0.02662816986876121</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-0.09314230155300302</v>
+        <v>-0.09236125454223916</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.06209626182645942</v>
+        <v>-0.03673254023187976</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.2299191137310003</v>
+        <v>0.2350679324462549</v>
       </c>
       <c r="AM33" t="n">
-        <v>-0.01148040364927585</v>
+        <v>-0.02095105694814079</v>
       </c>
     </row>
     <row r="34">
@@ -4499,118 +4499,118 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.02660642310995417</v>
+        <v>-0.01557973530699345</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.07829998742629059</v>
+        <v>-0.05069201368705699</v>
       </c>
       <c r="D34" t="n">
-        <v>0.07389975312941718</v>
+        <v>0.109442256778459</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.07257974945751368</v>
+        <v>-0.04876196204867768</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.05032961222202263</v>
+        <v>-0.1241712451200391</v>
       </c>
       <c r="G34" t="n">
-        <v>0.06031564003378743</v>
+        <v>0.06420969514996855</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.0920811748756737</v>
+        <v>-0.1203378324896288</v>
       </c>
       <c r="I34" t="n">
-        <v>0.02168904689640586</v>
+        <v>0.0703119413668022</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.01629973017812746</v>
+        <v>-0.02504217273383481</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.1042297422424207</v>
+        <v>-0.1558810589898874</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.009259211382527015</v>
+        <v>0.03712125199121296</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0884110245886497</v>
+        <v>0.102427372763429</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.1505605063409815</v>
+        <v>-0.154403617876576</v>
       </c>
       <c r="O34" t="n">
-        <v>0.09117623973506245</v>
+        <v>0.1105888121836512</v>
       </c>
       <c r="P34" t="n">
-        <v>0.1311760302983295</v>
+        <v>0.06253686917187083</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.0731007475613598</v>
+        <v>0.08139255210818223</v>
       </c>
       <c r="R34" t="n">
-        <v>0.001877224387934411</v>
+        <v>0.01346432751608314</v>
       </c>
       <c r="S34" t="n">
-        <v>0.008925888860914893</v>
+        <v>0.03174918457203308</v>
       </c>
       <c r="T34" t="n">
-        <v>-0.004643772790877314</v>
+        <v>0.004539072906233244</v>
       </c>
       <c r="U34" t="n">
-        <v>-0.004782916242430454</v>
+        <v>0.04409029926723178</v>
       </c>
       <c r="V34" t="n">
-        <v>0.06406564211229447</v>
+        <v>0.06687520528944713</v>
       </c>
       <c r="W34" t="n">
-        <v>-0.08799495546515586</v>
+        <v>-0.1050692597441514</v>
       </c>
       <c r="X34" t="n">
-        <v>0.0202400452520998</v>
+        <v>0.02483183404841733</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.1489531295353475</v>
+        <v>0.09904479195052246</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.02311093948188197</v>
+        <v>-0.00838805465583046</v>
       </c>
       <c r="AA34" t="n">
-        <v>-0.02917287716011005</v>
+        <v>0.003348463737515781</v>
       </c>
       <c r="AB34" t="n">
-        <v>-0.228735512323846</v>
+        <v>-0.1975312920349051</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.02743859429640343</v>
+        <v>-0.1187960071844147</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.04931321406824798</v>
+        <v>0.07058405982208475</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.004281074827935901</v>
+        <v>0.0005717655094982244</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.002125639303751816</v>
+        <v>0.1403315801944311</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.1213020515726692</v>
+        <v>0.06892703351430983</v>
       </c>
       <c r="AH34" t="n">
         <v>1</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.1284506996040896</v>
+        <v>0.1297235323321908</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.01903425100941919</v>
+        <v>0.009869269489264714</v>
       </c>
       <c r="AK34" t="n">
-        <v>-0.1548592696232827</v>
+        <v>-0.2953029099565957</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.05440568318083076</v>
+        <v>0.07069885923522307</v>
       </c>
       <c r="AM34" t="n">
-        <v>-0.07857443134371904</v>
+        <v>-0.07076813412655004</v>
       </c>
     </row>
     <row r="35">
@@ -4620,118 +4620,118 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.02070778977938564</v>
+        <v>0.02248376290198343</v>
       </c>
       <c r="C35" t="n">
-        <v>0.02286278125906108</v>
+        <v>0.02531542127428177</v>
       </c>
       <c r="D35" t="n">
-        <v>0.08268452407301209</v>
+        <v>0.07091216352600369</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.0225806262958686</v>
+        <v>-0.02421338136450438</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.1247737087617955</v>
+        <v>-0.09466646578017396</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0223708674891002</v>
+        <v>0.007722041152113097</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.151371221076173</v>
+        <v>-0.1392493058251338</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.01383114541241584</v>
+        <v>-0.04604690155678313</v>
       </c>
       <c r="J35" t="n">
-        <v>0.03605121999259477</v>
+        <v>-0.003320340679930911</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.1850102522346893</v>
+        <v>-0.1966532787729737</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.1126512039312719</v>
+        <v>-0.1350750381760649</v>
       </c>
       <c r="M35" t="n">
-        <v>0.07187267454303473</v>
+        <v>0.07740411964590795</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.07676990751327779</v>
+        <v>-0.06028738530628312</v>
       </c>
       <c r="O35" t="n">
-        <v>0.06735060286635219</v>
+        <v>0.06765800229097831</v>
       </c>
       <c r="P35" t="n">
-        <v>0.08954226173832408</v>
+        <v>0.09963274822586074</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.1723337734295052</v>
+        <v>0.1257749295421985</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.0937725174513806</v>
+        <v>-0.1165513071808118</v>
       </c>
       <c r="S35" t="n">
-        <v>-0.0716573430255163</v>
+        <v>-0.08242151664333695</v>
       </c>
       <c r="T35" t="n">
-        <v>0.01546335272816284</v>
+        <v>0.04802358655719308</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.03239079750678218</v>
+        <v>-0.06134381435307598</v>
       </c>
       <c r="V35" t="n">
-        <v>0.0584740130158167</v>
+        <v>0.06069985519034429</v>
       </c>
       <c r="W35" t="n">
-        <v>-0.05494634526497122</v>
+        <v>-0.04936596969589684</v>
       </c>
       <c r="X35" t="n">
-        <v>-0.1257158992499894</v>
+        <v>-0.1692454369401523</v>
       </c>
       <c r="Y35" t="n">
-        <v>-0.02559729979924891</v>
+        <v>-0.06287078499266356</v>
       </c>
       <c r="Z35" t="n">
-        <v>-0.03385509408385932</v>
+        <v>-0.0410190506543692</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.05162334312940458</v>
+        <v>-0.07882612437787029</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.06438443538805516</v>
+        <v>0.07401979687732615</v>
       </c>
       <c r="AC35" t="n">
-        <v>-0.1434685852042632</v>
+        <v>-0.1437277089040234</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.08300093579337978</v>
+        <v>0.08212097102055843</v>
       </c>
       <c r="AE35" t="n">
-        <v>-0.1227387958225873</v>
+        <v>-0.105840627836392</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.02731187437055567</v>
+        <v>0.01117491479480457</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.07879144243330909</v>
+        <v>0.02662816986876121</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.1284506996040896</v>
+        <v>0.1297235323321908</v>
       </c>
       <c r="AI35" t="n">
         <v>1</v>
       </c>
       <c r="AJ35" t="n">
-        <v>-0.08626527531995123</v>
+        <v>-0.06229059382580943</v>
       </c>
       <c r="AK35" t="n">
-        <v>-0.1124133509236517</v>
+        <v>-0.09336192655872415</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.04050372650058295</v>
+        <v>0.03103768593000859</v>
       </c>
       <c r="AM35" t="n">
-        <v>-0.02733344394835103</v>
+        <v>-0.04003305270695982</v>
       </c>
     </row>
     <row r="36">
@@ -4741,118 +4741,118 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.06055183065567665</v>
+        <v>0.09313853133981533</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.04468516456514963</v>
+        <v>-0.04702960274841114</v>
       </c>
       <c r="D36" t="n">
-        <v>0.04113830011822168</v>
+        <v>0.04145736893493546</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.07076350084088558</v>
+        <v>-0.05659886028063899</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01205958210200804</v>
+        <v>0.001088144885599773</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.06386657037580507</v>
+        <v>-0.04285193184980705</v>
       </c>
       <c r="H36" t="n">
-        <v>0.04254251508171864</v>
+        <v>0.03912097008960316</v>
       </c>
       <c r="I36" t="n">
-        <v>0.05768907558258705</v>
+        <v>0.1128352462530348</v>
       </c>
       <c r="J36" t="n">
-        <v>0.03985109801639726</v>
+        <v>0.04380857502794992</v>
       </c>
       <c r="K36" t="n">
-        <v>0.006107822316626218</v>
+        <v>0.03061249721217357</v>
       </c>
       <c r="L36" t="n">
-        <v>0.06715208209719251</v>
+        <v>0.1285150003132419</v>
       </c>
       <c r="M36" t="n">
-        <v>0.04816148064538751</v>
+        <v>0.03921950257913655</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.00910270088149266</v>
+        <v>0.01131373754909017</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.09082482076844595</v>
+        <v>-0.08838657961624677</v>
       </c>
       <c r="P36" t="n">
-        <v>-0.01653791108975803</v>
+        <v>0.005352215309613654</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.07149311666886458</v>
+        <v>-0.1418405636559324</v>
       </c>
       <c r="R36" t="n">
-        <v>0.1560918975586815</v>
+        <v>0.1409744544663763</v>
       </c>
       <c r="S36" t="n">
-        <v>0.2079140640981204</v>
+        <v>0.18890226327545</v>
       </c>
       <c r="T36" t="n">
-        <v>0.1707350879842381</v>
+        <v>0.1538922148310312</v>
       </c>
       <c r="U36" t="n">
-        <v>0.09338800585643421</v>
+        <v>0.02335872046994559</v>
       </c>
       <c r="V36" t="n">
-        <v>-0.1381227751095845</v>
+        <v>-0.1133370470009298</v>
       </c>
       <c r="W36" t="n">
-        <v>0.09745564086479368</v>
+        <v>0.1161203218772501</v>
       </c>
       <c r="X36" t="n">
-        <v>0.1311917885649831</v>
+        <v>0.1393683530151411</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.1077660316141049</v>
+        <v>0.1292543701763148</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.2984225767769396</v>
+        <v>0.2783037713890198</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.150779985365596</v>
+        <v>0.1669357044389539</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.01078374339868272</v>
+        <v>-0.005355677601492692</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.1824562901897168</v>
+        <v>0.21982443557404</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.006761051019426505</v>
+        <v>0.01759440767427094</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.3308638520901785</v>
+        <v>0.3561606166402851</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.00527661640501789</v>
+        <v>-0.0259925460690936</v>
       </c>
       <c r="AG36" t="n">
-        <v>-0.09314230155300302</v>
+        <v>-0.09236125454223916</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.01903425100941919</v>
+        <v>0.009869269489264714</v>
       </c>
       <c r="AI36" t="n">
-        <v>-0.08626527531995123</v>
+        <v>-0.06229059382580943</v>
       </c>
       <c r="AJ36" t="n">
         <v>1</v>
       </c>
       <c r="AK36" t="n">
-        <v>-0.02645108826982346</v>
+        <v>-0.07207661785889515</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.02757115949809522</v>
+        <v>0.03061360632851289</v>
       </c>
       <c r="AM36" t="n">
-        <v>-0.009684040952457802</v>
+        <v>-0.005297148565513779</v>
       </c>
     </row>
     <row r="37">
@@ -4862,118 +4862,118 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.1199856792654779</v>
+        <v>-0.1932832690412749</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.04331934169259238</v>
+        <v>-0.03455516344636985</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.07258433773300187</v>
+        <v>-0.1201469003951805</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.03337615600880419</v>
+        <v>-0.004750214430648298</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2827652169448908</v>
+        <v>0.357193694517332</v>
       </c>
       <c r="G37" t="n">
-        <v>0.02619125271594785</v>
+        <v>0.0228640905639778</v>
       </c>
       <c r="H37" t="n">
-        <v>0.09687834182330435</v>
+        <v>0.1376772925775237</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.05982935279927063</v>
+        <v>-0.1087142311184365</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.05601339761222462</v>
+        <v>-0.0422713537798215</v>
       </c>
       <c r="K37" t="n">
-        <v>0.2903547206013168</v>
+        <v>0.3557231048932721</v>
       </c>
       <c r="L37" t="n">
-        <v>0.02010448954239287</v>
+        <v>-0.0003810795160044098</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.1000141145102716</v>
+        <v>-0.03614325861285465</v>
       </c>
       <c r="N37" t="n">
-        <v>0.1687884836597827</v>
+        <v>0.2260185669317089</v>
       </c>
       <c r="O37" t="n">
-        <v>0.03630756175922136</v>
+        <v>0.1614136135186657</v>
       </c>
       <c r="P37" t="n">
-        <v>-0.1729123751795936</v>
+        <v>-0.1156245413286303</v>
       </c>
       <c r="Q37" t="n">
-        <v>-0.2737198565370546</v>
+        <v>-0.06053690718227459</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.07712409568247811</v>
+        <v>-0.09752352145671984</v>
       </c>
       <c r="S37" t="n">
-        <v>-0.07030634670141503</v>
+        <v>-0.1196862608667493</v>
       </c>
       <c r="T37" t="n">
-        <v>-0.05790497859738603</v>
+        <v>-0.02266485559482928</v>
       </c>
       <c r="U37" t="n">
-        <v>-0.1117575912029964</v>
+        <v>0.02499257582493832</v>
       </c>
       <c r="V37" t="n">
-        <v>-0.03140179993924808</v>
+        <v>0.01408931292942522</v>
       </c>
       <c r="W37" t="n">
-        <v>0.05160164261045685</v>
+        <v>0.1552675035556252</v>
       </c>
       <c r="X37" t="n">
-        <v>0.06023483047205125</v>
+        <v>0.08401198414727033</v>
       </c>
       <c r="Y37" t="n">
-        <v>-0.07050299248843558</v>
+        <v>-0.2052387484364861</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.02680332647813333</v>
+        <v>0.004831115042512533</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.0466240469276788</v>
+        <v>0.01177142535445024</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.03206847489636617</v>
+        <v>0.01649119132158247</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.1461400800882485</v>
+        <v>0.1034451967092695</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.08320731686207405</v>
+        <v>-0.122954021193424</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.05313019012491828</v>
+        <v>-0.001225121283936577</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.08386679951724943</v>
+        <v>0.2428768817859106</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.06209626182645942</v>
+        <v>-0.03673254023187976</v>
       </c>
       <c r="AH37" t="n">
-        <v>-0.1548592696232827</v>
+        <v>-0.2953029099565957</v>
       </c>
       <c r="AI37" t="n">
-        <v>-0.1124133509236517</v>
+        <v>-0.09336192655872415</v>
       </c>
       <c r="AJ37" t="n">
-        <v>-0.02645108826982346</v>
+        <v>-0.07207661785889515</v>
       </c>
       <c r="AK37" t="n">
         <v>1</v>
       </c>
       <c r="AL37" t="n">
-        <v>-0.009724934215663361</v>
+        <v>-0.06948258108656435</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.08598707547789738</v>
+        <v>0.09663512782242119</v>
       </c>
     </row>
     <row r="38">
@@ -4983,118 +4983,118 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.04369434761947667</v>
+        <v>0.04991420707723565</v>
       </c>
       <c r="C38" t="n">
-        <v>0.02878162375726544</v>
+        <v>0.03582453827256738</v>
       </c>
       <c r="D38" t="n">
-        <v>0.01752410800053829</v>
+        <v>0.01739507195281018</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.01252691811916841</v>
+        <v>-0.0130962319225582</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.02016682154898497</v>
+        <v>-0.02850053632515961</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02474080071933559</v>
+        <v>0.03318385792398505</v>
       </c>
       <c r="H38" t="n">
-        <v>0.006979120211387076</v>
+        <v>0.02567084236753841</v>
       </c>
       <c r="I38" t="n">
-        <v>0.03231620516151021</v>
+        <v>0.06475014708383739</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.01838990425296168</v>
+        <v>-0.04571942718531442</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.006348383044623658</v>
+        <v>-0.002650952581590977</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.02358558055727042</v>
+        <v>0.01145480576553741</v>
       </c>
       <c r="M38" t="n">
-        <v>0.03938177142189196</v>
+        <v>0.03850841213680282</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.000682756027358706</v>
+        <v>-0.0279661825906723</v>
       </c>
       <c r="O38" t="n">
-        <v>0.1328570560334042</v>
+        <v>0.1177279562826777</v>
       </c>
       <c r="P38" t="n">
-        <v>0.08984920435561854</v>
+        <v>0.07423800517902247</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.04801467153188296</v>
+        <v>0.02975066125774279</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.01482333250957654</v>
+        <v>-0.003775362655905516</v>
       </c>
       <c r="S38" t="n">
-        <v>-0.00430818422993476</v>
+        <v>0.01915075203868699</v>
       </c>
       <c r="T38" t="n">
-        <v>-0.0336176380878981</v>
+        <v>0.01131706273348498</v>
       </c>
       <c r="U38" t="n">
-        <v>-0.03688661356033774</v>
+        <v>0.04794838272220092</v>
       </c>
       <c r="V38" t="n">
-        <v>0.008589749695373374</v>
+        <v>-0.03833885429104597</v>
       </c>
       <c r="W38" t="n">
-        <v>-0.03945118395865131</v>
+        <v>-0.06671001858465236</v>
       </c>
       <c r="X38" t="n">
-        <v>-0.0154444413432885</v>
+        <v>0.002245807558204633</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.008367212640206316</v>
+        <v>0.01481275793674942</v>
       </c>
       <c r="Z38" t="n">
-        <v>-0.001318707098640264</v>
+        <v>-0.01986809171855179</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.04196845334893702</v>
+        <v>0.04594528496591099</v>
       </c>
       <c r="AB38" t="n">
-        <v>-0.07188612629757719</v>
+        <v>-0.08411941622961244</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.03826403504689955</v>
+        <v>0.01856310268264218</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.04184125845058375</v>
+        <v>-0.01927207793431578</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0.02131551747179619</v>
+        <v>-0.02524996387762798</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.07737308647122249</v>
+        <v>0.02932280958967689</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.2299191137310003</v>
+        <v>0.2350679324462549</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.05440568318083076</v>
+        <v>0.07069885923522307</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.04050372650058295</v>
+        <v>0.03103768593000859</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.02757115949809522</v>
+        <v>0.03061360632851289</v>
       </c>
       <c r="AK38" t="n">
-        <v>-0.009724934215663361</v>
+        <v>-0.06948258108656435</v>
       </c>
       <c r="AL38" t="n">
         <v>1</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.009158040022286392</v>
+        <v>0.007004212744583222</v>
       </c>
     </row>
     <row r="39">
@@ -5104,115 +5104,115 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.02356751784422266</v>
+        <v>-0.01153433783728882</v>
       </c>
       <c r="C39" t="n">
-        <v>0.09285420806081821</v>
+        <v>0.09337859248232171</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.132974891054905</v>
+        <v>-0.1202532894096583</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.0182348649208518</v>
+        <v>0.008066099441391051</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1583703193751885</v>
+        <v>0.1233841420151827</v>
       </c>
       <c r="G39" t="n">
-        <v>0.04206301245545643</v>
+        <v>0.05375488601022387</v>
       </c>
       <c r="H39" t="n">
-        <v>0.04159135941381416</v>
+        <v>0.02349933314193967</v>
       </c>
       <c r="I39" t="n">
-        <v>0.01175153130266056</v>
+        <v>0.007960125724786068</v>
       </c>
       <c r="J39" t="n">
-        <v>0.04344884681400774</v>
+        <v>0.1005430860688317</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1719640818434555</v>
+        <v>0.1391279009679643</v>
       </c>
       <c r="L39" t="n">
-        <v>0.04422131885005764</v>
+        <v>0.04490067847168426</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.004442661562165791</v>
+        <v>-0.03248599822604527</v>
       </c>
       <c r="N39" t="n">
-        <v>0.06043314061843652</v>
+        <v>0.01866377910837834</v>
       </c>
       <c r="O39" t="n">
-        <v>0.0364422421236778</v>
+        <v>0.03987860464449715</v>
       </c>
       <c r="P39" t="n">
-        <v>0.06560257166452294</v>
+        <v>0.04572139647582533</v>
       </c>
       <c r="Q39" t="n">
-        <v>-0.05921562488546625</v>
+        <v>0.01139611505143039</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.09227270806344895</v>
+        <v>-0.07935022954746014</v>
       </c>
       <c r="S39" t="n">
-        <v>-0.1201712782548971</v>
+        <v>-0.08910589315564565</v>
       </c>
       <c r="T39" t="n">
-        <v>-0.0944442778409173</v>
+        <v>-0.01419843883629691</v>
       </c>
       <c r="U39" t="n">
-        <v>-0.1207906220624961</v>
+        <v>-0.01254719346114898</v>
       </c>
       <c r="V39" t="n">
-        <v>-0.03466037578468611</v>
+        <v>-0.02420958839001201</v>
       </c>
       <c r="W39" t="n">
-        <v>0.05743700788546895</v>
+        <v>0.05631938963740523</v>
       </c>
       <c r="X39" t="n">
-        <v>0.04288568974563574</v>
+        <v>0.03408872175788728</v>
       </c>
       <c r="Y39" t="n">
-        <v>-0.1110169822412851</v>
+        <v>-0.08814755491224889</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.02298395062106526</v>
+        <v>0.05457044928817863</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.0411458088196802</v>
+        <v>0.05395999196570581</v>
       </c>
       <c r="AB39" t="n">
-        <v>-0.04453039166457341</v>
+        <v>-0.04513258315519091</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.02715984333781421</v>
+        <v>0.03948681695964336</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.06147210330866285</v>
+        <v>-0.06142063364338014</v>
       </c>
       <c r="AE39" t="n">
-        <v>-0.01609719787912343</v>
+        <v>-0.004231438816541684</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.03893810004768056</v>
+        <v>0.05226552907284862</v>
       </c>
       <c r="AG39" t="n">
-        <v>-0.01148040364927585</v>
+        <v>-0.02095105694814079</v>
       </c>
       <c r="AH39" t="n">
-        <v>-0.07857443134371904</v>
+        <v>-0.07076813412655004</v>
       </c>
       <c r="AI39" t="n">
-        <v>-0.02733344394835103</v>
+        <v>-0.04003305270695982</v>
       </c>
       <c r="AJ39" t="n">
-        <v>-0.009684040952457802</v>
+        <v>-0.005297148565513779</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.08598707547789738</v>
+        <v>0.09663512782242119</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.009158040022286392</v>
+        <v>0.007004212744583222</v>
       </c>
       <c r="AM39" t="n">
         <v>1</v>
